--- a/docs/가게조사_챔필주변_초안.xlsx
+++ b/docs/가게조사_챔필주변_초안.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>광주 북구 하서로 52</t>
+          <t>전남광주 북구 하서로 52</t>
         </is>
       </c>
       <c r="F3" s="11" t="n"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="X3" s="11" t="inlineStr">
         <is>
-          <t>1992년 지방 공립미술관으로는 처음 개관했고, 2007년 중외공원 안 현재 건물로 신축 이전했다. 관람료는 무료이며 유료 특별기획전은 별도 요금이 있을 수 있다.</t>
+          <t>1992년 개관한 공립미술관. 2007년 중외공원 안 지금 건물로 이전, 관람 무료</t>
         </is>
       </c>
       <c r="Y3" s="11" t="n"/>
@@ -1219,14 +1219,10 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AA3" s="11" t="inlineStr">
-        <is>
-          <t>Claude(웹 검색)</t>
-        </is>
-      </c>
+      <c r="AA3" s="11" t="n"/>
       <c r="AB3" s="11" t="inlineStr">
         <is>
-          <t>머무는 시간은 추정치. [웹 출처 대조, 현장 미확인] WebFetch 가 모든 도메인에서 DNS 오류로 실패해 공식 누리집 본문을 직접 열지 못했다. 값은 WebSearch 결과 요약(광주시 문화 페이지 포함)을 기준으로 했다. 2026년 본관 휴관·공사 공지는 찾지 못했고, 플레이광주에 본관 전시(제3·4전시실 2026.3.17~2027.2.28)가 진행 중으로 나와 있다. 위키백과는 관람시간을 09:00-18:00으로 적어 광주시 페이지(10:00-18:00)와 다르다. 개관일은 1992년 8월 1일이라는 자료와 7월 개관 예정이라는 1992년 기사가 엇갈린다. 출처: https://www.gwangju.go.kr/culture/contentsView.do?pageId=culture24 https://ko.wikipedia.org/wiki/%EA%B4%91%EC%A3%BC%EC%8B%9C%EB%A6%BD%EB%AF%B8%EC%88%A0%EA%B4%80 https://namu.wiki/w/%EA%B4%91%EC%A3%BC%EC%8B%9C%EB%A6%BD%EB%AF%B8%EC%88%A0%EA%B4%80 https://www.ktriptips.com/kor/culture/129761 https://playgwangju.co.kr/bbs/board.php?bo_table=hall&amp;wr_id=9 https://www.d-art.co.kr/news/articleView.html?idxno=4842</t>
+          <t>매월 마지막 수요일 20:00까지. 유료 특별전은 별도 요금. 출처: https://www.gwangju.go.kr/culture/contentsView.do?pageId=culture24. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1249,7 @@
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>광주 북구 서하로 48-25</t>
+          <t>전남광주 북구 서하로 48-25</t>
         </is>
       </c>
       <c r="F4" s="11" t="n"/>
@@ -1316,7 +1312,7 @@
       </c>
       <c r="X4" s="11" t="inlineStr">
         <is>
-          <t>1987년 광주직할시립민속박물관으로 개관했고, 1995년 광주광역시립민속박물관을 거쳐 2020년 6월 1일 광주역사민속박물관으로 이름을 바꿨다. 남도 민속과 광주 근대 역사·문화를 전시한다.</t>
+          <t>남도 민속과 광주 근대사를 전시하는 박물관. 옛 광주시립민속박물관(2020년 개칭), 관람 무료</t>
         </is>
       </c>
       <c r="Y4" s="11" t="n"/>
@@ -1325,14 +1321,10 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AA4" s="11" t="inlineStr">
-        <is>
-          <t>Claude(웹 검색)</t>
-        </is>
-      </c>
+      <c r="AA4" s="11" t="n"/>
       <c r="AB4" s="11" t="inlineStr">
         <is>
-          <t>머무는 시간은 추정치. [웹 출처 대조, 현장 미확인] 이름이 바뀌었다. 2020년 개보수 뒤 개칭했으며, 디지털광주문화대전·플레이광주는 개칭일을 2020.6.1로, 이뉴스투데이 2020.5.26 기사는 5.27 재개관으로 적는다. 관람시간·휴관일은 공식 누리집의 검색 요약 기준이다(중앙이코노미뉴스는 계절별 09:30-18:00/17:00, 1/1·1/2 휴관으로 적었으나 오래된 정보로 보임). 관람료는 공식 페이지에서 확인하지 못했고 리뷰·안내 사이트의 무료 표기를 따랐다. 사전예약 현황에 따라 현장 접수가 제한될 수 있다고 한다. area 는 중외공원 일대여서 운암동으로 적었으나 법정동은 확인하지 못했다. 출처: https://www.gwangju.go.kr/gjhfm/ https://gwangju.grandculture.net/gwangju/toc/GC60004155 https://playgwangju.co.kr/bbs/board.php?bo_table=hall&amp;wr_id=46 https://www.enewstoday.co.kr/news/articleView.html?idxno=1389480 https://ko.wikipedia.org/wiki/%EA%B4%91%EC%A3%BC%EC%97%AD%EC%82%AC%EB%AF%BC%EC%86%8D%EB%B0%95%EB%AC%BC%EA%B4%80 https://www.yugacrew.com/gwangju/bukgu/museum/118_10</t>
+          <t>매주 수요일 20:00까지(2026.4.1부터). 공휴일 다음 날 휴관. 관람료 무료는 안내 사이트 기준. 출처: https://www.gwangju.go.kr/gjhfm/. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1351,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>광주 북구 하서로 110</t>
+          <t>전남광주 북구 하서로 110</t>
         </is>
       </c>
       <c r="F5" s="11" t="n"/>
@@ -1418,7 +1410,7 @@
       </c>
       <c r="X5" s="11" t="inlineStr">
         <is>
-          <t>1978년 12월 6일 개관한 국립박물관이다. 상설전시는 무료이고(유료 특별전 제외), 어린이박물관은 10:00-17:00, 박물관 정원은 08:00-20:00에 개방한다.</t>
+          <t>1978년 개관한 국립박물관. 상설전시 무료, 정원은 08:00-20:00 개방</t>
         </is>
       </c>
       <c r="Y5" s="11" t="n"/>
@@ -1427,14 +1419,10 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AA5" s="11" t="inlineStr">
-        <is>
-          <t>Claude(웹 검색)</t>
-        </is>
-      </c>
+      <c r="AA5" s="11" t="n"/>
       <c r="AB5" s="11" t="inlineStr">
         <is>
-          <t>정기 휴관 요일 없음(1/1, 설·추석 당일, 9·12월 둘째 월요일 임시 휴실). 머무는 시간은 추정치. [웹 출처 대조, 현장 미확인] 정기휴관이 매주 월요일이 아니라 1/1·설·추석 당일뿐이라는 것은 공식 관람안내 검색 요약 기준이다. 토요일 야간 개장은 출처마다 다르고(4~11월 토 20:00, 매주 토 21:00, 3~10월 토·마지막 수 21:00) 공식 메인에서는 확인되지 않아 hours 에 넣지 않았다. area 의 법정동(매곡동)은 하서로 110 위치를 기준으로 추정했으며 출처로 확인하지 못했다. 출처: https://gwangju.museum.go.kr/kor/sub01_01.do https://gwangju.museum.go.kr/ https://www.ktriptips.com/kor/culture/129782 https://tour.gwangju.go.kr/home/tour/info/culture.cs?act=view&amp;infoId=291 https://xn--ok0b236bp0a.com/place/26422</t>
+          <t>정기 휴관 요일 없음(1/1, 설·추석 당일, 9·12월 둘째 월요일 임시 휴실). 입장 마감 17:30. 토요일 야간 개장은 출처마다 달라 넣지 않음. 출처: https://gwangju.museum.go.kr/kor/sub01_01.do. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1449,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>광주 북구 하서로 50</t>
+          <t>전남광주 북구 하서로 50</t>
         </is>
       </c>
       <c r="F6" s="11" t="n"/>
@@ -1516,7 +1504,7 @@
       </c>
       <c r="X6" s="11" t="inlineStr">
         <is>
-          <t>북구 운암동 일대의 근린공원으로, 안에 광주비엔날레 전시관·광주시립미술관·광주역사민속박물관·국립광주박물관·광주예술의전당이 모여 있다. 제1회 광주비엔날레를 기념한 김영종 작가의 무지개다리를 건너 문화시설들로 이어진다.</t>
+          <t>시립미술관·역사민속박물관·국립광주박물관·예술의전당이 모인 근린공원</t>
         </is>
       </c>
       <c r="Y6" s="11" t="n"/>
@@ -1525,14 +1513,10 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AA6" s="11" t="inlineStr">
-        <is>
-          <t>Claude(웹 검색)</t>
-        </is>
-      </c>
+      <c r="AA6" s="11" t="n"/>
       <c r="AB6" s="11" t="inlineStr">
         <is>
-          <t>머무는 시간은 추정치. [웹 출처 대조, 현장 미확인] 24시간·무료는 나무위키 기준이며 공식 출처로 확인하지 못했다. 도로명 주소(하서로 50)는 검색 요약에 나온 값이라 다시 확인이 필요하다. 면적은 출처마다 다르다(나무위키 2,439,130㎡, 디지털광주문화대전 438,693㎡). 민간공원 특례사업으로 약 208만㎡ 부지에 개발이 진행 중이라는 보도가 있어 일부 구역이 공사 중일 수 있다. 출처: https://gwangju.grandculture.net/gwangju/bukgu/toc/GC60000605 https://namu.wiki/w/%EC%A4%91%EC%99%B8%EA%B3%B5%EC%9B%90 https://www.culture.go.kr/portal/cltLife/cltVideo/viewPortal.do?idx=3808&amp;category=video&amp;menuNo=200046&amp;pageIndex=1 https://m.sedaily.com/article/13825732 https://m.news.nate.com/view/20260320n29351</t>
+          <t>24시간 개방은 공식 출처로 확인 못 함. 도로명 주소 재확인 필요. 민간공원 특례사업으로 일부 공사 중일 수 있음. 출처: https://gwangju.grandculture.net/gwangju/bukgu/toc/GC60000605. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1543,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>광주광역시 북구 하서로 52</t>
+          <t>전남광주 북구 하서로 52</t>
         </is>
       </c>
       <c r="F7" s="11" t="n"/>
@@ -1618,7 +1602,7 @@
       </c>
       <c r="X7" s="11" t="inlineStr">
         <is>
-          <t>광주시립미술관이 중외공원에 조성해 2024년 9월 7일 개장한 약 5만6200㎡ 규모의 예술정원이다. 예술의전당과 시립미술관을 잇는 길이 347m의 공중연결로 '하늘다리'(높이 20m 승강기)와, 옛 어린이대공원 자리에 만든 생태예술놀이터(물놀이장, 9m 모험놀이대)가 있다.</t>
+          <t>2024년 9월 개장한 중외공원 예술정원. 예술의전당과 시립미술관을 잇는 하늘다리(347m)</t>
         </is>
       </c>
       <c r="Y7" s="11" t="n"/>
@@ -1627,14 +1611,10 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AA7" s="11" t="inlineStr">
-        <is>
-          <t>Claude(웹 검색)</t>
-        </is>
-      </c>
+      <c r="AA7" s="11" t="n"/>
       <c r="AB7" s="11" t="inlineStr">
         <is>
-          <t>도로명 주소를 못 찾아 시립미술관 주소를 넣었다. 가져온 뒤 장소 관리 화면에서 지도로 좌표를 고칠 것. 머무는 시간은 추정치. [웹 출처 대조, 현장 미확인] 추가 장소다. 도로명 주소는 따로 확인하지 못했다(시립미술관 하서로 52 주변). 상시 개방·무료·승강기 06:00-21:00은 육아 정보 사이트(맘맘) 한 곳에만 나온다. 물놀이장은 계절에 따라 운영할 것으로 보이나 확인하지 못했다. 시립미술관 관람과 묶어 짧은 산책 코스로 쓰기 좋다. 출처: https://www.seoul.co.kr/news/society/2024/09/06/20240906500031 https://www.namdonews.com/news/articleView.html?idxno=788443 https://mgj.nocutnews.co.kr/news/6207571 https://www.latimes.kr/news/articleView.html?idxno=52397 https://mom-mom.net/travel/places/69087347538f6ff43f3536d2</t>
+          <t>도로명 주소를 못 찾아 시립미술관 주소를 넣음. 가져온 뒤 지도에서 좌표 수정 필요. 하늘다리 승강기 06:00-21:00(블로그 출처). 출처: https://www.seoul.co.kr/news/society/2024/09/06/20240906500031. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1641,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>광주광역시 북구 용봉로 77</t>
+          <t>전남광주 북구 용봉로 77</t>
         </is>
       </c>
       <c r="F8" s="11" t="n"/>
@@ -1716,7 +1696,7 @@
       </c>
       <c r="X8" s="11" t="inlineStr">
         <is>
-          <t>5·18 사적지 제1호. 1980년 5월 18일 아침 정문 앞에서 학생들과 계엄군이 충돌한 5·18민주화운동의 발원지로 꼽힌다. 2026년 5월 18일 정문 일원에 당시 장면을 담은 부조 작품 등을 갖춘 '5·18 기억의 정원'이 개원했다.</t>
+          <t>5·18 사적지 제1호. 1980년 5월 18일 학생과 계엄군이 처음 충돌한 곳, 2026년 5·18 기억의 정원 개원</t>
         </is>
       </c>
       <c r="Y8" s="11" t="n"/>
@@ -1725,14 +1705,10 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AA8" s="11" t="inlineStr">
-        <is>
-          <t>Claude(웹 검색)</t>
-        </is>
-      </c>
+      <c r="AA8" s="11" t="n"/>
       <c r="AB8" s="11" t="inlineStr">
         <is>
-          <t>주소는 대학 대표 주소. 정문 위치로 좌표 확인 필요. 머무는 시간은 추정치. [웹 출처 대조, 현장 미확인] 사적지 번호는 광주시 5·18 사적지 안내 페이지 검색 요약과 언론 기사에서 확인했다(WebFetch가 DNS 오류로 실패해서 원문 페이지를 직접 열지는 못함). 주소 용봉로 77은 대학 대표 주소다. 표지석의 정확한 위치와 야간 출입 제한 여부는 확인하지 못했다. 정문 앞 녹지에 조성한다고 보도된 '민주공원(가칭)'이 기억의 정원과 같은 사업인지는 불분명하다. 출처: https://www.gwangju.go.kr/518/contentsView.do?pageId=maycenter43 https://namu.wiki/w/5.18%20%EC%82%AC%EC%A0%81%EC%A7%80%20%EB%AA%A9%EB%A1%9D https://dhnews.co.kr/news/view/1065592552782970 https://www.wikitree.co.kr/articles/1137184 https://www.heraldk.com/article/2026040419124343952</t>
+          <t>주소는 대학 대표 주소. 정문 위치로 좌표 확인 필요. 출처: https://www.gwangju.go.kr/518/contentsView.do?pageId=maycenter43. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1735,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>광주광역시 북구 무등로 235</t>
+          <t>전남광주 북구 무등로 235</t>
         </is>
       </c>
       <c r="F9" s="11" t="n"/>
@@ -1814,7 +1790,7 @@
       </c>
       <c r="X9" s="11" t="inlineStr">
         <is>
-          <t>5·18 사적지 제2호. 1980년 5월 20일 밤 공수부대가 시민들에게 발포해 다수의 사상자가 난 곳이다.</t>
+          <t>5·18 사적지 제2호. 1980년 5월 20일 밤 계엄군 발포가 있었던 곳</t>
         </is>
       </c>
       <c r="Y9" s="11" t="n"/>
@@ -1823,14 +1799,10 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AA9" s="11" t="inlineStr">
-        <is>
-          <t>Claude(웹 검색)</t>
-        </is>
-      </c>
+      <c r="AA9" s="11" t="n"/>
       <c r="AB9" s="11" t="inlineStr">
         <is>
-          <t>머무는 시간은 추정치. [웹 출처 대조, 현장 미확인] 사적지 지정은 확인했다. 현재 모습은 확인하지 못했다: 광주역 일대 도시재생·민간복합개발(빛고을창업스테이션 등)이 추진 중이지만 2026년 기준 광장 공사 여부, 표지석 위치와 상태는 출처가 없다. 주소 무등로 235는 나무위키 기준이다. 2026년 4월 전남대 정문(제1호)에서 광주역(제2호)까지 잇는 '5·18 캠퍼스 마라톤'이 열렸다. 경기 동선에서 볼거리가 적으니 짧게 들르는 곳으로 쓰는 것을 권한다. 출처: https://www.gwangju.go.kr/518/contentsView.do?pageId=maycenter43 https://namu.wiki/w/5.18%20%EC%82%AC%EC%A0%81%EC%A7%80%20%EB%AA%A9%EB%A1%9D https://www.ohmynews.com/NWS_Web/View/at_pg.aspx?CNTN_CD=A0003125716 https://korean.visitkorea.or.kr/detail/rem_detail.do?cotid=c95936b0-952d-422d-9f72-9b8b954d6e6a https://view.asiae.co.kr/article/2026040514550266571</t>
+          <t>광장의 현재 모습·표지석 위치는 확인 못 함. 볼거리가 적어 짧게 들르는 곳. 출처: https://www.gwangju.go.kr/518/contentsView.do?pageId=maycenter43. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1829,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>광주광역시 북구 용봉로 77</t>
+          <t>전남광주 북구 용봉로 77</t>
         </is>
       </c>
       <c r="F10" s="11" t="n"/>
@@ -1920,7 +1892,7 @@
       </c>
       <c r="X10" s="11" t="inlineStr">
         <is>
-          <t>1957년 4월 15일 설립된 대학 박물관으로 일반인도 무료로 관람할 수 있다. 목제 민속유물 등을 소장하며, 2층에는 남도서화실(2012년 조성)과 기획전시실이 있다.</t>
+          <t>1957년 설립된 대학 박물관. 남도서화실·기획전시실, 일반인 무료 관람</t>
         </is>
       </c>
       <c r="Y10" s="11" t="n"/>
@@ -1929,14 +1901,10 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AA10" s="11" t="inlineStr">
-        <is>
-          <t>Claude(웹 검색)</t>
-        </is>
-      </c>
+      <c r="AA10" s="11" t="n"/>
       <c r="AB10" s="11" t="inlineStr">
         <is>
-          <t>2·4주 토요일 휴관은 휴무 요일 칸으로 표현할 수 없어 토요일은 운영으로 두었다. 주말 방문 전 062-530-3583 확인. 머무는 시간은 추정치. [웹 출처 대조, 현장 미확인] 휴관일은 출처마다 다르다. 공식 관람안내는 법정공휴일, 설·추석 연휴, 개교기념일(6/9)만 휴관으로 적었고, 대학 대표 홈페이지는 '평일 및 1·3주 토요일 10:00-17:00 개방'이라고 적었다. 그래서 일요일과 2·4주 토요일은 휴관으로 보수적으로 적었다. 제3자 사이트는 주말에도 연다고 적어 서로 맞지 않는다. 토·일 방문 전에는 062-530-3583~5로 확인이 필요하다. 주소는 대학 대표 주소이며, 박물관 건물의 개별 주소는 확인하지 못했다. 의학박물관(동구 학동)은 다른 시설이다. 출처: https://museum.jnu.ac.kr/museum/14597/subview.do https://www.jnu.ac.kr/MainUniLife/Welfare/Display https://www.jnu.ac.kr/Data/tmfiles/Down/introduction/DirectoryBulletin/2023_2024/7-3.pdf https://dhnews.co.kr/news/view/179516627630301</t>
+          <t>주말 운영은 출처마다 다름(2·4주 토요일·일요일 휴관으로 적은 곳 있음). 방문 전 062-530-3583 확인. 출처: https://museum.jnu.ac.kr/museum/14597/subview.do. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1931,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>광주광역시 서구 학생독립로 30</t>
+          <t>전남광주 서구 학생독립로 30</t>
         </is>
       </c>
       <c r="F11" s="11" t="n"/>
@@ -2026,7 +1994,7 @@
       </c>
       <c r="X11" s="11" t="inlineStr">
         <is>
-          <t>1929년 광주학생독립운동을 기념하는 전시관이다. 2005년 11월 서구 화정동에 신축 개관했으며(국가보훈부 현충시설 자료상 건립일 2005-11-03), 높이 39m 기념탑과 야외 원형 무대가 있다.</t>
+          <t>1929년 광주학생독립운동 기념관. 2005년 개관, 높이 39m 기념탑, 관람 무료</t>
         </is>
       </c>
       <c r="Y11" s="11" t="n"/>
@@ -2035,14 +2003,10 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AA11" s="11" t="inlineStr">
-        <is>
-          <t>Claude(웹 검색)</t>
-        </is>
-      </c>
+      <c r="AA11" s="11" t="n"/>
       <c r="AB11" s="11" t="inlineStr">
         <is>
-          <t>머무는 시간은 추정치. [웹 출처 대조, 현장 미확인] 주소와 시간은 한국관광공사 데이터 기반 사이트(기준일 2026-08-14)와 나무위키가 일치한다. 공식 누리집에 2026년 월별 휴관일 공지가 있다(예: 5/1 노동절 휴관). 리모델링 휴관 공지는 찾지 못했다. 이름이 비슷한 '학생독립운동기념회관'(교육청 도서관 등, 1967년 동구 황금동에서 개관, 2014년 이전)은 다른 시설이다. 광주제일고 교정의 기념탑·기념역사관과도 다르다. 챔필(임동)과의 거리는 약 3~4km로 추정한다(직접 측정하지 않음). 출처: https://www.ktriptips.com/kor/culture/129757 https://gsim.gen.go.kr:446/main/main.php https://namu.wiki/w/%EA%B4%91%EC%A3%BC%ED%95%99%EC%83%9D%EB%8F%85%EB%A6%BD%EC%9A%B4%EB%8F%99%EA%B8%B0%EB%85%90%EA%B4%80 http://mfis.mpva.go.kr/memorial/movementView.do?gubunCode=DR&amp;sid=220&amp;pageIndex=1&amp;searFacilgubun=&amp;searTopicsort=&amp;searAddr_sigun=&amp;searMpvabranch=&amp;searVR=&amp;searGbn=tit&amp;searTxt= https://i815.or.kr/memorial/museum/Museum07_GSIMMH/html/index.html</t>
+          <t>공휴일 휴관(3·1절·현충일·광복절은 개관). 출처: https://www.ktriptips.com/kor/culture/129757. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2033,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>광주광역시 북구 동문대로85번길 62</t>
+          <t>전남광주 북구 동문대로85번길 62</t>
         </is>
       </c>
       <c r="F12" s="11" t="n"/>
@@ -2128,7 +2092,7 @@
       </c>
       <c r="X12" s="11" t="inlineStr">
         <is>
-          <t>끝자리가 2·4·7·9인 날(한 달 12번)에 장이 서는 광주 대표 장터다. 2·7일은 큰 장, 4·9일은 작은 장이다. 상설 점포 약 500개에 장날에는 노점 800여 개가 더 들어선다.</t>
+          <t>끝자리 2·4·7·9일에 장이 서는 전통시장. 2·7일 큰 장, 상설 점포 약 500개</t>
         </is>
       </c>
       <c r="Y12" s="11" t="n"/>
@@ -2137,14 +2101,10 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AA12" s="11" t="inlineStr">
-        <is>
-          <t>Claude(웹 검색)</t>
-        </is>
-      </c>
+      <c r="AA12" s="11" t="n"/>
       <c r="AB12" s="11" t="inlineStr">
         <is>
-          <t>1인 지출은 다른 시장 데이터에 맞춘 추정치(10,000원). 장날(2·4·7·9일)이 아니면 상설 점포만 연다. 머무는 시간은 추정치. [웹 출처 대조, 현장 미확인] 장날은 2, 4, 7, 9일이다(매달 2·4·7·9·12·14·17·19·22·24·27·29일). 영업시간은 출처마다 다르다. 한국관광공사 국문은 07:00-19:00, 영문은 장날 06:00-21:00·평일 07:00-20:00, 여행기사는 10:00-18:00(하절기 19시)로 적었다. hours 에는 국문 공식값을 넣었다. 문의 062-262-4082. 장날이 아니면 상설 점포만 연다. 챔필과의 거리는 확인하지 않았다(우산동이라 4km 안팎일 수 있음). 출처: https://www.ktriptips.com/kor/shopping/1433867 https://english.visitkorea.or.kr/svc/contents/contentsView.do?vcontsId=184226 https://korean.visitkorea.or.kr/detail/rem_detail.do?cotid=6145f0e4-b6ca-4537-a8be-18deaccf7f5a https://dh.aks.ac.kr/~gwangju/wiki/index.php/광주의_장날 https://gwangju.grandculture.net/gwangju/bukgu/toc/GC60005096</t>
+          <t>장날이 아니면 상설 점포만 엶. 영업시간은 출처마다 다름(한국관광공사 국문 기준). 1인 지출은 다른 시장에 맞춘 어림값. 출처: https://www.ktriptips.com/kor/shopping/1433867. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2131,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>광주광역시 남구 중앙로107번길 15</t>
+          <t>전남광주 남구 중앙로107번길 15</t>
         </is>
       </c>
       <c r="F13" s="11" t="n"/>
@@ -2226,7 +2186,7 @@
       </c>
       <c r="X13" s="11" t="inlineStr">
         <is>
-          <t>광주 제1호 도시공원으로 소개되며, 공원 안에 현충탑(높이 25m, 광주·전남 출신 한국전쟁 전몰자 15,867명 이름 수록), 시민회관(1971년 건립), 4·19 희생자 기념비 등이 있다. 매년 6월 6일 현충탑에서 현충일 추념식이 열린다(2026년 제71회 포함). 공원 앞으로 광주천이 흐른다.</t>
+          <t>광주 제1호 도시공원. 현충탑·시민회관(1971년)·4·19 기념비, 앞으로 광주천이 흐름</t>
         </is>
       </c>
       <c r="Y13" s="11" t="n"/>
@@ -2235,14 +2195,10 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AA13" s="11" t="inlineStr">
-        <is>
-          <t>Claude(웹 검색)</t>
-        </is>
-      </c>
+      <c r="AA13" s="11" t="n"/>
       <c r="AB13" s="11" t="inlineStr">
         <is>
-          <t>머무는 시간은 추정치. [웹 출처 대조, 현장 미확인] WebFetch 가 모든 도메인에서 DNS 오류라 검색 결과 요약으로만 확인. 상시 개방·연중무휴는 TourAPI 계열 집계 사이트 기준(일부는 '24시간' 표기). '시민의 종'은 광주공원 관련 어떤 출처에서도 확인되지 않음(광주의 타종 행사는 '민주의 종'으로 보도되며 위치 미확인). 공원관리사무소 062-672-0660. 출처 일부는 행정명을 '전남광주통합특별시'로 표기. 현충탑 건립 연도 미확인. 출처: https://www.wegive.co.kr/contents/wetownDetail/127075 https://www.koreatriptips.com/tourist-attractions/127075.html https://www.ktourmap.com/spotDetails.jsp?contentId=127075 https://xn--ok0b236bp0a.com/place/6410 https://www.twig24.com/news/local_gj/2026/06/06/20260606500017</t>
+          <t>상시 개방·무료. 바로 앞 광주공원 포장마차 거리와 이어짐. 출처: https://www.wegive.co.kr/contents/wetownDetail/127075. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2225,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>광주광역시 서구 상무민주로 61</t>
+          <t>전남광주 서구 상무민주로 61</t>
         </is>
       </c>
       <c r="F14" s="11" t="n"/>
@@ -2324,7 +2280,7 @@
       </c>
       <c r="X14" s="11" t="inlineStr">
         <is>
-          <t>1994년 상무대 이전 뒤 광주시가 양여받은 부지에 1996년 11월 착공해 1998년 10월 완공했다. 현황조각, 추모승화공간, 대동광장, 오월루(5·18상징탑)와 5·18기념문화센터, 연못·잔디광장·산책로 등이 있으며 면적의 약 45%가 녹지다.</t>
+          <t>옛 상무대 자리에 1998년 조성한 5·18 기념공원. 오월루·추모승화공간·산책로</t>
         </is>
       </c>
       <c r="Y14" s="11" t="n"/>
@@ -2333,14 +2289,10 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AA14" s="11" t="inlineStr">
-        <is>
-          <t>Claude(웹 검색)</t>
-        </is>
-      </c>
+      <c r="AA14" s="11" t="n"/>
       <c r="AB14" s="11" t="inlineStr">
         <is>
-          <t>머무는 시간은 추정치. [웹 출처 대조, 현장 미확인] 조성 면적 출처별 상이(204,985㎡ 광주시 현황 / 205,000㎡ / 208,000㎡). 도로명 주소가 '상무민주로 61'과 '내방로 152'(문화센터 주소)로 엇갈림(우편번호 61965 동일). 이용시간도 '상시 개방'과 '09:00-18:00'으로 엇갈림. 공원 야외 공간은 상시 개방으로 적었으나 공식 확인은 못 함. 입장 무료, 주차 가능. 출처: https://www.gwangju.go.kr/518/contentsView.do?pageId=maycenter59 https://gwangju.grandculture.net/gwangju/seogu/toc/GC60000592 https://korean.visitkorea.or.kr/detail/ms_detail.do?cotid=6370af0e-2293-4319-a10c-b4cf342ea558 https://www.ktriptips.com/kor/tourspot/129444</t>
+          <t>이용시간이 출처마다 다름(상시 개방 / 09:00-18:00). 주소도 상무민주로 61 / 내방로 152 로 엇갈림. 출처: https://www.gwangju.go.kr/518/contentsView.do?pageId=maycenter59. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2319,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>광주광역시 서구 내방로 152</t>
+          <t>전남광주 서구 내방로 152</t>
         </is>
       </c>
       <c r="F15" s="11" t="n"/>
@@ -2422,7 +2374,7 @@
       </c>
       <c r="X15" s="11" t="inlineStr">
         <is>
-          <t>5·18기념공원 안에 있는 광주시 시설로 1998년 1월 1일 개소, 2001년 7월 23일 5·18기념문화센터로 명칭을 바꿨다. 5·18 정신을 기리고 교육 공간으로 쓰인다.</t>
+          <t>5·18기념공원 안 광주시 시설(1998년 개소). 5·18 교육·전시 공간</t>
         </is>
       </c>
       <c r="Y15" s="11" t="n"/>
@@ -2431,14 +2383,10 @@
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="AA15" s="11" t="inlineStr">
-        <is>
-          <t>Claude(웹 검색)</t>
-        </is>
-      </c>
+      <c r="AA15" s="11" t="n"/>
       <c r="AB15" s="11" t="inlineStr">
         <is>
-          <t>머무는 시간은 추정치. [웹 출처 대조, 현장 미확인] 09:00-18:00 은 TourAPI 계열 집계 사이트 기준. 휴관일은 '연중무휴'/'휴관일 없음'(집계 사이트)과 '매주 주말'(블로그)로 엇갈려 null. 입장료 0 은 공원 무료 안내에 근거한 것으로 센터 전시실 무료 여부는 직접 확인 못 함. 2025~2026 휴관·리모델링 공지는 검색되지 않음. 문의 062-376-5197 / 062-613-7916 두 번호가 혼재. 상설 전시 내용 미확인. 출처: https://ko.wikipedia.org/wiki/%EA%B4%91%EC%A3%BC%EA%B4%91%EC%97%AD%EC%8B%9C5%C2%B718%EA%B8%B0%EB%85%90%EB%AC%B8%ED%99%94%EC%84%BC%ED%84%B0 https://www.culture.go.kr/space/facilityView.do?seq=2727 https://www.wegive.co.kr/contents/wetownDetail/3029585 https://www.gwangju.go.kr/518/contentsView.do?pageId=maycenter35 https://gwangju.grandculture.net/gwangju/toc/GC60003359</t>
+          <t>휴관일은 출처마다 달라 비워 둠. 전시실 무료 여부 확인 필요. 출처: https://ko.wikipedia.org/wiki/%EA%B4%91%EC%A3%BC%EA%B4%91%EC%97%AD%EC%8B%9C5%C2%B718%EA%B8%B0%EB%85%90%EB%AC%B8%ED%99%94%EC%84%BC%ED%84%B0. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
         </is>
       </c>
     </row>

--- a/docs/가게조사_챔필주변_초안.xlsx
+++ b/docs/가게조사_챔필주변_초안.xlsx
@@ -2396,33 +2396,97 @@
           <t>n_014</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>광주비엔날레 전시관</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>북구 용봉동</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 비엔날레로 111</t>
+        </is>
+      </c>
       <c r="F16" s="11" t="n"/>
       <c r="G16" s="11" t="n"/>
-      <c r="H16" s="12" t="n"/>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>10:00-18:00</t>
+        </is>
+      </c>
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
       <c r="L16" s="11" t="n"/>
-      <c r="M16" s="11" t="n"/>
-      <c r="N16" s="11" t="n"/>
+      <c r="M16" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="N16" s="11" t="n">
+        <v>20000</v>
+      </c>
       <c r="O16" s="11" t="n"/>
       <c r="P16" s="11" t="n"/>
       <c r="Q16" s="11" t="n"/>
-      <c r="R16" s="11" t="n"/>
-      <c r="S16" s="11" t="n"/>
-      <c r="T16" s="11" t="n"/>
-      <c r="U16" s="11" t="n"/>
-      <c r="V16" s="11" t="n"/>
-      <c r="W16" s="11" t="n"/>
-      <c r="X16" s="11" t="n"/>
+      <c r="R16" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 사진, 건축 구경</t>
+        </is>
+      </c>
+      <c r="S16" s="11" t="inlineStr">
+        <is>
+          <t>현대적인, 활기찬</t>
+        </is>
+      </c>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U16" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V16" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>비엔날레 전시관, 광주비엔날레전시관, 광주비엔날레</t>
+        </is>
+      </c>
+      <c r="X16" s="11" t="inlineStr">
+        <is>
+          <t>광주비엔날레 본전시장. 제16회 광주비엔날레 2026.9.5~11.15</t>
+        </is>
+      </c>
       <c r="Y16" s="11" t="n"/>
-      <c r="Z16" s="12" t="n"/>
+      <c r="Z16" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA16" s="11" t="n"/>
-      <c r="AB16" s="11" t="n"/>
+      <c r="AB16" s="11" t="inlineStr">
+        <is>
+          <t>기간 한정: 2026.11.15 비엔날레 폐막 뒤 운영·요금 확인 못 함. 폐막 후에는 빼거나 다시 확인할 것. 1인 지출은 성인 현장가(지역민 14,000). 운영시간은 10:00-18:00 / 10:00-17:30 으로 출처가 다름. 출처: https://www.gwangjubiennale.org/gb/exhibition/biennale/visitorinfo.do?subPage=ticketInfo. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -2430,33 +2494,97 @@
           <t>n_015</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>대인예술야시장</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>야간 콘텐츠</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>동구 대인동</t>
+        </is>
+      </c>
       <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="12" t="n"/>
+      <c r="F17" s="11" t="n">
+        <v>35.1541</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>126.9182</v>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>16:00-21:00</t>
+        </is>
+      </c>
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
-      <c r="L17" s="11" t="n"/>
-      <c r="M17" s="11" t="n"/>
-      <c r="N17" s="11" t="n"/>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>지정 운영일(금 또는 토)에만 열림</t>
+        </is>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>10000</v>
+      </c>
       <c r="O17" s="11" t="n"/>
       <c r="P17" s="11" t="n"/>
       <c r="Q17" s="11" t="n"/>
-      <c r="R17" s="11" t="n"/>
-      <c r="S17" s="11" t="n"/>
-      <c r="T17" s="11" t="n"/>
-      <c r="U17" s="11" t="n"/>
-      <c r="V17" s="11" t="n"/>
-      <c r="W17" s="11" t="n"/>
-      <c r="X17" s="11" t="n"/>
+      <c r="R17" s="11" t="inlineStr">
+        <is>
+          <t>시장 구경, 길거리 음식, 쇼핑, 공방 체험</t>
+        </is>
+      </c>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>활기찬, 정겨운, 캐주얼한</t>
+        </is>
+      </c>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U17" s="11" t="inlineStr">
+        <is>
+          <t>오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V17" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>대인야시장, 남도달밤야시장</t>
+        </is>
+      </c>
+      <c r="X17" s="11" t="inlineStr">
+        <is>
+          <t>대인예술시장 일원 야시장. 2026년 6/19~10/31 금 또는 토 지정일, 총 12회, 공연·플리마켓</t>
+        </is>
+      </c>
       <c r="Y17" s="11" t="n"/>
-      <c r="Z17" s="12" t="n"/>
+      <c r="Z17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA17" s="11" t="n"/>
-      <c r="AB17" s="11" t="n"/>
+      <c r="AB17" s="11" t="inlineStr">
+        <is>
+          <t>기간 한정: 2026 시즌 10/31 종료. 운영일이 주마다 달라 휴무 요일로 표현할 수 없음(비워 둠). 21:00 종료라 야간경기 뒤에는 어려움. 도로명 주소 미확인, 좌표는 기존 대인예술시장(daein_market) 값을 씀. 1인 지출은 어림값. 출처: https://www.sidae.com/article/2026061809281153906. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -2464,33 +2592,101 @@
           <t>n_016</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>군분로 토요 야시장</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>야간 콘텐츠</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>남구 월산동</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 군분로 41</t>
+        </is>
+      </c>
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="12" t="n"/>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>17:00-21:00</t>
+        </is>
+      </c>
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="11" t="n"/>
-      <c r="M18" s="11" t="n"/>
-      <c r="N18" s="11" t="n"/>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>월, 화, 수, 목, 금, 일</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>2026년 10/17·24·31 토요일만</t>
+        </is>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N18" s="11" t="n">
+        <v>10000</v>
+      </c>
       <c r="O18" s="11" t="n"/>
       <c r="P18" s="11" t="n"/>
       <c r="Q18" s="11" t="n"/>
-      <c r="R18" s="11" t="n"/>
-      <c r="S18" s="11" t="n"/>
-      <c r="T18" s="11" t="n"/>
-      <c r="U18" s="11" t="n"/>
-      <c r="V18" s="11" t="n"/>
-      <c r="W18" s="11" t="n"/>
-      <c r="X18" s="11" t="n"/>
+      <c r="R18" s="11" t="inlineStr">
+        <is>
+          <t>시장 구경, 길거리 음식, 산책, 사진</t>
+        </is>
+      </c>
+      <c r="S18" s="11" t="inlineStr">
+        <is>
+          <t>활기찬, 정겨운, 레트로한</t>
+        </is>
+      </c>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U18" s="11" t="inlineStr">
+        <is>
+          <t>저녁, 밤</t>
+        </is>
+      </c>
+      <c r="V18" s="11" t="inlineStr">
+        <is>
+          <t>친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>무등시장 야시장, 토요 밤마실 야시장</t>
+        </is>
+      </c>
+      <c r="X18" s="11" t="inlineStr">
+        <is>
+          <t>무등시장 군분로 1.1km 구간 토요 야시장. 운영일 차 없는 거리, 국악·통기타 공연</t>
+        </is>
+      </c>
       <c r="Y18" s="11" t="n"/>
-      <c r="Z18" s="12" t="n"/>
+      <c r="Z18" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA18" s="11" t="n"/>
-      <c r="AB18" s="11" t="n"/>
+      <c r="AB18" s="11" t="inlineStr">
+        <is>
+          <t>운영시간 미확인: 17:00-21:00 은 임시값, 남구청·상인회 확인 필요. 기간 한정: 2026 시즌 10/31 종료. 주소는 시장 근처 건물(군분로 41)로 대신 넣음, 가져온 뒤 지도에서 좌표 수정. 1인 지출은 어림값. 출처: https://www.wikitree.co.kr/articles/1165478. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">

--- a/docs/가게조사_챔필주변_초안.xlsx
+++ b/docs/가게조사_챔필주변_초안.xlsx
@@ -2694,33 +2694,93 @@
           <t>n_017</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>상무시민공원</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>서구 치평동</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 서구 상무공원로 101</t>
+        </is>
+      </c>
       <c r="F19" s="11" t="n"/>
       <c r="G19" s="11" t="n"/>
-      <c r="H19" s="12" t="n"/>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="11" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="11" t="n"/>
+      <c r="M19" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O19" s="11" t="n"/>
       <c r="P19" s="11" t="n"/>
       <c r="Q19" s="11" t="n"/>
-      <c r="R19" s="11" t="n"/>
-      <c r="S19" s="11" t="n"/>
-      <c r="T19" s="11" t="n"/>
-      <c r="U19" s="11" t="n"/>
-      <c r="V19" s="11" t="n"/>
-      <c r="W19" s="11" t="n"/>
-      <c r="X19" s="11" t="n"/>
+      <c r="R19" s="11" t="inlineStr">
+        <is>
+          <t>산책, 사진, 휴식, 야경</t>
+        </is>
+      </c>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 캐주얼한, 현대적인</t>
+        </is>
+      </c>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U19" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁, 밤</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>상무시민공원 조각공원</t>
+        </is>
+      </c>
+      <c r="X19" s="11" t="inlineStr">
+        <is>
+          <t>상무지구 아파트 단지 안 근린공원. 인공호수 2개, 호숫가 조각공원(야간 조명)</t>
+        </is>
+      </c>
       <c r="Y19" s="11" t="n"/>
-      <c r="Z19" s="12" t="n"/>
+      <c r="Z19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA19" s="11" t="n"/>
-      <c r="AB19" s="11" t="n"/>
+      <c r="AB19" s="11" t="inlineStr">
+        <is>
+          <t>상시 개방은 안내 사이트 기준. 주소가 상무시민로 3 으로 적힌 곳도 있음. 출처: https://www.ktriptips.com/kor/tourspot/1622203. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
@@ -2728,33 +2788,93 @@
           <t>n_018</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>5·18자유공원</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>서구 치평동</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 서구 상무평화로 13</t>
+        </is>
+      </c>
       <c r="F20" s="11" t="n"/>
       <c r="G20" s="11" t="n"/>
-      <c r="H20" s="12" t="n"/>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="11" t="n"/>
-      <c r="M20" s="11" t="n"/>
-      <c r="N20" s="11" t="n"/>
+      <c r="M20" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N20" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O20" s="11" t="n"/>
       <c r="P20" s="11" t="n"/>
       <c r="Q20" s="11" t="n"/>
-      <c r="R20" s="11" t="n"/>
-      <c r="S20" s="11" t="n"/>
-      <c r="T20" s="11" t="n"/>
-      <c r="U20" s="11" t="n"/>
-      <c r="V20" s="11" t="n"/>
-      <c r="W20" s="11" t="n"/>
-      <c r="X20" s="11" t="n"/>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 전시 관람, 산책</t>
+        </is>
+      </c>
+      <c r="S20" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 레트로한</t>
+        </is>
+      </c>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U20" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V20" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>5.18자유공원, 오일팔자유공원, 상무대 옛터</t>
+        </is>
+      </c>
+      <c r="X20" s="11" t="inlineStr">
+        <is>
+          <t>상무대 군사법정·영창을 옮겨 원형 복원한 곳. 5·18 사적 제17호 '상무대 옛터'</t>
+        </is>
+      </c>
       <c r="Y20" s="11" t="n"/>
-      <c r="Z20" s="12" t="n"/>
+      <c r="Z20" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA20" s="11" t="n"/>
-      <c r="AB20" s="11" t="n"/>
+      <c r="AB20" s="11" t="inlineStr">
+        <is>
+          <t>겨울에는 09:00-17:00(블로그 기준). 휴관일 미확인. 사적 17호는 '상무대 옛터'로 지정된 것. 출처: https://www.gwangju.go.kr/518/contentsView.do?pageId=maycenter34. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -2762,33 +2882,101 @@
           <t>n_019</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>광주에너지파크 해담마루</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>서구 치평동</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 서구 상무공원로 131</t>
+        </is>
+      </c>
       <c r="F21" s="11" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="12" t="n"/>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>09:00-17:00</t>
+        </is>
+      </c>
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="11" t="n"/>
-      <c r="N21" s="11" t="n"/>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>일, 월</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>법정 공휴일</t>
+        </is>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O21" s="11" t="n"/>
       <c r="P21" s="11" t="n"/>
       <c r="Q21" s="11" t="n"/>
-      <c r="R21" s="11" t="n"/>
-      <c r="S21" s="11" t="n"/>
-      <c r="T21" s="11" t="n"/>
-      <c r="U21" s="11" t="n"/>
-      <c r="V21" s="11" t="n"/>
-      <c r="W21" s="11" t="n"/>
-      <c r="X21" s="11" t="n"/>
+      <c r="R21" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 공방 체험</t>
+        </is>
+      </c>
+      <c r="S21" s="11" t="inlineStr">
+        <is>
+          <t>현대적인, 조용한</t>
+        </is>
+      </c>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U21" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V21" s="11" t="inlineStr">
+        <is>
+          <t>가족, 아이 동반, 친구</t>
+        </is>
+      </c>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>해담마루, 광주에너지파크</t>
+        </is>
+      </c>
+      <c r="X21" s="11" t="inlineStr">
+        <is>
+          <t>상무시민공원 안 에너지·기후변화 전시·체험관. 2021년 개관, 무료</t>
+        </is>
+      </c>
       <c r="Y21" s="11" t="n"/>
-      <c r="Z21" s="12" t="n"/>
+      <c r="Z21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA21" s="11" t="n"/>
-      <c r="AB21" s="11" t="n"/>
+      <c r="AB21" s="11" t="inlineStr">
+        <is>
+          <t>12:00-13:00 휴게, 입장 마감 16:30. 법정 공휴일 휴관. 운영시간 출처는 한 곳. 출처: https://www.ktriptips.com/kor/culture/3442399. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2796,33 +2984,97 @@
           <t>n_020</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>기분좋은극장</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>서구 치평동</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 서구 상무중앙로 90 (우리은행 상무지점 7층)</t>
+        </is>
+      </c>
       <c r="F22" s="11" t="n"/>
       <c r="G22" s="11" t="n"/>
-      <c r="H22" s="12" t="n"/>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>14:00-21:30</t>
+        </is>
+      </c>
       <c r="I22" s="12" t="n"/>
       <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
       <c r="L22" s="11" t="n"/>
-      <c r="M22" s="11" t="n"/>
-      <c r="N22" s="11" t="n"/>
+      <c r="M22" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>40000</v>
+      </c>
       <c r="O22" s="11" t="n"/>
       <c r="P22" s="11" t="n"/>
       <c r="Q22" s="11" t="n"/>
-      <c r="R22" s="11" t="n"/>
-      <c r="S22" s="11" t="n"/>
-      <c r="T22" s="11" t="n"/>
-      <c r="U22" s="11" t="n"/>
-      <c r="V22" s="11" t="n"/>
-      <c r="W22" s="11" t="n"/>
-      <c r="X22" s="11" t="n"/>
+      <c r="R22" s="11" t="inlineStr">
+        <is>
+          <t>공연·영화</t>
+        </is>
+      </c>
+      <c r="S22" s="11" t="inlineStr">
+        <is>
+          <t>아늑한, 캐주얼한, 활기찬</t>
+        </is>
+      </c>
+      <c r="T22" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U22" s="11" t="inlineStr">
+        <is>
+          <t>오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V22" s="11" t="inlineStr">
+        <is>
+          <t>친구, 연인, 혼자</t>
+        </is>
+      </c>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>기분좋은극장 상무점</t>
+        </is>
+      </c>
+      <c r="X22" s="11" t="inlineStr">
+        <is>
+          <t>상무지구 건물 7층 연극 전용 소극장. 화-금 19:30, 주말 14:00·17:00 공연</t>
+        </is>
+      </c>
       <c r="Y22" s="11" t="n"/>
-      <c r="Z22" s="12" t="n"/>
+      <c r="Z22" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA22" s="11" t="n"/>
-      <c r="AB22" s="11" t="n"/>
+      <c r="AB22" s="11" t="inlineStr">
+        <is>
+          <t>공연 시각에만 볼 수 있는데 시간표 칸이 없어 영업시간을 14:00-21:30 으로 넣음(평일 낮에 잘못 추천될 수 있음). 1인 지출은 2026년 공연 전석가. 출처: https://www.ktriptips.com/kor/culture/3038297. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -2830,33 +3082,93 @@
           <t>n_021</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>광주천 벚꽃길</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>서구 쌍촌동</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 서구 쌍촌동 914-1</t>
+        </is>
+      </c>
       <c r="F23" s="11" t="n"/>
       <c r="G23" s="11" t="n"/>
-      <c r="H23" s="12" t="n"/>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I23" s="12" t="n"/>
       <c r="J23" s="12" t="n"/>
       <c r="K23" s="12" t="n"/>
       <c r="L23" s="11" t="n"/>
-      <c r="M23" s="11" t="n"/>
-      <c r="N23" s="11" t="n"/>
+      <c r="M23" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O23" s="11" t="n"/>
       <c r="P23" s="11" t="n"/>
       <c r="Q23" s="11" t="n"/>
-      <c r="R23" s="11" t="n"/>
-      <c r="S23" s="11" t="n"/>
-      <c r="T23" s="11" t="n"/>
-      <c r="U23" s="11" t="n"/>
-      <c r="V23" s="11" t="n"/>
-      <c r="W23" s="11" t="n"/>
-      <c r="X23" s="11" t="n"/>
+      <c r="R23" s="11" t="inlineStr">
+        <is>
+          <t>산책, 사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S23" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 캐주얼한, 정겨운</t>
+        </is>
+      </c>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U23" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V23" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>광주천 유채꽃길, 광천1교-서창 벚꽃길</t>
+        </is>
+      </c>
+      <c r="X23" s="11" t="inlineStr">
+        <is>
+          <t>광천제1교~서창 영산강 쉼터 약 3km 천변길. 봄 벚꽃·유채꽃</t>
+        </is>
+      </c>
       <c r="Y23" s="11" t="n"/>
-      <c r="Z23" s="12" t="n"/>
+      <c r="Z23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA23" s="11" t="n"/>
-      <c r="AB23" s="11" t="n"/>
+      <c r="AB23" s="11" t="inlineStr">
+        <is>
+          <t>계절 명소(봄). 그 밖의 계절에는 일반 천변 산책로. 주소는 지번. 주차 불가. 출처: https://www.ktriptips.com/kor/tourspot/2774295. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -2864,33 +3176,93 @@
           <t>n_022</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>풍암호수공원</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>서구 풍암동</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 서구 풍암동 460</t>
+        </is>
+      </c>
       <c r="F24" s="11" t="n"/>
       <c r="G24" s="11" t="n"/>
-      <c r="H24" s="12" t="n"/>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I24" s="12" t="n"/>
       <c r="J24" s="12" t="n"/>
       <c r="K24" s="12" t="n"/>
       <c r="L24" s="11" t="n"/>
-      <c r="M24" s="11" t="n"/>
-      <c r="N24" s="11" t="n"/>
+      <c r="M24" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O24" s="11" t="n"/>
       <c r="P24" s="11" t="n"/>
       <c r="Q24" s="11" t="n"/>
-      <c r="R24" s="11" t="n"/>
-      <c r="S24" s="11" t="n"/>
-      <c r="T24" s="11" t="n"/>
-      <c r="U24" s="11" t="n"/>
-      <c r="V24" s="11" t="n"/>
-      <c r="W24" s="11" t="n"/>
-      <c r="X24" s="11" t="n"/>
+      <c r="R24" s="11" t="inlineStr">
+        <is>
+          <t>산책, 사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 캐주얼한</t>
+        </is>
+      </c>
+      <c r="T24" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U24" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V24" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>풍암호수, 풍암호, 풍암저수지</t>
+        </is>
+      </c>
+      <c r="X24" s="11" t="inlineStr">
+        <is>
+          <t>1956년 농업용 저수지로 만든 호수공원. 장미원(140여 종)</t>
+        </is>
+      </c>
       <c r="Y24" s="11" t="n"/>
-      <c r="Z24" s="12" t="n"/>
+      <c r="Z24" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA24" s="11" t="n"/>
-      <c r="AB24" s="11" t="n"/>
+      <c r="AB24" s="11" t="inlineStr">
+        <is>
+          <t>2025.6~2027.10 수질개선 공사로 통행 제한 보도가 있으나 팀원이 2026년 10월 방문해 이용 가능 확인. 개방 시간은 임시값(상시). 주소는 지번. 출처: https://www.newsis.com/view/NISX20250423_0003150264. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -2898,33 +3270,93 @@
           <t>n_023</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>전평제근린공원</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>서구 매월동</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 서구 전평길 1</t>
+        </is>
+      </c>
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="11" t="n"/>
-      <c r="H25" s="12" t="n"/>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I25" s="12" t="n"/>
       <c r="J25" s="12" t="n"/>
       <c r="K25" s="12" t="n"/>
       <c r="L25" s="11" t="n"/>
-      <c r="M25" s="11" t="n"/>
-      <c r="N25" s="11" t="n"/>
+      <c r="M25" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N25" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O25" s="11" t="n"/>
       <c r="P25" s="11" t="n"/>
       <c r="Q25" s="11" t="n"/>
-      <c r="R25" s="11" t="n"/>
-      <c r="S25" s="11" t="n"/>
-      <c r="T25" s="11" t="n"/>
-      <c r="U25" s="11" t="n"/>
-      <c r="V25" s="11" t="n"/>
-      <c r="W25" s="11" t="n"/>
-      <c r="X25" s="11" t="n"/>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>산책, 사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S25" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 정겨운</t>
+        </is>
+      </c>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U25" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V25" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>전평제, 전평저수지</t>
+        </is>
+      </c>
+      <c r="X25" s="11" t="inlineStr">
+        <is>
+          <t>서구 매월동 저수지 공원. 인공섬을 잇는 목교, 회재 박광옥 유허비와 관련된 이름</t>
+        </is>
+      </c>
       <c r="Y25" s="11" t="n"/>
-      <c r="Z25" s="12" t="n"/>
+      <c r="Z25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA25" s="11" t="n"/>
-      <c r="AB25" s="11" t="n"/>
+      <c r="AB25" s="11" t="inlineStr">
+        <is>
+          <t>주소·상시 개방·무료는 안내 사이트 한 곳 기준. 정식 공원 명칭 미확인. 출처: https://www.ktriptips.com/kor/tourspot/1621573. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -2932,33 +3364,101 @@
           <t>n_024</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>서창한옥문화관</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>서구 세하동</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 서구 눌재로 420</t>
+        </is>
+      </c>
       <c r="F26" s="11" t="n"/>
       <c r="G26" s="11" t="n"/>
-      <c r="H26" s="12" t="n"/>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="11" t="n"/>
-      <c r="M26" s="11" t="n"/>
-      <c r="N26" s="11" t="n"/>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>토,일</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>공휴일, 2026-11-16 임시 휴관</t>
+        </is>
+      </c>
+      <c r="M26" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N26" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O26" s="11" t="n"/>
       <c r="P26" s="11" t="n"/>
       <c r="Q26" s="11" t="n"/>
-      <c r="R26" s="11" t="n"/>
-      <c r="S26" s="11" t="n"/>
-      <c r="T26" s="11" t="n"/>
-      <c r="U26" s="11" t="n"/>
-      <c r="V26" s="11" t="n"/>
-      <c r="W26" s="11" t="n"/>
-      <c r="X26" s="11" t="n"/>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>건축 구경, 공방 체험, 사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>전통적인, 조용한, 아늑한</t>
+        </is>
+      </c>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U26" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V26" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>서창전통한옥체험관, 전통한옥체험관, 서창한옥</t>
+        </is>
+      </c>
+      <c r="X26" s="11" t="inlineStr">
+        <is>
+          <t>2004년 전통한옥체험관으로 개관(2017년 개칭). 전통문화강좌·한옥스테이</t>
+        </is>
+      </c>
       <c r="Y26" s="11" t="n"/>
-      <c r="Z26" s="12" t="n"/>
+      <c r="Z26" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA26" s="11" t="n"/>
-      <c r="AB26" s="11" t="n"/>
+      <c r="AB26" s="11" t="inlineStr">
+        <is>
+          <t>서창동이 아니라 세하동. 평일 09:00-18:00 은 고객센터 시간일 수 있음(주말 관람 가능 여부 미확인). 2026-11-16 임시 휴관. 체험은 재료비 별도. 출처: http://www.schanok.or.kr/. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -2966,33 +3466,93 @@
           <t>n_025</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>서창 감성조망대</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>서구 서창동</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 서구 서창동 1044-17</t>
+        </is>
+      </c>
       <c r="F27" s="11" t="n"/>
       <c r="G27" s="11" t="n"/>
-      <c r="H27" s="12" t="n"/>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I27" s="12" t="n"/>
       <c r="J27" s="12" t="n"/>
       <c r="K27" s="12" t="n"/>
       <c r="L27" s="11" t="n"/>
-      <c r="M27" s="11" t="n"/>
-      <c r="N27" s="11" t="n"/>
+      <c r="M27" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N27" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O27" s="11" t="n"/>
       <c r="P27" s="11" t="n"/>
       <c r="Q27" s="11" t="n"/>
-      <c r="R27" s="11" t="n"/>
-      <c r="S27" s="11" t="n"/>
-      <c r="T27" s="11" t="n"/>
-      <c r="U27" s="11" t="n"/>
-      <c r="V27" s="11" t="n"/>
-      <c r="W27" s="11" t="n"/>
-      <c r="X27" s="11" t="n"/>
+      <c r="R27" s="11" t="inlineStr">
+        <is>
+          <t>사진, 산책, 야경, 휴식</t>
+        </is>
+      </c>
+      <c r="S27" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 현대적인</t>
+        </is>
+      </c>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U27" s="11" t="inlineStr">
+        <is>
+          <t>오후, 저녁, 밤</t>
+        </is>
+      </c>
+      <c r="V27" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>서창감성조망대, 나눔누리숲, 노을마루, 나눔누리정원</t>
+        </is>
+      </c>
+      <c r="X27" s="11" t="inlineStr">
+        <is>
+          <t>영산강 옛 서창포구의 뫼비우스 띠 모양 조망 데크(166m). 2025년 10월 개장, 일몰 명소</t>
+        </is>
+      </c>
       <c r="Y27" s="11" t="n"/>
-      <c r="Z27" s="12" t="n"/>
+      <c r="Z27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA27" s="11" t="n"/>
-      <c r="AB27" s="11" t="n"/>
+      <c r="AB27" s="11" t="inlineStr">
+        <is>
+          <t>주소는 지번. 24시간·무료는 여행 매체 한 곳 기준. 출처: https://www.heraldk.com/article/2025092121560617941. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -3000,33 +3560,93 @@
           <t>n_026</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>송정떡갈비골목</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>광산구 송정동</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 광산구 광산로29번길 1</t>
+        </is>
+      </c>
       <c r="F28" s="11" t="n"/>
       <c r="G28" s="11" t="n"/>
-      <c r="H28" s="12" t="n"/>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>11:00-21:00</t>
+        </is>
+      </c>
       <c r="I28" s="12" t="n"/>
       <c r="J28" s="12" t="n"/>
       <c r="K28" s="12" t="n"/>
       <c r="L28" s="11" t="n"/>
-      <c r="M28" s="11" t="n"/>
-      <c r="N28" s="11" t="n"/>
+      <c r="M28" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N28" s="11" t="n">
+        <v>18000</v>
+      </c>
       <c r="O28" s="11" t="n"/>
       <c r="P28" s="11" t="n"/>
       <c r="Q28" s="11" t="n"/>
-      <c r="R28" s="11" t="n"/>
-      <c r="S28" s="11" t="n"/>
-      <c r="T28" s="11" t="n"/>
-      <c r="U28" s="11" t="n"/>
-      <c r="V28" s="11" t="n"/>
-      <c r="W28" s="11" t="n"/>
-      <c r="X28" s="11" t="n"/>
+      <c r="R28" s="11" t="inlineStr">
+        <is>
+          <t>식사</t>
+        </is>
+      </c>
+      <c r="S28" s="11" t="inlineStr">
+        <is>
+          <t>정겨운, 전통적인, 활기찬</t>
+        </is>
+      </c>
+      <c r="T28" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U28" s="11" t="inlineStr">
+        <is>
+          <t>오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V28" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>광주 송정동 떡갈비 골목, 송정동 향토 떡갈비 거리, 송정 떡갈비 거리</t>
+        </is>
+      </c>
+      <c r="X28" s="11" t="inlineStr">
+        <is>
+          <t>송정 떡갈비 전문점 10~20곳이 모인 골목. 광주시 지정 향토 떡갈비 거리</t>
+        </is>
+      </c>
       <c r="Y28" s="11" t="n"/>
-      <c r="Z28" s="12" t="n"/>
+      <c r="Z28" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA28" s="11" t="n"/>
-      <c r="AB28" s="11" t="n"/>
+      <c r="AB28" s="11" t="inlineStr">
+        <is>
+          <t>영업시간은 임시값(가게마다 다름). 주소는 송정떡갈비 1호점. 1인 지출은 리뷰 메뉴판 기준(15,000~18,000). 출처: https://www.ktriptips.com/kor/tourspot/2605353. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -3034,33 +3654,93 @@
           <t>n_027</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>수완호수공원</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>광산구 장덕동</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 광산구 장신로82번길 57</t>
+        </is>
+      </c>
       <c r="F29" s="11" t="n"/>
       <c r="G29" s="11" t="n"/>
-      <c r="H29" s="12" t="n"/>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I29" s="12" t="n"/>
       <c r="J29" s="12" t="n"/>
       <c r="K29" s="12" t="n"/>
       <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
-      <c r="N29" s="11" t="n"/>
+      <c r="M29" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="N29" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O29" s="11" t="n"/>
       <c r="P29" s="11" t="n"/>
       <c r="Q29" s="11" t="n"/>
-      <c r="R29" s="11" t="n"/>
-      <c r="S29" s="11" t="n"/>
-      <c r="T29" s="11" t="n"/>
-      <c r="U29" s="11" t="n"/>
-      <c r="V29" s="11" t="n"/>
-      <c r="W29" s="11" t="n"/>
-      <c r="X29" s="11" t="n"/>
+      <c r="R29" s="11" t="inlineStr">
+        <is>
+          <t>산책, 야경, 사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S29" s="11" t="inlineStr">
+        <is>
+          <t>캐주얼한, 현대적인, 활기찬</t>
+        </is>
+      </c>
+      <c r="T29" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U29" s="11" t="inlineStr">
+        <is>
+          <t>오후, 저녁, 밤</t>
+        </is>
+      </c>
+      <c r="V29" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>광주 수완호수공원, 수완호수</t>
+        </is>
+      </c>
+      <c r="X29" s="11" t="inlineStr">
+        <is>
+          <t>수완지구 호수공원. 호수 둘레길, 풍영정천 둑길, 분수</t>
+        </is>
+      </c>
       <c r="Y29" s="11" t="n"/>
-      <c r="Z29" s="12" t="n"/>
+      <c r="Z29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA29" s="11" t="n"/>
-      <c r="AB29" s="11" t="n"/>
+      <c r="AB29" s="11" t="inlineStr">
+        <is>
+          <t>주소는 공원관리사무소. 행정동은 장덕동/수완동으로 출처가 다름. 출처: https://korean.visitkorea.or.kr/detail/rem_detail.do?cotid=ed2d1bb6-375c-42c9-a061-27cc4823cc89. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -3068,33 +3748,93 @@
           <t>n_028</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>우치공원 동물원</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>북구 생용동</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 우치로 677</t>
+        </is>
+      </c>
       <c r="F30" s="11" t="n"/>
       <c r="G30" s="11" t="n"/>
-      <c r="H30" s="12" t="n"/>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I30" s="12" t="n"/>
       <c r="J30" s="12" t="n"/>
       <c r="K30" s="12" t="n"/>
       <c r="L30" s="11" t="n"/>
-      <c r="M30" s="11" t="n"/>
-      <c r="N30" s="11" t="n"/>
+      <c r="M30" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="N30" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O30" s="11" t="n"/>
       <c r="P30" s="11" t="n"/>
       <c r="Q30" s="11" t="n"/>
-      <c r="R30" s="11" t="n"/>
-      <c r="S30" s="11" t="n"/>
-      <c r="T30" s="11" t="n"/>
-      <c r="U30" s="11" t="n"/>
-      <c r="V30" s="11" t="n"/>
-      <c r="W30" s="11" t="n"/>
-      <c r="X30" s="11" t="n"/>
+      <c r="R30" s="11" t="inlineStr">
+        <is>
+          <t>산책, 사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S30" s="11" t="inlineStr">
+        <is>
+          <t>캐주얼한, 정겨운, 활기찬</t>
+        </is>
+      </c>
+      <c r="T30" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U30" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V30" s="11" t="inlineStr">
+        <is>
+          <t>가족, 아이 동반, 연인, 친구</t>
+        </is>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>우치동물원, 우치공원동물원</t>
+        </is>
+      </c>
+      <c r="X30" s="11" t="inlineStr">
+        <is>
+          <t>1992년 개원한 시립 동물원. 입장 무료</t>
+        </is>
+      </c>
       <c r="Y30" s="11" t="n"/>
-      <c r="Z30" s="12" t="n"/>
+      <c r="Z30" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA30" s="11" t="n"/>
-      <c r="AB30" s="11" t="n"/>
+      <c r="AB30" s="11" t="inlineStr">
+        <is>
+          <t>입장 마감 17:00. 옆 광주패밀리랜드 안에 벅스랜드(파충류관, 유료)가 있음. 출처: https://www.ktriptips.com/kor/tourspot/2002480. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -3102,33 +3842,93 @@
           <t>n_029</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>광주시민의숲</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>북구</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 추암로 190</t>
+        </is>
+      </c>
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="11" t="n"/>
-      <c r="H31" s="12" t="n"/>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I31" s="12" t="n"/>
       <c r="J31" s="12" t="n"/>
       <c r="K31" s="12" t="n"/>
       <c r="L31" s="11" t="n"/>
-      <c r="M31" s="11" t="n"/>
-      <c r="N31" s="11" t="n"/>
+      <c r="M31" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N31" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O31" s="11" t="n"/>
       <c r="P31" s="11" t="n"/>
       <c r="Q31" s="11" t="n"/>
-      <c r="R31" s="11" t="n"/>
-      <c r="S31" s="11" t="n"/>
-      <c r="T31" s="11" t="n"/>
-      <c r="U31" s="11" t="n"/>
-      <c r="V31" s="11" t="n"/>
-      <c r="W31" s="11" t="n"/>
-      <c r="X31" s="11" t="n"/>
+      <c r="R31" s="11" t="inlineStr">
+        <is>
+          <t>산책, 휴식, 사진</t>
+        </is>
+      </c>
+      <c r="S31" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 캐주얼한, 정겨운</t>
+        </is>
+      </c>
+      <c r="T31" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U31" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>시민의숲</t>
+        </is>
+      </c>
+      <c r="X31" s="11" t="inlineStr">
+        <is>
+          <t>광주시 도시 숲공원. 야영장(57면), 여름 어린이 물놀이장</t>
+        </is>
+      </c>
       <c r="Y31" s="11" t="n"/>
-      <c r="Z31" s="12" t="n"/>
+      <c r="Z31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA31" s="11" t="n"/>
-      <c r="AB31" s="11" t="n"/>
+      <c r="AB31" s="11" t="inlineStr">
+        <is>
+          <t>개방 시간은 임시값(상시). 법정동 미확인. 야영장은 유료·예약제. 출처: https://www.ktriptips.com/kor/tourspot/2783939. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -3136,33 +3936,93 @@
           <t>n_030</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>광주호 호수생태원</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>북구 충효동</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 충효샘길 7</t>
+        </is>
+      </c>
       <c r="F32" s="11" t="n"/>
       <c r="G32" s="11" t="n"/>
-      <c r="H32" s="12" t="n"/>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I32" s="12" t="n"/>
       <c r="J32" s="12" t="n"/>
       <c r="K32" s="12" t="n"/>
       <c r="L32" s="11" t="n"/>
-      <c r="M32" s="11" t="n"/>
-      <c r="N32" s="11" t="n"/>
+      <c r="M32" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N32" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O32" s="11" t="n"/>
       <c r="P32" s="11" t="n"/>
       <c r="Q32" s="11" t="n"/>
-      <c r="R32" s="11" t="n"/>
-      <c r="S32" s="11" t="n"/>
-      <c r="T32" s="11" t="n"/>
-      <c r="U32" s="11" t="n"/>
-      <c r="V32" s="11" t="n"/>
-      <c r="W32" s="11" t="n"/>
-      <c r="X32" s="11" t="n"/>
+      <c r="R32" s="11" t="inlineStr">
+        <is>
+          <t>산책, 사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S32" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 아늑한, 정겨운</t>
+        </is>
+      </c>
+      <c r="T32" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U32" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V32" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>광주호생태원, 광주호수생태원, 광주호</t>
+        </is>
+      </c>
+      <c r="X32" s="11" t="inlineStr">
+        <is>
+          <t>광주호 상류 생태공원. 6개 테마 산책길, 입장·주차 무료</t>
+        </is>
+      </c>
       <c r="Y32" s="11" t="n"/>
-      <c r="Z32" s="12" t="n"/>
+      <c r="Z32" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA32" s="11" t="n"/>
-      <c r="AB32" s="11" t="n"/>
+      <c r="AB32" s="11" t="inlineStr">
+        <is>
+          <t>정확한 개방 시간은 문의하라는 안내. 바로 옆에 충효동 왕버들 군. 출처: https://www.ktriptips.com/kor/tourspot/129443. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -3170,33 +4030,93 @@
           <t>n_031</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>충효동 왕버들 군</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>북구 충효동</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 충효샘길 7</t>
+        </is>
+      </c>
       <c r="F33" s="11" t="n"/>
       <c r="G33" s="11" t="n"/>
-      <c r="H33" s="12" t="n"/>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I33" s="12" t="n"/>
       <c r="J33" s="12" t="n"/>
       <c r="K33" s="12" t="n"/>
       <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
-      <c r="N33" s="11" t="n"/>
+      <c r="M33" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="N33" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O33" s="11" t="n"/>
       <c r="P33" s="11" t="n"/>
       <c r="Q33" s="11" t="n"/>
-      <c r="R33" s="11" t="n"/>
-      <c r="S33" s="11" t="n"/>
-      <c r="T33" s="11" t="n"/>
-      <c r="U33" s="11" t="n"/>
-      <c r="V33" s="11" t="n"/>
-      <c r="W33" s="11" t="n"/>
-      <c r="X33" s="11" t="n"/>
+      <c r="R33" s="11" t="inlineStr">
+        <is>
+          <t>사진, 산책, 역사 탐방</t>
+        </is>
+      </c>
+      <c r="S33" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인, 정겨운</t>
+        </is>
+      </c>
+      <c r="T33" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U33" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V33" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>충효동 왕버들, 충효동 왕버들군, 김덕령 왕버들</t>
+        </is>
+      </c>
+      <c r="X33" s="11" t="inlineStr">
+        <is>
+          <t>2012년 천연기념물로 지정된 약 400년 된 왕버들. 충효마을 경관수</t>
+        </is>
+      </c>
       <c r="Y33" s="11" t="n"/>
-      <c r="Z33" s="12" t="n"/>
+      <c r="Z33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA33" s="11" t="n"/>
-      <c r="AB33" s="11" t="n"/>
+      <c r="AB33" s="11" t="inlineStr">
+        <is>
+          <t>지정 그루 수는 출처마다 다름. 광주호 호수생태원 입구 쪽. 출처: https://encykorea.aks.ac.kr/Article/E0058259. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -3204,33 +4124,101 @@
           <t>n_032</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>충효동 요지 (무등산 분청사기 전시실)</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>북구 충효동</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 풍암제길 14</t>
+        </is>
+      </c>
       <c r="F34" s="11" t="n"/>
       <c r="G34" s="11" t="n"/>
-      <c r="H34" s="12" t="n"/>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I34" s="12" t="n"/>
       <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="11" t="n"/>
-      <c r="M34" s="11" t="n"/>
-      <c r="N34" s="11" t="n"/>
+      <c r="K34" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="L34" s="11" t="inlineStr">
+        <is>
+          <t>월요일이 공휴일이면 다음 날 휴관</t>
+        </is>
+      </c>
+      <c r="M34" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N34" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O34" s="11" t="n"/>
       <c r="P34" s="11" t="n"/>
       <c r="Q34" s="11" t="n"/>
-      <c r="R34" s="11" t="n"/>
-      <c r="S34" s="11" t="n"/>
-      <c r="T34" s="11" t="n"/>
-      <c r="U34" s="11" t="n"/>
-      <c r="V34" s="11" t="n"/>
-      <c r="W34" s="11" t="n"/>
-      <c r="X34" s="11" t="n"/>
+      <c r="R34" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 전시 관람, 공방 체험</t>
+        </is>
+      </c>
+      <c r="S34" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T34" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U34" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V34" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>충효동 분청사기 가마터, 무등산 분청사기 전시실, 충효동요지</t>
+        </is>
+      </c>
+      <c r="X34" s="11" t="inlineStr">
+        <is>
+          <t>사적 제141호 분청사기 가마터. 전시실 2025년 3월 리모델링 재개관</t>
+        </is>
+      </c>
       <c r="Y34" s="11" t="n"/>
-      <c r="Z34" s="12" t="n"/>
+      <c r="Z34" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA34" s="11" t="n"/>
-      <c r="AB34" s="11" t="n"/>
+      <c r="AB34" s="11" t="inlineStr">
+        <is>
+          <t>운영시간은 시점 불명 안내 사이트 기준. 전시실이 가마터와 같은 부지인지 미확인. 관람료 무료는 추정. 출처: https://www.ktriptips.com/kor/tourspot/127323. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -3238,33 +4226,93 @@
           <t>n_033</t>
         </is>
       </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>평촌마을 (무등산 평촌명품마을)</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>북구</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 평촌길 15</t>
+        </is>
+      </c>
       <c r="F35" s="11" t="n"/>
       <c r="G35" s="11" t="n"/>
-      <c r="H35" s="12" t="n"/>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I35" s="12" t="n"/>
       <c r="J35" s="12" t="n"/>
       <c r="K35" s="12" t="n"/>
       <c r="L35" s="11" t="n"/>
-      <c r="M35" s="11" t="n"/>
-      <c r="N35" s="11" t="n"/>
+      <c r="M35" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="N35" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O35" s="11" t="n"/>
       <c r="P35" s="11" t="n"/>
       <c r="Q35" s="11" t="n"/>
-      <c r="R35" s="11" t="n"/>
-      <c r="S35" s="11" t="n"/>
-      <c r="T35" s="11" t="n"/>
-      <c r="U35" s="11" t="n"/>
-      <c r="V35" s="11" t="n"/>
-      <c r="W35" s="11" t="n"/>
-      <c r="X35" s="11" t="n"/>
+      <c r="R35" s="11" t="inlineStr">
+        <is>
+          <t>산책, 공방 체험, 식사, 사진</t>
+        </is>
+      </c>
+      <c r="S35" s="11" t="inlineStr">
+        <is>
+          <t>정겨운, 조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T35" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U35" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V35" s="11" t="inlineStr">
+        <is>
+          <t>가족, 아이 동반, 연인, 친구</t>
+        </is>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>무등산 평촌명품마을, 평촌명품마을</t>
+        </is>
+      </c>
+      <c r="X35" s="11" t="inlineStr">
+        <is>
+          <t>무등산 북쪽 농촌 체험마을. 반딧불이·수달 서식, 반디누리길(왕복 6km)</t>
+        </is>
+      </c>
       <c r="Y35" s="11" t="n"/>
-      <c r="Z35" s="12" t="n"/>
+      <c r="Z35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA35" s="11" t="n"/>
-      <c r="AB35" s="11" t="n"/>
+      <c r="AB35" s="11" t="inlineStr">
+        <is>
+          <t>체험·식사 프로그램은 예약이 필요할 수 있음. 법정동 미확인. 출처: https://www.ktriptips.com/kor/tourspot/2489843. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -3272,33 +4320,89 @@
           <t>n_034</t>
         </is>
       </c>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>광주문학관</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>북구 각화동</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 각화대로 93</t>
+        </is>
+      </c>
       <c r="F36" s="11" t="n"/>
       <c r="G36" s="11" t="n"/>
-      <c r="H36" s="12" t="n"/>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
       <c r="K36" s="12" t="n"/>
       <c r="L36" s="11" t="n"/>
-      <c r="M36" s="11" t="n"/>
-      <c r="N36" s="11" t="n"/>
+      <c r="M36" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N36" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O36" s="11" t="n"/>
       <c r="P36" s="11" t="n"/>
       <c r="Q36" s="11" t="n"/>
-      <c r="R36" s="11" t="n"/>
-      <c r="S36" s="11" t="n"/>
-      <c r="T36" s="11" t="n"/>
-      <c r="U36" s="11" t="n"/>
-      <c r="V36" s="11" t="n"/>
+      <c r="R36" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 카페·디저트, 휴식</t>
+        </is>
+      </c>
+      <c r="S36" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 현대적인, 아늑한</t>
+        </is>
+      </c>
+      <c r="T36" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U36" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V36" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
       <c r="W36" s="11" t="n"/>
-      <c r="X36" s="11" t="n"/>
+      <c r="X36" s="11" t="inlineStr">
+        <is>
+          <t>2024년 개관한 시립 문학관. 광주 4대 문인(박용철·김현승 등) 상설전시</t>
+        </is>
+      </c>
       <c r="Y36" s="11" t="n"/>
-      <c r="Z36" s="12" t="n"/>
+      <c r="Z36" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA36" s="11" t="n"/>
-      <c r="AB36" s="11" t="n"/>
+      <c r="AB36" s="11" t="inlineStr">
+        <is>
+          <t>휴관일 미확인. 입장 마감 17:30. 주소가 금봉미술관과 같게 나옴. 출처: https://kpinews.kr/newsView/1065600035939914. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -3306,33 +4410,89 @@
           <t>n_035</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>광주향교</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>남구 사동</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 중앙로107번길 5</t>
+        </is>
+      </c>
       <c r="F37" s="11" t="n"/>
       <c r="G37" s="11" t="n"/>
-      <c r="H37" s="12" t="n"/>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I37" s="12" t="n"/>
       <c r="J37" s="12" t="n"/>
       <c r="K37" s="12" t="n"/>
       <c r="L37" s="11" t="n"/>
-      <c r="M37" s="11" t="n"/>
-      <c r="N37" s="11" t="n"/>
+      <c r="M37" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="N37" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O37" s="11" t="n"/>
       <c r="P37" s="11" t="n"/>
       <c r="Q37" s="11" t="n"/>
-      <c r="R37" s="11" t="n"/>
-      <c r="S37" s="11" t="n"/>
-      <c r="T37" s="11" t="n"/>
-      <c r="U37" s="11" t="n"/>
-      <c r="V37" s="11" t="n"/>
+      <c r="R37" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 건축 구경, 사진</t>
+        </is>
+      </c>
+      <c r="S37" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T37" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U37" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V37" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
       <c r="W37" s="11" t="n"/>
-      <c r="X37" s="11" t="n"/>
+      <c r="X37" s="11" t="inlineStr">
+        <is>
+          <t>1488년 지금 자리로 옮긴 향교. 광주시 유형문화유산, 대성전·명륜당</t>
+        </is>
+      </c>
       <c r="Y37" s="11" t="n"/>
-      <c r="Z37" s="12" t="n"/>
+      <c r="Z37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA37" s="11" t="n"/>
-      <c r="AB37" s="11" t="n"/>
+      <c r="AB37" s="11" t="inlineStr">
+        <is>
+          <t>개방 시간은 임시값(안내 사이트는 '전화 문의' 062-672-7008). 광주공원 바로 옆. 출처: https://encykorea.aks.ac.kr/Article/E0005302. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
@@ -3340,33 +4500,101 @@
           <t>n_036</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>의재미술관</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>동구 운림동</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 증심사길 155</t>
+        </is>
+      </c>
       <c r="F38" s="11" t="n"/>
       <c r="G38" s="11" t="n"/>
-      <c r="H38" s="12" t="n"/>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>10:00-17:00</t>
+        </is>
+      </c>
       <c r="I38" s="12" t="n"/>
       <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="11" t="n"/>
-      <c r="M38" s="11" t="n"/>
-      <c r="N38" s="11" t="n"/>
+      <c r="K38" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="L38" s="11" t="inlineStr">
+        <is>
+          <t>1/1, 설·추석</t>
+        </is>
+      </c>
+      <c r="M38" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N38" s="11" t="n">
+        <v>2000</v>
+      </c>
       <c r="O38" s="11" t="n"/>
       <c r="P38" s="11" t="n"/>
       <c r="Q38" s="11" t="n"/>
-      <c r="R38" s="11" t="n"/>
-      <c r="S38" s="11" t="n"/>
-      <c r="T38" s="11" t="n"/>
-      <c r="U38" s="11" t="n"/>
-      <c r="V38" s="11" t="n"/>
-      <c r="W38" s="11" t="n"/>
-      <c r="X38" s="11" t="n"/>
+      <c r="R38" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 건축 구경, 산책</t>
+        </is>
+      </c>
+      <c r="S38" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인, 아늑한</t>
+        </is>
+      </c>
+      <c r="T38" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U38" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V38" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>(재)의재문화재단 의재미술관, Uijae Museum of Korean Art</t>
+        </is>
+      </c>
+      <c r="X38" s="11" t="inlineStr">
+        <is>
+          <t>남종화가 의재 허백련 미술관. 2001년 증심사 계곡 옆 개관</t>
+        </is>
+      </c>
       <c r="Y38" s="11" t="n"/>
-      <c r="Z38" s="12" t="n"/>
+      <c r="Z38" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA38" s="11" t="n"/>
-      <c r="AB38" s="11" t="n"/>
+      <c r="AB38" s="11" t="inlineStr">
+        <is>
+          <t>하절기 10:00-17:30, 동절기 10:00-17:00(짧은 쪽을 넣음). 1/1·설·추석 휴관. 관람료 일반 2,000원. 출처: https://ko.wikipedia.org/wiki/%EC%9D%98%EC%9E%AC%EB%AF%B8%EC%88%A0%EA%B4%80. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -3374,33 +4602,97 @@
           <t>n_037</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>광주시립수목원</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>남구 양과동</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 도동길 142</t>
+        </is>
+      </c>
       <c r="F39" s="11" t="n"/>
       <c r="G39" s="11" t="n"/>
-      <c r="H39" s="12" t="n"/>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I39" s="12" t="n"/>
       <c r="J39" s="12" t="n"/>
-      <c r="K39" s="12" t="n"/>
+      <c r="K39" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
       <c r="L39" s="11" t="n"/>
-      <c r="M39" s="11" t="n"/>
-      <c r="N39" s="11" t="n"/>
+      <c r="M39" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="N39" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O39" s="11" t="n"/>
       <c r="P39" s="11" t="n"/>
       <c r="Q39" s="11" t="n"/>
-      <c r="R39" s="11" t="n"/>
-      <c r="S39" s="11" t="n"/>
-      <c r="T39" s="11" t="n"/>
-      <c r="U39" s="11" t="n"/>
-      <c r="V39" s="11" t="n"/>
-      <c r="W39" s="11" t="n"/>
-      <c r="X39" s="11" t="n"/>
+      <c r="R39" s="11" t="inlineStr">
+        <is>
+          <t>산책, 사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S39" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 아늑한</t>
+        </is>
+      </c>
+      <c r="T39" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U39" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V39" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>광주광역시 시립수목원</t>
+        </is>
+      </c>
+      <c r="X39" s="11" t="inlineStr">
+        <is>
+          <t>매립장 주변을 복원한 24ha 수목원. 2025년 12월 광주 제1호 공립수목원 등록</t>
+        </is>
+      </c>
       <c r="Y39" s="11" t="n"/>
-      <c r="Z39" s="12" t="n"/>
+      <c r="Z39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA39" s="11" t="n"/>
-      <c r="AB39" s="11" t="n"/>
+      <c r="AB39" s="11" t="inlineStr">
+        <is>
+          <t>방문자센터·온실은 종료 1시간 전 입장 마감. 주소·무료는 후기 기준. 출처: https://www.twig24.com/news/2025/12/17/20251217500076. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
@@ -3408,33 +4700,97 @@
           <t>n_038</t>
         </is>
       </c>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>무등산국립공원 증심사지구</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>동구 운림동</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 증심사길 177</t>
+        </is>
+      </c>
       <c r="F40" s="11" t="n"/>
       <c r="G40" s="11" t="n"/>
-      <c r="H40" s="12" t="n"/>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I40" s="12" t="n"/>
       <c r="J40" s="12" t="n"/>
       <c r="K40" s="12" t="n"/>
-      <c r="L40" s="11" t="n"/>
-      <c r="M40" s="11" t="n"/>
-      <c r="N40" s="11" t="n"/>
+      <c r="L40" s="11" t="inlineStr">
+        <is>
+          <t>기상특보·산불조심기간 탐방로 부분 통제 가능(미확인)</t>
+        </is>
+      </c>
+      <c r="M40" s="11" t="n">
+        <v>180</v>
+      </c>
+      <c r="N40" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O40" s="11" t="n"/>
       <c r="P40" s="11" t="n"/>
       <c r="Q40" s="11" t="n"/>
-      <c r="R40" s="11" t="n"/>
-      <c r="S40" s="11" t="n"/>
-      <c r="T40" s="11" t="n"/>
-      <c r="U40" s="11" t="n"/>
-      <c r="V40" s="11" t="n"/>
-      <c r="W40" s="11" t="n"/>
-      <c r="X40" s="11" t="n"/>
+      <c r="R40" s="11" t="inlineStr">
+        <is>
+          <t>산책, 사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S40" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 캐주얼한</t>
+        </is>
+      </c>
+      <c r="T40" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U40" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V40" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>증심사 탐방로, 증심사 입구</t>
+        </is>
+      </c>
+      <c r="X40" s="11" t="inlineStr">
+        <is>
+          <t>무등산 대표 등산로 들머리. 증심사~중머리재(편도 약 4km)</t>
+        </is>
+      </c>
       <c r="Y40" s="11" t="n"/>
-      <c r="Z40" s="12" t="n"/>
+      <c r="Z40" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA40" s="11" t="n"/>
-      <c r="AB40" s="11" t="n"/>
+      <c r="AB40" s="11" t="inlineStr">
+        <is>
+          <t>주소는 증심사 주소로 대신. 머무는 시간은 중머리재 왕복 기준이며 서석대·입석대(천연기념물 주상절리)까지는 왕복 4~5시간. 출처: https://mountainandcamp.com/%EB%AC%B4%EB%93%B1%EC%82%B0-%EB%93%B1%EC%82%B0-%EC%BD%94%EC%8A%A4-%EC%A0%95%EB%A6%AC%EC%B4%88%EB%B3%B4%EC%9E%90-%EC%BD%94%EC%8A%A4%EB%B6%80%ED%84%B0-%EC%83%81%EA%B8%89%EC%9E%90-%EC%BD%94%EC%8A%A4-2/. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -3442,33 +4798,93 @@
           <t>n_039</t>
         </is>
       </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>증심사</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>동구 운림동</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 증심사길 177</t>
+        </is>
+      </c>
       <c r="F41" s="11" t="n"/>
       <c r="G41" s="11" t="n"/>
-      <c r="H41" s="12" t="n"/>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>04:30-17:00</t>
+        </is>
+      </c>
       <c r="I41" s="12" t="n"/>
       <c r="J41" s="12" t="n"/>
       <c r="K41" s="12" t="n"/>
       <c r="L41" s="11" t="n"/>
-      <c r="M41" s="11" t="n"/>
-      <c r="N41" s="11" t="n"/>
+      <c r="M41" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N41" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O41" s="11" t="n"/>
       <c r="P41" s="11" t="n"/>
       <c r="Q41" s="11" t="n"/>
-      <c r="R41" s="11" t="n"/>
-      <c r="S41" s="11" t="n"/>
-      <c r="T41" s="11" t="n"/>
-      <c r="U41" s="11" t="n"/>
-      <c r="V41" s="11" t="n"/>
-      <c r="W41" s="11" t="n"/>
-      <c r="X41" s="11" t="n"/>
+      <c r="R41" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 건축 구경, 산책, 사진</t>
+        </is>
+      </c>
+      <c r="S41" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T41" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U41" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V41" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>證心寺</t>
+        </is>
+      </c>
+      <c r="X41" s="11" t="inlineStr">
+        <is>
+          <t>무등산 서쪽 기슭 사찰. 보물 철조비로자나불좌상</t>
+        </is>
+      </c>
       <c r="Y41" s="11" t="n"/>
-      <c r="Z41" s="12" t="n"/>
+      <c r="Z41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA41" s="11" t="n"/>
-      <c r="AB41" s="11" t="n"/>
+      <c r="AB41" s="11" t="inlineStr">
+        <is>
+          <t>관람료 징수 여부 미확인(0 으로 넣음). 증심사지구 등산로 들머리. 출처: https://www.ktriptips.com/kor/tourspot/126351. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
@@ -3476,33 +4892,97 @@
           <t>n_040</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>무등산 옛길 2구간 (원효사~서석대)</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>북구 금곡동</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 무등로 1514-35 (원효사 일대)</t>
+        </is>
+      </c>
       <c r="F42" s="11" t="n"/>
       <c r="G42" s="11" t="n"/>
-      <c r="H42" s="12" t="n"/>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I42" s="12" t="n"/>
       <c r="J42" s="12" t="n"/>
       <c r="K42" s="12" t="n"/>
-      <c r="L42" s="11" t="n"/>
-      <c r="M42" s="11" t="n"/>
-      <c r="N42" s="11" t="n"/>
+      <c r="L42" s="11" t="inlineStr">
+        <is>
+          <t>원효계곡 상가 철거 공사로 일부 탐방로 통제(2026년 5월 보도, 철거 완료 시까지)</t>
+        </is>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>210</v>
+      </c>
+      <c r="N42" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O42" s="11" t="n"/>
       <c r="P42" s="11" t="n"/>
       <c r="Q42" s="11" t="n"/>
-      <c r="R42" s="11" t="n"/>
-      <c r="S42" s="11" t="n"/>
-      <c r="T42" s="11" t="n"/>
-      <c r="U42" s="11" t="n"/>
-      <c r="V42" s="11" t="n"/>
-      <c r="W42" s="11" t="n"/>
-      <c r="X42" s="11" t="n"/>
+      <c r="R42" s="11" t="inlineStr">
+        <is>
+          <t>산책, 역사 탐방, 사진</t>
+        </is>
+      </c>
+      <c r="S42" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T42" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U42" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V42" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인</t>
+        </is>
+      </c>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>원효사지구, 무등산옛길</t>
+        </is>
+      </c>
+      <c r="X42" s="11" t="inlineStr">
+        <is>
+          <t>원효사에서 서석대까지 4.2km 옛길(편도 약 1시간 50분)</t>
+        </is>
+      </c>
       <c r="Y42" s="11" t="n"/>
-      <c r="Z42" s="12" t="n"/>
+      <c r="Z42" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA42" s="11" t="n"/>
-      <c r="AB42" s="11" t="n"/>
+      <c r="AB42" s="11" t="inlineStr">
+        <is>
+          <t>가볍게 걸으려면 원효사~제철유적지(편도 15분)만 왕복. 2026년 5월 원효계곡 상가 철거로 일부 탐방로 통제 보도, 해제 여부 미확인. 출처: https://www.ktriptips.com/kor/leisure/1051809. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
@@ -3510,33 +4990,97 @@
           <t>n_041</t>
         </is>
       </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>광주신세계</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>상점가</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>서구 광천동</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 서구 무진대로 932</t>
+        </is>
+      </c>
       <c r="F43" s="11" t="n"/>
       <c r="G43" s="11" t="n"/>
-      <c r="H43" s="12" t="n"/>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>10:30-20:00</t>
+        </is>
+      </c>
       <c r="I43" s="12" t="n"/>
       <c r="J43" s="12" t="n"/>
       <c r="K43" s="12" t="n"/>
-      <c r="L43" s="11" t="n"/>
-      <c r="M43" s="11" t="n"/>
-      <c r="N43" s="11" t="n"/>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
+          <t>설 당일·익일 휴점(2026년 설 2/16·2/17 휴점 확인), 월 1회 정기 휴점(요일 미확인)</t>
+        </is>
+      </c>
+      <c r="M43" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="N43" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O43" s="11" t="n"/>
       <c r="P43" s="11" t="n"/>
       <c r="Q43" s="11" t="n"/>
-      <c r="R43" s="11" t="n"/>
-      <c r="S43" s="11" t="n"/>
-      <c r="T43" s="11" t="n"/>
-      <c r="U43" s="11" t="n"/>
-      <c r="V43" s="11" t="n"/>
-      <c r="W43" s="11" t="n"/>
-      <c r="X43" s="11" t="n"/>
+      <c r="R43" s="11" t="inlineStr">
+        <is>
+          <t>쇼핑, 식사, 카페·디저트</t>
+        </is>
+      </c>
+      <c r="S43" s="11" t="inlineStr">
+        <is>
+          <t>현대적인, 고급스러운</t>
+        </is>
+      </c>
+      <c r="T43" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U43" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V43" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>신세계백화점 광주점, 광주신세계백화점</t>
+        </is>
+      </c>
+      <c r="X43" s="11" t="inlineStr">
+        <is>
+          <t>1995년 개점한 신세계백화점 광주점. 유스퀘어(광천터미널) 옆</t>
+        </is>
+      </c>
       <c r="Y43" s="11" t="n"/>
-      <c r="Z43" s="12" t="n"/>
+      <c r="Z43" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA43" s="11" t="n"/>
-      <c r="AB43" s="11" t="n"/>
+      <c r="AB43" s="11" t="inlineStr">
+        <is>
+          <t>영업시간은 임시값(공식 확인 못 함). 월 1회 정기 휴점, 요일 미확인. 1인 지출 0 은 입장료 기준. 출처: https://www.hankyung.com/amp/1995082400641. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
@@ -3544,33 +5088,97 @@
           <t>n_042</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="11" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>1913송정역시장</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>전통시장</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>광산구 송정동</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 광산구 송정로8번길 13</t>
+        </is>
+      </c>
       <c r="F44" s="11" t="n"/>
       <c r="G44" s="11" t="n"/>
-      <c r="H44" s="12" t="n"/>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>10:00-21:00</t>
+        </is>
+      </c>
       <c r="I44" s="12" t="n"/>
       <c r="J44" s="12" t="n"/>
       <c r="K44" s="12" t="n"/>
-      <c r="L44" s="11" t="n"/>
-      <c r="M44" s="11" t="n"/>
-      <c r="N44" s="11" t="n"/>
+      <c r="L44" s="11" t="inlineStr">
+        <is>
+          <t>둘째·넷째 월요일 휴무(2019년 기사 기준)</t>
+        </is>
+      </c>
+      <c r="M44" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N44" s="11" t="n">
+        <v>10000</v>
+      </c>
       <c r="O44" s="11" t="n"/>
       <c r="P44" s="11" t="n"/>
       <c r="Q44" s="11" t="n"/>
-      <c r="R44" s="11" t="n"/>
-      <c r="S44" s="11" t="n"/>
-      <c r="T44" s="11" t="n"/>
-      <c r="U44" s="11" t="n"/>
-      <c r="V44" s="11" t="n"/>
-      <c r="W44" s="11" t="n"/>
-      <c r="X44" s="11" t="n"/>
+      <c r="R44" s="11" t="inlineStr">
+        <is>
+          <t>시장 구경, 길거리 음식, 식사, 카페·디저트, 사진</t>
+        </is>
+      </c>
+      <c r="S44" s="11" t="inlineStr">
+        <is>
+          <t>레트로한, 활기찬, 캐주얼한</t>
+        </is>
+      </c>
+      <c r="T44" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U44" s="11" t="inlineStr">
+        <is>
+          <t>오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V44" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>송정역전매일시장, 송정역시장</t>
+        </is>
+      </c>
+      <c r="X44" s="11" t="inlineStr">
+        <is>
+          <t>1913년 문을 연 송정역전매일시장을 2016년 청년 상인 중심으로 재개장. 광주송정역 앞</t>
+        </is>
+      </c>
       <c r="Y44" s="11" t="n"/>
-      <c r="Z44" s="12" t="n"/>
+      <c r="Z44" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA44" s="11" t="n"/>
-      <c r="AB44" s="11" t="n"/>
+      <c r="AB44" s="11" t="inlineStr">
+        <is>
+          <t>영업시간은 임시값(점포마다 다름). 둘째·넷째 월요일 휴무(2019년 기사). 1인 지출은 어림값. 출처: https://www.ajunews.com/view/20191031190914712. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
@@ -3578,33 +5186,97 @@
           <t>n_043</t>
         </is>
       </c>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="11" t="n"/>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>국립5·18민주묘지</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>북구 운정동</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 민주로 200</t>
+        </is>
+      </c>
       <c r="F45" s="11" t="n"/>
       <c r="G45" s="11" t="n"/>
-      <c r="H45" s="12" t="n"/>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I45" s="12" t="n"/>
       <c r="J45" s="12" t="n"/>
       <c r="K45" s="12" t="n"/>
-      <c r="L45" s="11" t="n"/>
-      <c r="M45" s="11" t="n"/>
-      <c r="N45" s="11" t="n"/>
+      <c r="L45" s="11" t="inlineStr">
+        <is>
+          <t>입장 마감 17:00</t>
+        </is>
+      </c>
+      <c r="M45" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N45" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O45" s="11" t="n"/>
       <c r="P45" s="11" t="n"/>
       <c r="Q45" s="11" t="n"/>
-      <c r="R45" s="11" t="n"/>
-      <c r="S45" s="11" t="n"/>
-      <c r="T45" s="11" t="n"/>
-      <c r="U45" s="11" t="n"/>
-      <c r="V45" s="11" t="n"/>
-      <c r="W45" s="11" t="n"/>
-      <c r="X45" s="11" t="n"/>
+      <c r="R45" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 전시 관람, 산책</t>
+        </is>
+      </c>
+      <c r="S45" s="11" t="inlineStr">
+        <is>
+          <t>조용한</t>
+        </is>
+      </c>
+      <c r="T45" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U45" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V45" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>5·18묘지, 5.18 민주묘지, 신묘역</t>
+        </is>
+      </c>
+      <c r="X45" s="11" t="inlineStr">
+        <is>
+          <t>5·18민주화운동 희생자가 안장된 국립묘지. 추모관, 옛 망월동 묘역 인근</t>
+        </is>
+      </c>
       <c r="Y45" s="11" t="n"/>
-      <c r="Z45" s="12" t="n"/>
+      <c r="Z45" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA45" s="11" t="n"/>
-      <c r="AB45" s="11" t="n"/>
+      <c r="AB45" s="11" t="inlineStr">
+        <is>
+          <t>입장 마감 17:00. 운영시간은 안내 사이트 기준. 단정한 복장 요청. 출처: https://www.ktriptips.com/kor/tourspot/126425. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
@@ -3612,33 +5284,97 @@
           <t>n_044</t>
         </is>
       </c>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="11" t="n"/>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="11" t="n"/>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>무각사</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>서구 치평동</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 서구 운천로 230</t>
+        </is>
+      </c>
       <c r="F46" s="11" t="n"/>
       <c r="G46" s="11" t="n"/>
-      <c r="H46" s="12" t="n"/>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I46" s="12" t="n"/>
       <c r="J46" s="12" t="n"/>
       <c r="K46" s="12" t="n"/>
-      <c r="L46" s="11" t="n"/>
-      <c r="M46" s="11" t="n"/>
-      <c r="N46" s="11" t="n"/>
+      <c r="L46" s="11" t="inlineStr">
+        <is>
+          <t>로터스갤러리(로터스아트스페이스)는 월요일 휴관, 10:00-18:00</t>
+        </is>
+      </c>
+      <c r="M46" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N46" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O46" s="11" t="n"/>
       <c r="P46" s="11" t="n"/>
       <c r="Q46" s="11" t="n"/>
-      <c r="R46" s="11" t="n"/>
-      <c r="S46" s="11" t="n"/>
-      <c r="T46" s="11" t="n"/>
-      <c r="U46" s="11" t="n"/>
-      <c r="V46" s="11" t="n"/>
-      <c r="W46" s="11" t="n"/>
-      <c r="X46" s="11" t="n"/>
+      <c r="R46" s="11" t="inlineStr">
+        <is>
+          <t>산책, 전시 관람, 건축 구경, 휴식</t>
+        </is>
+      </c>
+      <c r="S46" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 현대적인, 전통적인</t>
+        </is>
+      </c>
+      <c r="T46" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U46" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V46" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>로터스갤러리, 로터스아트스페이스</t>
+        </is>
+      </c>
+      <c r="X46" s="11" t="inlineStr">
+        <is>
+          <t>1971년 상무대 장병을 위해 세운 도심 사찰. 로터스아트스페이스 전시</t>
+        </is>
+      </c>
       <c r="Y46" s="11" t="n"/>
-      <c r="Z46" s="12" t="n"/>
+      <c r="Z46" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA46" s="11" t="n"/>
-      <c r="AB46" s="11" t="n"/>
+      <c r="AB46" s="11" t="inlineStr">
+        <is>
+          <t>경내 상시 개방(안내 사이트). 갤러리는 10:00-18:00, 월요일 휴관. 5·18기념공원·운천저수지와 가까움. 출처: https://sites.google.com/view/mugaksa2026gb/홈. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -3646,33 +5382,93 @@
           <t>n_045</t>
         </is>
       </c>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="11" t="n"/>
-      <c r="D47" s="11" t="n"/>
-      <c r="E47" s="11" t="n"/>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>운천저수지</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>서구 쌍촌동</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 서구 운천로 165 일대</t>
+        </is>
+      </c>
       <c r="F47" s="11" t="n"/>
       <c r="G47" s="11" t="n"/>
-      <c r="H47" s="12" t="n"/>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I47" s="12" t="n"/>
       <c r="J47" s="12" t="n"/>
       <c r="K47" s="12" t="n"/>
       <c r="L47" s="11" t="n"/>
-      <c r="M47" s="11" t="n"/>
-      <c r="N47" s="11" t="n"/>
+      <c r="M47" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N47" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O47" s="11" t="n"/>
       <c r="P47" s="11" t="n"/>
       <c r="Q47" s="11" t="n"/>
-      <c r="R47" s="11" t="n"/>
-      <c r="S47" s="11" t="n"/>
-      <c r="T47" s="11" t="n"/>
-      <c r="U47" s="11" t="n"/>
-      <c r="V47" s="11" t="n"/>
-      <c r="W47" s="11" t="n"/>
-      <c r="X47" s="11" t="n"/>
+      <c r="R47" s="11" t="inlineStr">
+        <is>
+          <t>산책, 휴식, 사진, 야경</t>
+        </is>
+      </c>
+      <c r="S47" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 캐주얼한, 정겨운</t>
+        </is>
+      </c>
+      <c r="T47" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U47" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁, 밤</t>
+        </is>
+      </c>
+      <c r="V47" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W47" s="11" t="inlineStr">
+        <is>
+          <t>운천저수지 수변공원, 운천호수</t>
+        </is>
+      </c>
+      <c r="X47" s="11" t="inlineStr">
+        <is>
+          <t>상무지구 옆 도심 저수지 수변공원. 지하철 공사 뒤 재개방, 봄 벚꽃</t>
+        </is>
+      </c>
       <c r="Y47" s="11" t="n"/>
-      <c r="Z47" s="12" t="n"/>
+      <c r="Z47" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA47" s="11" t="n"/>
-      <c r="AB47" s="11" t="n"/>
+      <c r="AB47" s="11" t="inlineStr">
+        <is>
+          <t>재개방 연도 미확인. 야간 조명 여부 미확인. 출처: https://www.telltrip.com/news/gwangju-uncheon-reservoir-cherry-blossom-reopening/. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -3680,33 +5476,97 @@
           <t>n_046</t>
         </is>
       </c>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="11" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="11" t="n"/>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>남광주시장</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>전통시장</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>동구 학동</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 제봉로17번길 18-6</t>
+        </is>
+      </c>
       <c r="F48" s="11" t="n"/>
       <c r="G48" s="11" t="n"/>
-      <c r="H48" s="12" t="n"/>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>06:00-18:00</t>
+        </is>
+      </c>
       <c r="I48" s="12" t="n"/>
       <c r="J48" s="12" t="n"/>
       <c r="K48" s="12" t="n"/>
-      <c r="L48" s="11" t="n"/>
-      <c r="M48" s="11" t="n"/>
-      <c r="N48" s="11" t="n"/>
+      <c r="L48" s="11" t="inlineStr">
+        <is>
+          <t>매월 첫째·셋째 일요일 휴무</t>
+        </is>
+      </c>
+      <c r="M48" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="N48" s="11" t="n">
+        <v>10000</v>
+      </c>
       <c r="O48" s="11" t="n"/>
       <c r="P48" s="11" t="n"/>
       <c r="Q48" s="11" t="n"/>
-      <c r="R48" s="11" t="n"/>
-      <c r="S48" s="11" t="n"/>
-      <c r="T48" s="11" t="n"/>
-      <c r="U48" s="11" t="n"/>
-      <c r="V48" s="11" t="n"/>
-      <c r="W48" s="11" t="n"/>
-      <c r="X48" s="11" t="n"/>
+      <c r="R48" s="11" t="inlineStr">
+        <is>
+          <t>시장 구경, 식사, 길거리 음식</t>
+        </is>
+      </c>
+      <c r="S48" s="11" t="inlineStr">
+        <is>
+          <t>정겨운, 전통적인, 활기찬</t>
+        </is>
+      </c>
+      <c r="T48" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U48" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V48" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 가족</t>
+        </is>
+      </c>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>남광주역시장</t>
+        </is>
+      </c>
+      <c r="X48" s="11" t="inlineStr">
+        <is>
+          <t>옛 남광주역 앞 시장. 새벽 남해안 수산물로 유명</t>
+        </is>
+      </c>
       <c r="Y48" s="11" t="n"/>
-      <c r="Z48" s="12" t="n"/>
+      <c r="Z48" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA48" s="11" t="n"/>
-      <c r="AB48" s="11" t="n"/>
+      <c r="AB48" s="11" t="inlineStr">
+        <is>
+          <t>영업시간은 임시값. 첫째·셋째 일요일 휴무(생활정보 사이트). 2016~17년 금·토 밤기차 야시장은 지금 운영 여부 미확인. 1인 지출은 어림값. 출처: https://xn--ok0b236bp0a.com/place/26697. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">

--- a/docs/가게조사_챔필주변_초안.xlsx
+++ b/docs/가게조사_챔필주변_초안.xlsx
@@ -5574,33 +5574,97 @@
           <t>n_047</t>
         </is>
       </c>
-      <c r="B49" s="11" t="n"/>
-      <c r="C49" s="11" t="n"/>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="11" t="n"/>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>광주패밀리랜드</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>북구 생용동</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 우치로 677</t>
+        </is>
+      </c>
       <c r="F49" s="11" t="n"/>
       <c r="G49" s="11" t="n"/>
-      <c r="H49" s="12" t="n"/>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>09:30-18:00</t>
+        </is>
+      </c>
       <c r="I49" s="12" t="n"/>
       <c r="J49" s="12" t="n"/>
       <c r="K49" s="12" t="n"/>
-      <c r="L49" s="11" t="n"/>
-      <c r="M49" s="11" t="n"/>
-      <c r="N49" s="11" t="n"/>
+      <c r="L49" s="11" t="inlineStr">
+        <is>
+          <t>기상 상황에 따라 변동</t>
+        </is>
+      </c>
+      <c r="M49" s="11" t="n">
+        <v>180</v>
+      </c>
+      <c r="N49" s="11" t="n">
+        <v>32000</v>
+      </c>
       <c r="O49" s="11" t="n"/>
       <c r="P49" s="11" t="n"/>
       <c r="Q49" s="11" t="n"/>
-      <c r="R49" s="11" t="n"/>
-      <c r="S49" s="11" t="n"/>
-      <c r="T49" s="11" t="n"/>
-      <c r="U49" s="11" t="n"/>
-      <c r="V49" s="11" t="n"/>
-      <c r="W49" s="11" t="n"/>
-      <c r="X49" s="11" t="n"/>
+      <c r="R49" s="11" t="inlineStr">
+        <is>
+          <t>사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S49" s="11" t="inlineStr">
+        <is>
+          <t>활기찬, 레트로한, 캐주얼한</t>
+        </is>
+      </c>
+      <c r="T49" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U49" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V49" s="11" t="inlineStr">
+        <is>
+          <t>가족, 아이 동반, 친구, 연인</t>
+        </is>
+      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>패밀리랜드, 우치공원 패밀리랜드, 벅스랜드</t>
+        </is>
+      </c>
+      <c r="X49" s="11" t="inlineStr">
+        <is>
+          <t>우치공원 안 시 소유 놀이공원. 놀이기구 22개, 안에 벅스랜드(파충류관)</t>
+        </is>
+      </c>
       <c r="Y49" s="11" t="n"/>
-      <c r="Z49" s="12" t="n"/>
+      <c r="Z49" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA49" s="11" t="n"/>
-      <c r="AB49" s="11" t="n"/>
+      <c r="AB49" s="11" t="inlineStr">
+        <is>
+          <t>팀원 확인: 2026년 10월 영업 중(6/30 위탁 계약 종료 뒤 새 운영사 여부는 미확인). 운영시간 09:30-18:00·연중무휴·자유이용권 성인 32,000원은 날짜 불명 안내 사이트 기준, 문의 062-607-8000. 벅스랜드(파충류관, 유료)는 별도 요금. 할 거리 태그에 '놀이기구' 값이 없어 사진·휴식으로 넣음. 출처: https://www.ktriptips.com/kor/tourspot/127539. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">

--- a/docs/가게조사_챔필주변_초안.xlsx
+++ b/docs/가게조사_챔필주변_초안.xlsx
@@ -5672,33 +5672,101 @@
           <t>n_048</t>
         </is>
       </c>
-      <c r="B50" s="11" t="n"/>
-      <c r="C50" s="11" t="n"/>
-      <c r="D50" s="11" t="n"/>
-      <c r="E50" s="11" t="n"/>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>여행자의 집(ZIP)</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>동구 동명동</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 동계천로 137-17</t>
+        </is>
+      </c>
       <c r="F50" s="11" t="n"/>
       <c r="G50" s="11" t="n"/>
-      <c r="H50" s="12" t="n"/>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>10:00-19:00</t>
+        </is>
+      </c>
       <c r="I50" s="12" t="n"/>
       <c r="J50" s="12" t="n"/>
-      <c r="K50" s="12" t="n"/>
-      <c r="L50" s="11" t="n"/>
-      <c r="M50" s="11" t="n"/>
-      <c r="N50" s="11" t="n"/>
+      <c r="K50" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
+          <t>공휴일은 별도 공지</t>
+        </is>
+      </c>
+      <c r="M50" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N50" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O50" s="11" t="n"/>
       <c r="P50" s="11" t="n"/>
       <c r="Q50" s="11" t="n"/>
-      <c r="R50" s="11" t="n"/>
-      <c r="S50" s="11" t="n"/>
-      <c r="T50" s="11" t="n"/>
-      <c r="U50" s="11" t="n"/>
-      <c r="V50" s="11" t="n"/>
-      <c r="W50" s="11" t="n"/>
-      <c r="X50" s="11" t="n"/>
+      <c r="R50" s="11" t="inlineStr">
+        <is>
+          <t>휴식, 쇼핑, 사진, 건축 구경</t>
+        </is>
+      </c>
+      <c r="S50" s="11" t="inlineStr">
+        <is>
+          <t>아늑한, 캐주얼한, 레트로한</t>
+        </is>
+      </c>
+      <c r="T50" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U50" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V50" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>여행자의zip, 여행자의 ZIP, 여행자의집</t>
+        </is>
+      </c>
+      <c r="X50" s="11" t="inlineStr">
+        <is>
+          <t>1980~2007년 전남도 교육감 관사로 쓰인 건물을 동구가 매입·리모델링해 2022년 7월 8일 개관한 관광 플랫폼.</t>
+        </is>
+      </c>
       <c r="Y50" s="11" t="n"/>
-      <c r="Z50" s="12" t="n"/>
+      <c r="Z50" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA50" s="11" t="n"/>
-      <c r="AB50" s="11" t="n"/>
+      <c r="AB50" s="11" t="inlineStr">
+        <is>
+          <t>운영시간 출처끼리 다름: 관광정보 페이지 10:00-19:00, 블로그 소개 11:00-20:00(둘 다 월 휴무). 도로명 주소(동계천로 137-17)는 블로그 소개에만 있어 공식 확인 필요. 문의번호도 070-7733-4680/4679로 다름. 출처: https://view.asiae.co.kr/article/2022071013564709931. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
@@ -5706,33 +5774,93 @@
           <t>n_049</t>
         </is>
       </c>
-      <c r="B51" s="11" t="n"/>
-      <c r="C51" s="11" t="n"/>
-      <c r="D51" s="11" t="n"/>
-      <c r="E51" s="11" t="n"/>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>어반브룩</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>카페·디저트</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>남구 임암동</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 임암길 181</t>
+        </is>
+      </c>
       <c r="F51" s="11" t="n"/>
       <c r="G51" s="11" t="n"/>
-      <c r="H51" s="12" t="n"/>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>10:00-21:00</t>
+        </is>
+      </c>
       <c r="I51" s="12" t="n"/>
       <c r="J51" s="12" t="n"/>
       <c r="K51" s="12" t="n"/>
       <c r="L51" s="11" t="n"/>
-      <c r="M51" s="11" t="n"/>
-      <c r="N51" s="11" t="n"/>
+      <c r="M51" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="N51" s="11" t="n">
+        <v>20000</v>
+      </c>
       <c r="O51" s="11" t="n"/>
       <c r="P51" s="11" t="n"/>
       <c r="Q51" s="11" t="n"/>
-      <c r="R51" s="11" t="n"/>
-      <c r="S51" s="11" t="n"/>
-      <c r="T51" s="11" t="n"/>
-      <c r="U51" s="11" t="n"/>
-      <c r="V51" s="11" t="n"/>
-      <c r="W51" s="11" t="n"/>
-      <c r="X51" s="11" t="n"/>
+      <c r="R51" s="11" t="inlineStr">
+        <is>
+          <t>식사, 카페·디저트, 휴식, 산책, 사진</t>
+        </is>
+      </c>
+      <c r="S51" s="11" t="inlineStr">
+        <is>
+          <t>현대적인, 고급스러운, 조용한</t>
+        </is>
+      </c>
+      <c r="T51" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U51" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V51" s="11" t="inlineStr">
+        <is>
+          <t>친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W51" s="11" t="inlineStr">
+        <is>
+          <t>Urban Brook, 어반브룩 카페</t>
+        </is>
+      </c>
+      <c r="X51" s="11" t="inlineStr">
+        <is>
+          <t>남구 임암동의 복합문화공간 겸 식당·카페.</t>
+        </is>
+      </c>
       <c r="Y51" s="11" t="n"/>
-      <c r="Z51" s="12" t="n"/>
+      <c r="Z51" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA51" s="11" t="n"/>
-      <c r="AB51" s="11" t="n"/>
+      <c r="AB51" s="11" t="inlineStr">
+        <is>
+          <t>입장료는 없고 식음료 공간. 1인 지출은 카페 기준 어림값(식사 35,000원~). 웨딩·행사일 이용 제한 여부 미확인. 운영시간 어반브룩 10:00-21:00, 카페 10:00-21:30, 연중무휴(등록 시점 기준, 2차 자료). 입장료는 없는 것으로 보고 cost 0으로 적었으나 사실상 식음료 이용 공간(어반정식 A 35,000원~킨포크 코스 B 98,000원). 출처: https://www.ktriptips.com/kor/culture/4065105. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
@@ -5740,33 +5868,93 @@
           <t>n_050</t>
         </is>
       </c>
-      <c r="B52" s="11" t="n"/>
-      <c r="C52" s="11" t="n"/>
-      <c r="D52" s="11" t="n"/>
-      <c r="E52" s="11" t="n"/>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>광주벅스랜드</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>북구 생용동</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 우치로 677</t>
+        </is>
+      </c>
       <c r="F52" s="11" t="n"/>
       <c r="G52" s="11" t="n"/>
-      <c r="H52" s="12" t="n"/>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>10:00-18:00</t>
+        </is>
+      </c>
       <c r="I52" s="12" t="n"/>
       <c r="J52" s="12" t="n"/>
       <c r="K52" s="12" t="n"/>
       <c r="L52" s="11" t="n"/>
-      <c r="M52" s="11" t="n"/>
-      <c r="N52" s="11" t="n"/>
+      <c r="M52" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N52" s="11" t="n">
+        <v>8000</v>
+      </c>
       <c r="O52" s="11" t="n"/>
       <c r="P52" s="11" t="n"/>
       <c r="Q52" s="11" t="n"/>
-      <c r="R52" s="11" t="n"/>
-      <c r="S52" s="11" t="n"/>
-      <c r="T52" s="11" t="n"/>
-      <c r="U52" s="11" t="n"/>
-      <c r="V52" s="11" t="n"/>
-      <c r="W52" s="11" t="n"/>
-      <c r="X52" s="11" t="n"/>
+      <c r="R52" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 사진</t>
+        </is>
+      </c>
+      <c r="S52" s="11" t="inlineStr">
+        <is>
+          <t>활기찬, 캐주얼한</t>
+        </is>
+      </c>
+      <c r="T52" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U52" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V52" s="11" t="inlineStr">
+        <is>
+          <t>가족, 아이 동반, 연인</t>
+        </is>
+      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>벅스랜드, 광주 벅스랜드</t>
+        </is>
+      </c>
+      <c r="X52" s="11" t="inlineStr">
+        <is>
+          <t>광주패밀리랜드 안의 곤충관·파충류관·소동물관·포토존으로 된 체험관. 소동물관에서 동물 만지기와 먹이 주기 체험을 한다.</t>
+        </is>
+      </c>
       <c r="Y52" s="11" t="n"/>
-      <c r="Z52" s="12" t="n"/>
+      <c r="Z52" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA52" s="11" t="n"/>
-      <c r="AB52" s="11" t="n"/>
+      <c r="AB52" s="11" t="inlineStr">
+        <is>
+          <t>광주패밀리랜드 안. 네이버 예약 시 패밀리랜드 입장 무료 안내. 요금: 성인(만14~64세) 8,000원, 어린이(25개월~만13세) 13,000원, 경로 4,000원(나무위키; 공식 예약 페이지도 성인 정가 8,000원, 14세부터 성인 요금). 어린이가 성인보다 비싼 구조가 맞는지는 공식 요금표로 재확인 권장. 출처: http://bugsland.co.kr/reservation. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
@@ -5774,33 +5962,97 @@
           <t>n_051</t>
         </is>
       </c>
-      <c r="B53" s="11" t="n"/>
-      <c r="C53" s="11" t="n"/>
-      <c r="D53" s="11" t="n"/>
-      <c r="E53" s="11" t="n"/>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>옛 전남도청</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>동구 광산동</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 문화전당로 38</t>
+        </is>
+      </c>
       <c r="F53" s="11" t="n"/>
       <c r="G53" s="11" t="n"/>
-      <c r="H53" s="12" t="n"/>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>10:00-18:00</t>
+        </is>
+      </c>
       <c r="I53" s="12" t="n"/>
       <c r="J53" s="12" t="n"/>
-      <c r="K53" s="12" t="n"/>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
       <c r="L53" s="11" t="n"/>
-      <c r="M53" s="11" t="n"/>
-      <c r="N53" s="11" t="n"/>
+      <c r="M53" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N53" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O53" s="11" t="n"/>
       <c r="P53" s="11" t="n"/>
       <c r="Q53" s="11" t="n"/>
-      <c r="R53" s="11" t="n"/>
-      <c r="S53" s="11" t="n"/>
-      <c r="T53" s="11" t="n"/>
-      <c r="U53" s="11" t="n"/>
-      <c r="V53" s="11" t="n"/>
-      <c r="W53" s="11" t="n"/>
-      <c r="X53" s="11" t="n"/>
+      <c r="R53" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 전시 관람, 건축 구경</t>
+        </is>
+      </c>
+      <c r="S53" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T53" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U53" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V53" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>옛전남도청, 5·18민주화운동의 현장 옛 전남도청</t>
+        </is>
+      </c>
+      <c r="X53" s="11" t="inlineStr">
+        <is>
+          <t>5·18 최후 항쟁지.</t>
+        </is>
+      </c>
       <c r="Y53" s="11" t="n"/>
-      <c r="Z53" s="12" t="n"/>
+      <c r="Z53" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA53" s="11" t="n"/>
-      <c r="AB53" s="11" t="n"/>
+      <c r="AB53" s="11" t="inlineStr">
+        <is>
+          <t>도로명 주소를 못 찾아 ACC 주소로 대신. 주말 개방 여부가 출처마다 다름. 운영 요일 출처끼리 다름: 헤럴드(2026.4) '화~금 10~18시, 월 휴관', 블로그 '화~일 10:00-18:00'. 주말 개방 여부 공식 확인 필요. 무료는 블로그에만 있음(cost 0은 미확정). 출처: https://www.korea.kr/news/policyNewsView.do?newsId=148964509. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
@@ -5808,33 +6060,101 @@
           <t>n_052</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
-      <c r="C54" s="11" t="n"/>
-      <c r="D54" s="11" t="n"/>
-      <c r="E54" s="11" t="n"/>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>국립광주과학관</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>북구 오룡동</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 첨단과기로 235</t>
+        </is>
+      </c>
       <c r="F54" s="11" t="n"/>
       <c r="G54" s="11" t="n"/>
-      <c r="H54" s="12" t="n"/>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>09:30-17:30</t>
+        </is>
+      </c>
       <c r="I54" s="12" t="n"/>
       <c r="J54" s="12" t="n"/>
-      <c r="K54" s="12" t="n"/>
-      <c r="L54" s="11" t="n"/>
-      <c r="M54" s="11" t="n"/>
-      <c r="N54" s="11" t="n"/>
+      <c r="K54" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="L54" s="11" t="inlineStr">
+        <is>
+          <t>1/1, 설·추석 당일</t>
+        </is>
+      </c>
+      <c r="M54" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="N54" s="11" t="n">
+        <v>3000</v>
+      </c>
       <c r="O54" s="11" t="n"/>
       <c r="P54" s="11" t="n"/>
       <c r="Q54" s="11" t="n"/>
-      <c r="R54" s="11" t="n"/>
-      <c r="S54" s="11" t="n"/>
-      <c r="T54" s="11" t="n"/>
-      <c r="U54" s="11" t="n"/>
-      <c r="V54" s="11" t="n"/>
-      <c r="W54" s="11" t="n"/>
-      <c r="X54" s="11" t="n"/>
+      <c r="R54" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 사진</t>
+        </is>
+      </c>
+      <c r="S54" s="11" t="inlineStr">
+        <is>
+          <t>현대적인, 활기찬</t>
+        </is>
+      </c>
+      <c r="T54" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U54" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V54" s="11" t="inlineStr">
+        <is>
+          <t>가족, 아이 동반, 친구, 연인</t>
+        </is>
+      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>광주과학관</t>
+        </is>
+      </c>
+      <c r="X54" s="11" t="inlineStr">
+        <is>
+          <t>2013년 북구 오룡동 첨단산업단지에 개관한 국립과학관.</t>
+        </is>
+      </c>
       <c r="Y54" s="11" t="n"/>
-      <c r="Z54" s="12" t="n"/>
+      <c r="Z54" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA54" s="11" t="n"/>
-      <c r="AB54" s="11" t="n"/>
+      <c r="AB54" s="11" t="inlineStr">
+        <is>
+          <t>도로명 주소는 출처에서 못 찾아 알려진 주소를 넣음(확인 필요). 관람료는 상설전시관 성인 기준. 새로 생긴 곳은 아니고 최근 인기로 주목받는 곳이라 포함. 운영시간·휴관일은 2차 안내(입장 마감 16:30). 요금 상설전시관 성인 3,000원, 청소년·어린이 2,000원, 유아 무료(블로그 FAQ, 공식 재확인 필요). 출처: https://www.etnews.com/20260921000443. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -5842,33 +6162,101 @@
           <t>n_053</t>
         </is>
       </c>
-      <c r="B55" s="11" t="n"/>
-      <c r="C55" s="11" t="n"/>
-      <c r="D55" s="11" t="n"/>
-      <c r="E55" s="11" t="n"/>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>고려인마을·월곡고려인문화관 결</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>광산구 월곡동</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 광산구 산정공원로50번길 29</t>
+        </is>
+      </c>
       <c r="F55" s="11" t="n"/>
       <c r="G55" s="11" t="n"/>
-      <c r="H55" s="12" t="n"/>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>10:00-17:00</t>
+        </is>
+      </c>
       <c r="I55" s="12" t="n"/>
       <c r="J55" s="12" t="n"/>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="11" t="n"/>
-      <c r="M55" s="11" t="n"/>
-      <c r="N55" s="11" t="n"/>
+      <c r="K55" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="L55" s="11" t="inlineStr">
+        <is>
+          <t>1/1, 설·추석 연휴</t>
+        </is>
+      </c>
+      <c r="M55" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N55" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O55" s="11" t="n"/>
       <c r="P55" s="11" t="n"/>
       <c r="Q55" s="11" t="n"/>
-      <c r="R55" s="11" t="n"/>
-      <c r="S55" s="11" t="n"/>
-      <c r="T55" s="11" t="n"/>
-      <c r="U55" s="11" t="n"/>
-      <c r="V55" s="11" t="n"/>
-      <c r="W55" s="11" t="n"/>
-      <c r="X55" s="11" t="n"/>
+      <c r="R55" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 전시 관람, 산책, 식사</t>
+        </is>
+      </c>
+      <c r="S55" s="11" t="inlineStr">
+        <is>
+          <t>이국적인, 정겨운</t>
+        </is>
+      </c>
+      <c r="T55" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U55" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V55" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>광주 고려인마을, 고려인마을 골목, 월곡고려인문화관, 고려인문화관 결</t>
+        </is>
+      </c>
+      <c r="X55" s="11" t="inlineStr">
+        <is>
+          <t>월곡고려인문화관은 2021년 5월 개관했고 고려인 유물 1만 2,000여 점을 소장한다.</t>
+        </is>
+      </c>
       <c r="Y55" s="11" t="n"/>
-      <c r="Z55" s="12" t="n"/>
+      <c r="Z55" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA55" s="11" t="n"/>
-      <c r="AB55" s="11" t="n"/>
+      <c r="AB55" s="11" t="inlineStr">
+        <is>
+          <t>관람시간·휴관일·무료는 2022년 등록 관광정보 기준(문의 062-955-1925). 마을투어(고려인마을주민관광청 해설)는 예약제일 수 있음. 챔피언스필드에서 먼 광산구. 출처: https://newsseoul.co.kr/news/view/1065601236374192. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -5876,33 +6264,97 @@
           <t>n_054</t>
         </is>
       </c>
-      <c r="B56" s="11" t="n"/>
-      <c r="C56" s="11" t="n"/>
-      <c r="D56" s="11" t="n"/>
-      <c r="E56" s="11" t="n"/>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>광주미디어아트플랫폼 G.MAP</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>남구 사동</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 천변좌로338번길 10</t>
+        </is>
+      </c>
       <c r="F56" s="11" t="n"/>
       <c r="G56" s="11" t="n"/>
-      <c r="H56" s="12" t="n"/>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>10:00-18:00</t>
+        </is>
+      </c>
       <c r="I56" s="12" t="n"/>
       <c r="J56" s="12" t="n"/>
-      <c r="K56" s="12" t="n"/>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
       <c r="L56" s="11" t="n"/>
-      <c r="M56" s="11" t="n"/>
-      <c r="N56" s="11" t="n"/>
+      <c r="M56" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N56" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O56" s="11" t="n"/>
       <c r="P56" s="11" t="n"/>
       <c r="Q56" s="11" t="n"/>
-      <c r="R56" s="11" t="n"/>
-      <c r="S56" s="11" t="n"/>
-      <c r="T56" s="11" t="n"/>
-      <c r="U56" s="11" t="n"/>
-      <c r="V56" s="11" t="n"/>
-      <c r="W56" s="11" t="n"/>
-      <c r="X56" s="11" t="n"/>
+      <c r="R56" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 야경, 사진</t>
+        </is>
+      </c>
+      <c r="S56" s="11" t="inlineStr">
+        <is>
+          <t>현대적인, 조용한</t>
+        </is>
+      </c>
+      <c r="T56" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U56" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V56" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>G.MAP, GMAP, 지맵, 광주광역시미디어아트플랫폼</t>
+        </is>
+      </c>
+      <c r="X56" s="11" t="inlineStr">
+        <is>
+          <t>광주천변 빛고을시민문화관 건물에 있는 광주시 미디어아트 전시 공간. 건물 옥상에 홀로그램 파사드가 설치돼 있다.</t>
+        </is>
+      </c>
       <c r="Y56" s="11" t="n"/>
-      <c r="Z56" s="12" t="n"/>
+      <c r="Z56" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA56" s="11" t="n"/>
-      <c r="AB56" s="11" t="n"/>
+      <c r="AB56" s="11" t="inlineStr">
+        <is>
+          <t>빛고을시민문화관과 같은 건물(공연장인 문화관은 뺐지만 G.MAP 전시는 상설). EXISTING '(조사했지만 뺀 곳) 빛고을시민문화관'과 같은 건물 — 그 건물을 뺀 이유가 G.MAP에도 해당하는지 팀 확인 필요. 개관 연도 미확인. 월 휴관은 영문 가이드의 '화~일 운영'에서 추정. 유료 특별전 있을 수 있음. 출처: https://www.ktriptips.com/kor/culture/3029365. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
@@ -5910,33 +6362,93 @@
           <t>n_055</t>
         </is>
       </c>
-      <c r="B57" s="11" t="n"/>
-      <c r="C57" s="11" t="n"/>
-      <c r="D57" s="11" t="n"/>
-      <c r="E57" s="11" t="n"/>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>시리단길</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>상점가</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>광산구 쌍암동</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 광산구 쌍암동</t>
+        </is>
+      </c>
       <c r="F57" s="11" t="n"/>
       <c r="G57" s="11" t="n"/>
-      <c r="H57" s="12" t="n"/>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I57" s="12" t="n"/>
       <c r="J57" s="12" t="n"/>
       <c r="K57" s="12" t="n"/>
       <c r="L57" s="11" t="n"/>
-      <c r="M57" s="11" t="n"/>
-      <c r="N57" s="11" t="n"/>
+      <c r="M57" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N57" s="11" t="n">
+        <v>15000</v>
+      </c>
       <c r="O57" s="11" t="n"/>
       <c r="P57" s="11" t="n"/>
       <c r="Q57" s="11" t="n"/>
-      <c r="R57" s="11" t="n"/>
-      <c r="S57" s="11" t="n"/>
-      <c r="T57" s="11" t="n"/>
-      <c r="U57" s="11" t="n"/>
-      <c r="V57" s="11" t="n"/>
-      <c r="W57" s="11" t="n"/>
-      <c r="X57" s="11" t="n"/>
+      <c r="R57" s="11" t="inlineStr">
+        <is>
+          <t>카페·디저트, 식사, 술, 산책</t>
+        </is>
+      </c>
+      <c r="S57" s="11" t="inlineStr">
+        <is>
+          <t>현대적인, 활기찬</t>
+        </is>
+      </c>
+      <c r="T57" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U57" s="11" t="inlineStr">
+        <is>
+          <t>오후, 저녁, 밤</t>
+        </is>
+      </c>
+      <c r="V57" s="11" t="inlineStr">
+        <is>
+          <t>친구, 연인</t>
+        </is>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>첨단 시리단길</t>
+        </is>
+      </c>
+      <c r="X57" s="11" t="inlineStr">
+        <is>
+          <t>광산구 첨단지구 쌍암동 상권의 별칭.</t>
+        </is>
+      </c>
       <c r="Y57" s="11" t="n"/>
-      <c r="Z57" s="12" t="n"/>
+      <c r="Z57" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA57" s="11" t="n"/>
-      <c r="AB57" s="11" t="n"/>
+      <c r="AB57" s="11" t="inlineStr">
+        <is>
+          <t>주소는 동 이름만(지도에서 좌표 수정 필요). 관광객보다 지역 젊은 층 상권. 1인 지출은 어림값. 2024년 아시아경제 기사는 동리단길 유동인구 감소 원인으로 시리단길 같은 경쟁 상권 등장을 꼽음. 2025~2026년 현황 기사 없음. 거리 중심 도로명 미확인. 관광객 대상이라기보다 지역 젊은층 상권 — 포함 여부 팀 판단. 출처: https://view.asiae.co.kr/article/2024082210201616316. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -5944,33 +6456,97 @@
           <t>n_056</t>
         </is>
       </c>
-      <c r="B58" s="11" t="n"/>
-      <c r="C58" s="11" t="n"/>
-      <c r="D58" s="11" t="n"/>
-      <c r="E58" s="11" t="n"/>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>양림인디</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>야간 콘텐츠</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>남구 양림동</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 제중로47번길 20</t>
+        </is>
+      </c>
       <c r="F58" s="11" t="n"/>
       <c r="G58" s="11" t="n"/>
-      <c r="H58" s="12" t="n"/>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>18:00-19:20</t>
+        </is>
+      </c>
       <c r="I58" s="12" t="n"/>
       <c r="J58" s="12" t="n"/>
-      <c r="K58" s="12" t="n"/>
+      <c r="K58" s="12" t="inlineStr">
+        <is>
+          <t>월, 화, 수, 목, 금, 일</t>
+        </is>
+      </c>
       <c r="L58" s="11" t="n"/>
-      <c r="M58" s="11" t="n"/>
-      <c r="N58" s="11" t="n"/>
+      <c r="M58" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="N58" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O58" s="11" t="n"/>
       <c r="P58" s="11" t="n"/>
       <c r="Q58" s="11" t="n"/>
-      <c r="R58" s="11" t="n"/>
-      <c r="S58" s="11" t="n"/>
-      <c r="T58" s="11" t="n"/>
-      <c r="U58" s="11" t="n"/>
-      <c r="V58" s="11" t="n"/>
-      <c r="W58" s="11" t="n"/>
-      <c r="X58" s="11" t="n"/>
+      <c r="R58" s="11" t="inlineStr">
+        <is>
+          <t>공연·영화</t>
+        </is>
+      </c>
+      <c r="S58" s="11" t="inlineStr">
+        <is>
+          <t>아늑한, 캐주얼한</t>
+        </is>
+      </c>
+      <c r="T58" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U58" s="11" t="inlineStr">
+        <is>
+          <t>저녁</t>
+        </is>
+      </c>
+      <c r="V58" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인</t>
+        </is>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>양림 인디 라이브</t>
+        </is>
+      </c>
+      <c r="X58" s="11" t="inlineStr">
+        <is>
+          <t>광주시 양림권역 활성화 마을투어 사업의 하나로, 인디 뮤지션이 양림동 여러 장소에서 여는 소규모 라이브(회당 약 50명).</t>
+        </is>
+      </c>
       <c r="Y58" s="11" t="n"/>
-      <c r="Z58" s="12" t="n"/>
+      <c r="Z58" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA58" s="11" t="n"/>
-      <c r="AB58" s="11" t="n"/>
+      <c r="AB58" s="11" t="inlineStr">
+        <is>
+          <t>기간 한정: 2026.4~12월 매월 마지막 주 토요일만(남은 회차 11/28, 12/26 추정). 매회 장소가 바뀌어 주소는 첫 공연장(호랑가시나무 아트폴리곤). 참가비 미확인(0 으로 넣음), 사전 신청제로 보임. 매회 장소가 바뀜(일정은 '양림인디' 인스타그램). 참가비·예약 방식 확인 못 함(첫 회 50석 매진 → 사전 신청제로 보임). 2026년 남은 회차는 10/31, 11/28, 12/26(마지막 주 토요일 계산값, 공식 확인 필요). 출처: https://www.newsis.com/view/NISX20260423_0003603118. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -5978,33 +6554,97 @@
           <t>n_057</t>
         </is>
       </c>
-      <c r="B59" s="11" t="n"/>
-      <c r="C59" s="11" t="n"/>
-      <c r="D59" s="11" t="n"/>
-      <c r="E59" s="11" t="n"/>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>양림 파빌리온 전시투어</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>남구 양림동</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 제중로47번길 20</t>
+        </is>
+      </c>
       <c r="F59" s="11" t="n"/>
       <c r="G59" s="11" t="n"/>
-      <c r="H59" s="12" t="n"/>
+      <c r="H59" s="12" t="inlineStr">
+        <is>
+          <t>14:00-17:30</t>
+        </is>
+      </c>
       <c r="I59" s="12" t="n"/>
       <c r="J59" s="12" t="n"/>
-      <c r="K59" s="12" t="n"/>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>월, 화, 수, 목, 일</t>
+        </is>
+      </c>
       <c r="L59" s="11" t="n"/>
-      <c r="M59" s="11" t="n"/>
-      <c r="N59" s="11" t="n"/>
+      <c r="M59" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="N59" s="11" t="n">
+        <v>10000</v>
+      </c>
       <c r="O59" s="11" t="n"/>
       <c r="P59" s="11" t="n"/>
       <c r="Q59" s="11" t="n"/>
-      <c r="R59" s="11" t="n"/>
-      <c r="S59" s="11" t="n"/>
-      <c r="T59" s="11" t="n"/>
-      <c r="U59" s="11" t="n"/>
-      <c r="V59" s="11" t="n"/>
-      <c r="W59" s="11" t="n"/>
-      <c r="X59" s="11" t="n"/>
+      <c r="R59" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 역사 탐방, 산책</t>
+        </is>
+      </c>
+      <c r="S59" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T59" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U59" s="11" t="inlineStr">
+        <is>
+          <t>오후</t>
+        </is>
+      </c>
+      <c r="V59" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W59" s="11" t="inlineStr">
+        <is>
+          <t>양림 마을투어 전시투어, 광주비엔날레 양림동 파빌리온 투어</t>
+        </is>
+      </c>
+      <c r="X59" s="11" t="inlineStr">
+        <is>
+          <t>제16회 광주비엔날레 연계 해설 투어로, 이장우 가옥·이강하미술관·우일선 선교사 사택·이이남 스튜디오 등 양림동 파빌리온을 돈다.</t>
+        </is>
+      </c>
       <c r="Y59" s="11" t="n"/>
-      <c r="Z59" s="12" t="n"/>
+      <c r="Z59" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA59" s="11" t="n"/>
-      <c r="AB59" s="11" t="n"/>
+      <c r="AB59" s="11" t="inlineStr">
+        <is>
+          <t>기간 한정: 2026.9.18~11.14 금·토 14:00·16:00 출발. 출발 장소 미확인이라 주소는 양림동 안 아트폴리곤으로 대신. 광주관광공사 예약. 회당 소요시간 미확인(90분은 추정). 셔틀버스 운행 언급 있음(MTN). 들르는 곳 중 이장우 가옥은 EXISTING에 있음. 예약 광주관광공사. 출처: https://www.tournews21.com/news/articleView.html?idxno=143164. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -6012,33 +6652,93 @@
           <t>n_058</t>
         </is>
       </c>
-      <c r="B60" s="11" t="n"/>
-      <c r="C60" s="11" t="n"/>
-      <c r="D60" s="11" t="n"/>
-      <c r="E60" s="11" t="n"/>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>장록습지 (장록국가습지)</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>광산구 장록동·서봉동·선암동</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 광산구 장록동</t>
+        </is>
+      </c>
       <c r="F60" s="11" t="n"/>
       <c r="G60" s="11" t="n"/>
-      <c r="H60" s="12" t="n"/>
+      <c r="H60" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I60" s="12" t="n"/>
       <c r="J60" s="12" t="n"/>
       <c r="K60" s="12" t="n"/>
       <c r="L60" s="11" t="n"/>
-      <c r="M60" s="11" t="n"/>
-      <c r="N60" s="11" t="n"/>
+      <c r="M60" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N60" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O60" s="11" t="n"/>
       <c r="P60" s="11" t="n"/>
       <c r="Q60" s="11" t="n"/>
-      <c r="R60" s="11" t="n"/>
-      <c r="S60" s="11" t="n"/>
-      <c r="T60" s="11" t="n"/>
-      <c r="U60" s="11" t="n"/>
-      <c r="V60" s="11" t="n"/>
-      <c r="W60" s="11" t="n"/>
-      <c r="X60" s="11" t="n"/>
+      <c r="R60" s="11" t="inlineStr">
+        <is>
+          <t>산책, 사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S60" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 캐주얼한</t>
+        </is>
+      </c>
+      <c r="T60" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U60" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V60" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W60" s="11" t="inlineStr">
+        <is>
+          <t>황룡강 장록습지, 장록국가습지보호지역</t>
+        </is>
+      </c>
+      <c r="X60" s="11" t="inlineStr">
+        <is>
+          <t>광산구 황룡강의 도심 하천습지로, 2020년 12월 도심 하천습지로는 국내 처음 국가습지로 지정됐다(지정 면적 2.70㎢).</t>
+        </is>
+      </c>
       <c r="Y60" s="11" t="n"/>
-      <c r="Z60" s="12" t="n"/>
+      <c r="Z60" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA60" s="11" t="n"/>
-      <c r="AB60" s="11" t="n"/>
+      <c r="AB60" s="11" t="inlineStr">
+        <is>
+          <t>주소는 동 이름만(지도에서 좌표 수정 필요). 탐방로·데크 위치, 진입 주소, 탐방안내소 운영 여부는 확인 못 함(hours 는 하천 습지라 상시 개방으로 둔 추정). 2026년 8월 반도체 산단과 습지 사이 완충녹지 조성 계획 보도. 출처: https://news.tf.co.kr/read/ogmeta/1829766.htm. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
@@ -6046,33 +6746,93 @@
           <t>n_059</t>
         </is>
       </c>
-      <c r="B61" s="11" t="n"/>
-      <c r="C61" s="11" t="n"/>
-      <c r="D61" s="11" t="n"/>
-      <c r="E61" s="11" t="n"/>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>쌍암공원</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>광산구 쌍암동</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 광산구 쌍암동</t>
+        </is>
+      </c>
       <c r="F61" s="11" t="n"/>
       <c r="G61" s="11" t="n"/>
-      <c r="H61" s="12" t="n"/>
+      <c r="H61" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I61" s="12" t="n"/>
       <c r="J61" s="12" t="n"/>
       <c r="K61" s="12" t="n"/>
       <c r="L61" s="11" t="n"/>
-      <c r="M61" s="11" t="n"/>
-      <c r="N61" s="11" t="n"/>
+      <c r="M61" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N61" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O61" s="11" t="n"/>
       <c r="P61" s="11" t="n"/>
       <c r="Q61" s="11" t="n"/>
-      <c r="R61" s="11" t="n"/>
-      <c r="S61" s="11" t="n"/>
-      <c r="T61" s="11" t="n"/>
-      <c r="U61" s="11" t="n"/>
-      <c r="V61" s="11" t="n"/>
-      <c r="W61" s="11" t="n"/>
-      <c r="X61" s="11" t="n"/>
+      <c r="R61" s="11" t="inlineStr">
+        <is>
+          <t>산책, 휴식, 사진</t>
+        </is>
+      </c>
+      <c r="S61" s="11" t="inlineStr">
+        <is>
+          <t>캐주얼한, 조용한</t>
+        </is>
+      </c>
+      <c r="T61" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U61" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁, 밤</t>
+        </is>
+      </c>
+      <c r="V61" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>첨단 호수공원, 첨단 쌍암호수공원</t>
+        </is>
+      </c>
+      <c r="X61" s="11" t="inlineStr">
+        <is>
+          <t>첨단지구 광주과학기술원 앞에 있는 호수공원으로, 호수 둘레에 철쭉 숲과 소나무숲, 잔디광장, 팔각정이 있다.</t>
+        </is>
+      </c>
       <c r="Y61" s="11" t="n"/>
-      <c r="Z61" s="12" t="n"/>
+      <c r="Z61" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA61" s="11" t="n"/>
-      <c r="AB61" s="11" t="n"/>
+      <c r="AB61" s="11" t="inlineStr">
+        <is>
+          <t>주소는 동 이름만(지도에서 좌표 수정 필요). 도로명 주소 확인 못 함. 출처는 관광공사 데이터를 옮긴 제3자 사이트. 출처: https://www.ktriptips.com/kor/tourspot/250453. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
@@ -6080,33 +6840,93 @@
           <t>n_060</t>
         </is>
       </c>
-      <c r="B62" s="11" t="n"/>
-      <c r="C62" s="11" t="n"/>
-      <c r="D62" s="11" t="n"/>
-      <c r="E62" s="11" t="n"/>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>월봉서원</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 광산구 광곡길 133</t>
+        </is>
+      </c>
       <c r="F62" s="11" t="n"/>
       <c r="G62" s="11" t="n"/>
-      <c r="H62" s="12" t="n"/>
+      <c r="H62" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I62" s="12" t="n"/>
       <c r="J62" s="12" t="n"/>
       <c r="K62" s="12" t="n"/>
       <c r="L62" s="11" t="n"/>
-      <c r="M62" s="11" t="n"/>
-      <c r="N62" s="11" t="n"/>
+      <c r="M62" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N62" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O62" s="11" t="n"/>
       <c r="P62" s="11" t="n"/>
       <c r="Q62" s="11" t="n"/>
-      <c r="R62" s="11" t="n"/>
-      <c r="S62" s="11" t="n"/>
-      <c r="T62" s="11" t="n"/>
-      <c r="U62" s="11" t="n"/>
-      <c r="V62" s="11" t="n"/>
-      <c r="W62" s="11" t="n"/>
-      <c r="X62" s="11" t="n"/>
+      <c r="R62" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 건축 구경, 산책</t>
+        </is>
+      </c>
+      <c r="S62" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T62" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U62" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V62" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>광곡마을 월봉서원</t>
+        </is>
+      </c>
+      <c r="X62" s="11" t="inlineStr">
+        <is>
+          <t>1578년 고봉 기대승을 기리려 세운 서원으로 1646년 현 위치로 옮기고 1654년 '월봉' 사액을 받았으며, 1868년 서원 철폐 때 훼철됐다.</t>
+        </is>
+      </c>
       <c r="Y62" s="11" t="n"/>
-      <c r="Z62" s="12" t="n"/>
+      <c r="Z62" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA62" s="11" t="n"/>
-      <c r="AB62" s="11" t="n"/>
+      <c r="AB62" s="11" t="inlineStr">
+        <is>
+          <t>법정동 확인 못 함. 국가유산 활용사업 '달의 정원, 월봉서원'이 대표 브랜드 사업 10선으로 2027년까지 인문교육·공연 등 운영(기간 한정 프로그램, 일정 미확인). 문의 광산구청 관광육성과 062-960-8255. 출처: https://www.ktriptips.com/kor/tourspot/250450. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -6114,33 +6934,93 @@
           <t>n_061</t>
         </is>
       </c>
-      <c r="B63" s="11" t="n"/>
-      <c r="C63" s="11" t="n"/>
-      <c r="D63" s="11" t="n"/>
-      <c r="E63" s="11" t="n"/>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>신창동 마한유적체험관</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>광산구 신창동</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 광산구 북문대로 396-2</t>
+        </is>
+      </c>
       <c r="F63" s="11" t="n"/>
       <c r="G63" s="11" t="n"/>
-      <c r="H63" s="12" t="n"/>
+      <c r="H63" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I63" s="12" t="n"/>
       <c r="J63" s="12" t="n"/>
       <c r="K63" s="12" t="n"/>
       <c r="L63" s="11" t="n"/>
-      <c r="M63" s="11" t="n"/>
-      <c r="N63" s="11" t="n"/>
+      <c r="M63" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N63" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O63" s="11" t="n"/>
       <c r="P63" s="11" t="n"/>
       <c r="Q63" s="11" t="n"/>
-      <c r="R63" s="11" t="n"/>
-      <c r="S63" s="11" t="n"/>
-      <c r="T63" s="11" t="n"/>
-      <c r="U63" s="11" t="n"/>
-      <c r="V63" s="11" t="n"/>
-      <c r="W63" s="11" t="n"/>
-      <c r="X63" s="11" t="n"/>
+      <c r="R63" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 전시 관람, 공방 체험</t>
+        </is>
+      </c>
+      <c r="S63" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T63" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U63" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V63" s="11" t="inlineStr">
+        <is>
+          <t>가족, 아이 동반, 혼자</t>
+        </is>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>광주 신창동 유적, 신창동 유적지</t>
+        </is>
+      </c>
+      <c r="X63" s="11" t="inlineStr">
+        <is>
+          <t>기원전 1세기경 초기철기시대 복합농경유적인 국가사적 '광주 신창동 유적' 옆에 2022년 12월 개관한 체험관이다.</t>
+        </is>
+      </c>
       <c r="Y63" s="11" t="n"/>
-      <c r="Z63" s="12" t="n"/>
+      <c r="Z63" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA63" s="11" t="n"/>
-      <c r="AB63" s="11" t="n"/>
+      <c r="AB63" s="11" t="inlineStr">
+        <is>
+          <t>운영시간은 임시값. 운영 시간·휴관일 미확인(광주역사민속박물관 소관이므로 월요일 휴관일 가능성 있으나 확인 못 함). 유적지 마한 옛 수로 재현 사업은 설계 단계였고 완공 여부 미확인. 출처: https://www.ktriptips.com/kor/tourspot/3060959. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -6148,33 +7028,93 @@
           <t>n_062</t>
         </is>
       </c>
-      <c r="B64" s="11" t="n"/>
-      <c r="C64" s="11" t="n"/>
-      <c r="D64" s="11" t="n"/>
-      <c r="E64" s="11" t="n"/>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>용아 박용철 생가</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>광산구 소촌동</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 광산구 소촌로46번길 24</t>
+        </is>
+      </c>
       <c r="F64" s="11" t="n"/>
       <c r="G64" s="11" t="n"/>
-      <c r="H64" s="12" t="n"/>
+      <c r="H64" s="12" t="inlineStr">
+        <is>
+          <t>10:00-17:00</t>
+        </is>
+      </c>
       <c r="I64" s="12" t="n"/>
       <c r="J64" s="12" t="n"/>
       <c r="K64" s="12" t="n"/>
       <c r="L64" s="11" t="n"/>
-      <c r="M64" s="11" t="n"/>
-      <c r="N64" s="11" t="n"/>
+      <c r="M64" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N64" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O64" s="11" t="n"/>
       <c r="P64" s="11" t="n"/>
       <c r="Q64" s="11" t="n"/>
-      <c r="R64" s="11" t="n"/>
-      <c r="S64" s="11" t="n"/>
-      <c r="T64" s="11" t="n"/>
-      <c r="U64" s="11" t="n"/>
-      <c r="V64" s="11" t="n"/>
-      <c r="W64" s="11" t="n"/>
-      <c r="X64" s="11" t="n"/>
+      <c r="R64" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 건축 구경</t>
+        </is>
+      </c>
+      <c r="S64" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인, 아늑한</t>
+        </is>
+      </c>
+      <c r="T64" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U64" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V64" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>용아생가, 박용철 생가</t>
+        </is>
+      </c>
+      <c r="X64" s="11" t="inlineStr">
+        <is>
+          <t>시문학파 시인 용아 박용철의 생가로 광주시기념물 제13호다. 안채·사랑채·행랑채·사당·서재가 남아 있다. 무료.</t>
+        </is>
+      </c>
       <c r="Y64" s="11" t="n"/>
-      <c r="Z64" s="12" t="n"/>
+      <c r="Z64" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA64" s="11" t="n"/>
-      <c r="AB64" s="11" t="n"/>
+      <c r="AB64" s="11" t="inlineStr">
+        <is>
+          <t>안내상 연중무휴·주차 불가. 개인 소유로 친척이 관리해 실제 개방 시간이 달라질 수 있음. 문의 062-944-1340. 광주송정역에서 가까운 편(거리 미확인). 출처: https://www.ktriptips.com/kor/tourspot/129198. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -6182,33 +7122,93 @@
           <t>n_063</t>
         </is>
       </c>
-      <c r="B65" s="11" t="n"/>
-      <c r="C65" s="11" t="n"/>
-      <c r="D65" s="11" t="n"/>
-      <c r="E65" s="11" t="n"/>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>송산유원지</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>광산구 송산동</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 광산구 송산동</t>
+        </is>
+      </c>
       <c r="F65" s="11" t="n"/>
       <c r="G65" s="11" t="n"/>
-      <c r="H65" s="12" t="n"/>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I65" s="12" t="n"/>
       <c r="J65" s="12" t="n"/>
       <c r="K65" s="12" t="n"/>
       <c r="L65" s="11" t="n"/>
-      <c r="M65" s="11" t="n"/>
-      <c r="N65" s="11" t="n"/>
+      <c r="M65" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="N65" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O65" s="11" t="n"/>
       <c r="P65" s="11" t="n"/>
       <c r="Q65" s="11" t="n"/>
-      <c r="R65" s="11" t="n"/>
-      <c r="S65" s="11" t="n"/>
-      <c r="T65" s="11" t="n"/>
-      <c r="U65" s="11" t="n"/>
-      <c r="V65" s="11" t="n"/>
-      <c r="W65" s="11" t="n"/>
-      <c r="X65" s="11" t="n"/>
+      <c r="R65" s="11" t="inlineStr">
+        <is>
+          <t>산책, 휴식, 사진</t>
+        </is>
+      </c>
+      <c r="S65" s="11" t="inlineStr">
+        <is>
+          <t>캐주얼한, 조용한</t>
+        </is>
+      </c>
+      <c r="T65" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U65" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V65" s="11" t="inlineStr">
+        <is>
+          <t>친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W65" s="11" t="inlineStr">
+        <is>
+          <t>송산공원</t>
+        </is>
+      </c>
+      <c r="X65" s="11" t="inlineStr">
+        <is>
+          <t>황룡강의 섬을 유원지로 꾸민 공원으로 2000년 5월 21일 개장했다. 상시 개방·연중무휴.</t>
+        </is>
+      </c>
       <c r="Y65" s="11" t="n"/>
-      <c r="Z65" s="12" t="n"/>
+      <c r="Z65" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA65" s="11" t="n"/>
-      <c r="AB65" s="11" t="n"/>
+      <c r="AB65" s="11" t="inlineStr">
+        <is>
+          <t>주소는 동 이름만(지도에서 좌표 수정 필요). 출처 1곳(관광공사 데이터 옮긴 사이트), 2025~2026년 현황 미확인. 무료 여부는 상시 개방 공원이라 0으로 둔 것(명시적 출처 없음). 도로명 주소 미확인. 황룡강생태길30 시작점 '송산근린공원'과 같은 곳인지 미확인. 출처: https://www.ktriptips.com/kor/tourspot/129202. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -6216,33 +7216,89 @@
           <t>n_064</t>
         </is>
       </c>
-      <c r="B66" s="11" t="n"/>
-      <c r="C66" s="11" t="n"/>
-      <c r="D66" s="11" t="n"/>
-      <c r="E66" s="11" t="n"/>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>호가정</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>광산구 본덕동</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 광산구 동곡분토길 195</t>
+        </is>
+      </c>
       <c r="F66" s="11" t="n"/>
       <c r="G66" s="11" t="n"/>
-      <c r="H66" s="12" t="n"/>
+      <c r="H66" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I66" s="12" t="n"/>
       <c r="J66" s="12" t="n"/>
       <c r="K66" s="12" t="n"/>
       <c r="L66" s="11" t="n"/>
-      <c r="M66" s="11" t="n"/>
-      <c r="N66" s="11" t="n"/>
+      <c r="M66" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N66" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O66" s="11" t="n"/>
       <c r="P66" s="11" t="n"/>
       <c r="Q66" s="11" t="n"/>
-      <c r="R66" s="11" t="n"/>
-      <c r="S66" s="11" t="n"/>
-      <c r="T66" s="11" t="n"/>
-      <c r="U66" s="11" t="n"/>
-      <c r="V66" s="11" t="n"/>
+      <c r="R66" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 건축 구경, 사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S66" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T66" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U66" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V66" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인</t>
+        </is>
+      </c>
       <c r="W66" s="11" t="n"/>
-      <c r="X66" s="11" t="n"/>
+      <c r="X66" s="11" t="inlineStr">
+        <is>
+          <t>조선 중·명종 때 문신 설강 유사(1502~1571)가 만년에 지은 정자로 광주문화재자료 제14호다.</t>
+        </is>
+      </c>
       <c r="Y66" s="11" t="n"/>
-      <c r="Z66" s="12" t="n"/>
+      <c r="Z66" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA66" s="11" t="n"/>
-      <c r="AB66" s="11" t="n"/>
+      <c r="AB66" s="11" t="inlineStr">
+        <is>
+          <t>개방 시간·요금 명시 출처 없음(야외 정자라 상시·무료로 둔 추정). 대중교통 접근성 낮을 수 있음(미확인). 문의 광산구 문화체육과 062-960-8252. 출처: https://www.ktriptips.com/kor/tourspot/250448. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -6250,33 +7306,101 @@
           <t>n_065</t>
         </is>
       </c>
-      <c r="B67" s="11" t="n"/>
-      <c r="C67" s="11" t="n"/>
-      <c r="D67" s="11" t="n"/>
-      <c r="E67" s="11" t="n"/>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>시화문화마을·금봉미술관</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>북구 각화동</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 북구 각화대로 91</t>
+        </is>
+      </c>
       <c r="F67" s="11" t="n"/>
       <c r="G67" s="11" t="n"/>
-      <c r="H67" s="12" t="n"/>
+      <c r="H67" s="12" t="inlineStr">
+        <is>
+          <t>10:00-18:00</t>
+        </is>
+      </c>
       <c r="I67" s="12" t="n"/>
       <c r="J67" s="12" t="n"/>
-      <c r="K67" s="12" t="n"/>
-      <c r="L67" s="11" t="n"/>
-      <c r="M67" s="11" t="n"/>
-      <c r="N67" s="11" t="n"/>
+      <c r="K67" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="L67" s="11" t="inlineStr">
+        <is>
+          <t>1/1, 설·추석 당일</t>
+        </is>
+      </c>
+      <c r="M67" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="N67" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O67" s="11" t="n"/>
       <c r="P67" s="11" t="n"/>
       <c r="Q67" s="11" t="n"/>
-      <c r="R67" s="11" t="n"/>
-      <c r="S67" s="11" t="n"/>
-      <c r="T67" s="11" t="n"/>
-      <c r="U67" s="11" t="n"/>
-      <c r="V67" s="11" t="n"/>
-      <c r="W67" s="11" t="n"/>
-      <c r="X67" s="11" t="n"/>
+      <c r="R67" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 산책, 사진</t>
+        </is>
+      </c>
+      <c r="S67" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 정겨운, 전통적인</t>
+        </is>
+      </c>
+      <c r="T67" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U67" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V67" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W67" s="11" t="inlineStr">
+        <is>
+          <t>각화동 시화마을, 금봉미술관, 詩畵마을</t>
+        </is>
+      </c>
+      <c r="X67" s="11" t="inlineStr">
+        <is>
+          <t>2002년 지역 시인이 시작한 시화(詩畵) 골목 마을로, 2010년부터 시화환경미술제를 열었다.</t>
+        </is>
+      </c>
       <c r="Y67" s="11" t="n"/>
-      <c r="Z67" s="12" t="n"/>
+      <c r="Z67" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA67" s="11" t="n"/>
-      <c r="AB67" s="11" t="n"/>
+      <c r="AB67" s="11" t="inlineStr">
+        <is>
+          <t>광주문학관(n_034)과 같은 마을. 미술관 주소가 출처마다 각화대로 91 / 93 으로 다름. 시간·휴관은 금봉미술관 기준, 마을 골목은 상시. 2025~2026년 마을 소식은 찾지 못함. 미술관 전화 062-269-9883, gbartmuseum.or.kr. 출처: https://www.ktriptips.com/kor/culture/3441618. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -6284,33 +7408,93 @@
           <t>n_066</t>
         </is>
       </c>
-      <c r="B68" s="11" t="n"/>
-      <c r="C68" s="11" t="n"/>
-      <c r="D68" s="11" t="n"/>
-      <c r="E68" s="11" t="n"/>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>청춘발산마을</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>서구 양동</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 서구 천변좌로 12-16</t>
+        </is>
+      </c>
       <c r="F68" s="11" t="n"/>
       <c r="G68" s="11" t="n"/>
-      <c r="H68" s="12" t="n"/>
+      <c r="H68" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I68" s="12" t="n"/>
       <c r="J68" s="12" t="n"/>
       <c r="K68" s="12" t="n"/>
       <c r="L68" s="11" t="n"/>
-      <c r="M68" s="11" t="n"/>
-      <c r="N68" s="11" t="n"/>
+      <c r="M68" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="N68" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O68" s="11" t="n"/>
       <c r="P68" s="11" t="n"/>
       <c r="Q68" s="11" t="n"/>
-      <c r="R68" s="11" t="n"/>
-      <c r="S68" s="11" t="n"/>
-      <c r="T68" s="11" t="n"/>
-      <c r="U68" s="11" t="n"/>
-      <c r="V68" s="11" t="n"/>
-      <c r="W68" s="11" t="n"/>
-      <c r="X68" s="11" t="n"/>
+      <c r="R68" s="11" t="inlineStr">
+        <is>
+          <t>산책, 사진, 카페·디저트</t>
+        </is>
+      </c>
+      <c r="S68" s="11" t="inlineStr">
+        <is>
+          <t>레트로한, 정겨운</t>
+        </is>
+      </c>
+      <c r="T68" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U68" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V68" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W68" s="11" t="inlineStr">
+        <is>
+          <t>발산마을, 양동 발산마을</t>
+        </is>
+      </c>
+      <c r="X68" s="11" t="inlineStr">
+        <is>
+          <t>6·25 이후 피란민이 모여 형성되고 1970년대 방직공장 여성 노동자들이 살던 언덕 마을이다.</t>
+        </is>
+      </c>
       <c r="Y68" s="11" t="n"/>
-      <c r="Z68" s="12" t="n"/>
+      <c r="Z68" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA68" s="11" t="n"/>
-      <c r="AB68" s="11" t="n"/>
+      <c r="AB68" s="11" t="inlineStr">
+        <is>
+          <t>마을 안 역사문화박물관 건물은 운영 여부 미확인. 주소는 광주문화예술인문스토리플랫폼 표기(마을 대표 지점). 마을 안 '발산마을 역사문화박물관'(천변좌로130번길 2-7) 건물에 경매 물건 표시가 있어 운영 여부 미확인. 2025~2026년 마을 소식 못 찾음. 출처: https://www.ktriptips.com/kor/tourspot/2511261. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -6318,33 +7502,101 @@
           <t>n_067</t>
         </is>
       </c>
-      <c r="B69" s="11" t="n"/>
-      <c r="C69" s="11" t="n"/>
-      <c r="D69" s="11" t="n"/>
-      <c r="E69" s="11" t="n"/>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>광주김치타운 (광주김치박물관)</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>남구 임암동</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 김치로 60</t>
+        </is>
+      </c>
       <c r="F69" s="11" t="n"/>
       <c r="G69" s="11" t="n"/>
-      <c r="H69" s="12" t="n"/>
+      <c r="H69" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I69" s="12" t="n"/>
       <c r="J69" s="12" t="n"/>
-      <c r="K69" s="12" t="n"/>
-      <c r="L69" s="11" t="n"/>
-      <c r="M69" s="11" t="n"/>
-      <c r="N69" s="11" t="n"/>
+      <c r="K69" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="L69" s="11" t="inlineStr">
+        <is>
+          <t>설·추석 당일</t>
+        </is>
+      </c>
+      <c r="M69" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N69" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O69" s="11" t="n"/>
       <c r="P69" s="11" t="n"/>
       <c r="Q69" s="11" t="n"/>
-      <c r="R69" s="11" t="n"/>
-      <c r="S69" s="11" t="n"/>
-      <c r="T69" s="11" t="n"/>
-      <c r="U69" s="11" t="n"/>
-      <c r="V69" s="11" t="n"/>
-      <c r="W69" s="11" t="n"/>
-      <c r="X69" s="11" t="n"/>
+      <c r="R69" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 공방 체험</t>
+        </is>
+      </c>
+      <c r="S69" s="11" t="inlineStr">
+        <is>
+          <t>전통적인, 정겨운</t>
+        </is>
+      </c>
+      <c r="T69" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U69" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V69" s="11" t="inlineStr">
+        <is>
+          <t>가족, 아이 동반, 친구</t>
+        </is>
+      </c>
+      <c r="W69" s="11" t="inlineStr">
+        <is>
+          <t>김치타운, 광주세계김치연구소 김치타운</t>
+        </is>
+      </c>
+      <c r="X69" s="11" t="inlineStr">
+        <is>
+          <t>김치 문화 종합시설로 김치박물관(무료)과 김치 담그기 체험장이 있다.</t>
+        </is>
+      </c>
       <c r="Y69" s="11" t="n"/>
-      <c r="Z69" s="12" t="n"/>
+      <c r="Z69" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA69" s="11" t="n"/>
-      <c r="AB69" s="11" t="n"/>
+      <c r="AB69" s="11" t="inlineStr">
+        <is>
+          <t>요청한 서구가 아니라 남구 임암동임. 세계김치연구소(연구기관)와는 별개로 보임. 관람 시간은 블로그형 기사 1곳 출처라 신뢰도 낮음. 체험은 유료일 수 있음(요금 미확인). 출처: https://www.wegive.co.kr/wezine/detail/1238. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
@@ -6352,33 +7604,93 @@
           <t>n_068</t>
         </is>
       </c>
-      <c r="B70" s="11" t="n"/>
-      <c r="C70" s="11" t="n"/>
-      <c r="D70" s="11" t="n"/>
-      <c r="E70" s="11" t="n"/>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>영산강문화관·승촌보</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>남구 승촌동</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 승촌보길 90</t>
+        </is>
+      </c>
       <c r="F70" s="11" t="n"/>
       <c r="G70" s="11" t="n"/>
-      <c r="H70" s="12" t="n"/>
+      <c r="H70" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I70" s="12" t="n"/>
       <c r="J70" s="12" t="n"/>
       <c r="K70" s="12" t="n"/>
       <c r="L70" s="11" t="n"/>
-      <c r="M70" s="11" t="n"/>
-      <c r="N70" s="11" t="n"/>
+      <c r="M70" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N70" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O70" s="11" t="n"/>
       <c r="P70" s="11" t="n"/>
       <c r="Q70" s="11" t="n"/>
-      <c r="R70" s="11" t="n"/>
-      <c r="S70" s="11" t="n"/>
-      <c r="T70" s="11" t="n"/>
-      <c r="U70" s="11" t="n"/>
-      <c r="V70" s="11" t="n"/>
-      <c r="W70" s="11" t="n"/>
-      <c r="X70" s="11" t="n"/>
+      <c r="R70" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 산책, 사진</t>
+        </is>
+      </c>
+      <c r="S70" s="11" t="inlineStr">
+        <is>
+          <t>캐주얼한, 조용한</t>
+        </is>
+      </c>
+      <c r="T70" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U70" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V70" s="11" t="inlineStr">
+        <is>
+          <t>친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W70" s="11" t="inlineStr">
+        <is>
+          <t>승촌보, 영산강 승촌보, 영산강 자전거길 승촌보 인증센터</t>
+        </is>
+      </c>
+      <c r="X70" s="11" t="inlineStr">
+        <is>
+          <t>K-water가 운영하는 지하 1층·지상 3층 문화관으로 1층 상설전시실(영산강 역사·문화·자연), 2층 기획전시실, 3층 야외 전망대가 있다.</t>
+        </is>
+      </c>
       <c r="Y70" s="11" t="n"/>
-      <c r="Z70" s="12" t="n"/>
+      <c r="Z70" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA70" s="11" t="n"/>
-      <c r="AB70" s="11" t="n"/>
+      <c r="AB70" s="11" t="inlineStr">
+        <is>
+          <t>운영시간은 임시값(승촌보 산책은 상시). 요청 목록엔 광산구로 되어 있으나 주소는 남구 승촌보길 90(승촌보 자체는 광산구·나주 경계에 걸침, 미확인). 운영 시간·휴관일 미확인, cost 0은 무료 공공 홍보관이라는 추정(명시 출처 없음, cost 를 null 로 바꿔도 됨). 출처: https://www.kwater.or.kr/cust/sub02/sub02/sub04/promotion13Page.do?s_mid=1066. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
@@ -6386,33 +7698,101 @@
           <t>n_069</t>
         </is>
       </c>
-      <c r="B71" s="11" t="n"/>
-      <c r="C71" s="11" t="n"/>
-      <c r="D71" s="11" t="n"/>
-      <c r="E71" s="11" t="n"/>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>5·18민주화운동기록관</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>동구 금남로</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 금남로 221</t>
+        </is>
+      </c>
       <c r="F71" s="11" t="n"/>
       <c r="G71" s="11" t="n"/>
-      <c r="H71" s="12" t="n"/>
+      <c r="H71" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I71" s="12" t="n"/>
       <c r="J71" s="12" t="n"/>
-      <c r="K71" s="12" t="n"/>
-      <c r="L71" s="11" t="n"/>
-      <c r="M71" s="11" t="n"/>
-      <c r="N71" s="11" t="n"/>
+      <c r="K71" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>월요일이 공휴일이면 다음 날 휴관, 1/1, 설·추석 연휴</t>
+        </is>
+      </c>
+      <c r="M71" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N71" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O71" s="11" t="n"/>
       <c r="P71" s="11" t="n"/>
       <c r="Q71" s="11" t="n"/>
-      <c r="R71" s="11" t="n"/>
-      <c r="S71" s="11" t="n"/>
-      <c r="T71" s="11" t="n"/>
-      <c r="U71" s="11" t="n"/>
-      <c r="V71" s="11" t="n"/>
-      <c r="W71" s="11" t="n"/>
-      <c r="X71" s="11" t="n"/>
+      <c r="R71" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 전시 관람</t>
+        </is>
+      </c>
+      <c r="S71" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 현대적인</t>
+        </is>
+      </c>
+      <c r="T71" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U71" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V71" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W71" s="11" t="inlineStr">
+        <is>
+          <t>5·18기록관, 옛 광주가톨릭센터</t>
+        </is>
+      </c>
+      <c r="X71" s="11" t="inlineStr">
+        <is>
+          <t>1980년 5월 현장인 옛 광주가톨릭센터 건물에 2015년 5월 개관.</t>
+        </is>
+      </c>
       <c r="Y71" s="11" t="n"/>
-      <c r="Z71" s="12" t="n"/>
+      <c r="Z71" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA71" s="11" t="n"/>
-      <c r="AB71" s="11" t="n"/>
+      <c r="AB71" s="11" t="inlineStr">
+        <is>
+          <t>도로명 주소는 출처에서 못 찾아 알려진 주소(옛 가톨릭센터)를 넣음, 확인 필요. 입장 마감 17:40. 특별·기획전은 유료일 수 있음. 주소 '금남로 221'은 검색 결과에서 확인 못 해 null. 2025-02-15 탄핵 반대 집회 때 안전 문제로 12~18시 임시 휴관한 적 있음(하루). 출처: https://www.ktriptips.com/kor/culture/2755010. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
@@ -6420,33 +7800,97 @@
           <t>n_070</t>
         </is>
       </c>
-      <c r="B72" s="11" t="n"/>
-      <c r="C72" s="11" t="n"/>
-      <c r="D72" s="11" t="n"/>
-      <c r="E72" s="11" t="n"/>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>무등산 리프트·모노레일 (지산유원지)</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>동구 지산동</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 지호로164번길 35-1</t>
+        </is>
+      </c>
       <c r="F72" s="11" t="n"/>
       <c r="G72" s="11" t="n"/>
-      <c r="H72" s="12" t="n"/>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>10:00-18:00</t>
+        </is>
+      </c>
       <c r="I72" s="12" t="n"/>
       <c r="J72" s="12" t="n"/>
       <c r="K72" s="12" t="n"/>
-      <c r="L72" s="11" t="n"/>
-      <c r="M72" s="11" t="n"/>
-      <c r="N72" s="11" t="n"/>
+      <c r="L72" s="11" t="inlineStr">
+        <is>
+          <t>기상 악화 시 운행 중단·조기 마감</t>
+        </is>
+      </c>
+      <c r="M72" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="N72" s="11" t="n">
+        <v>17000</v>
+      </c>
       <c r="O72" s="11" t="n"/>
       <c r="P72" s="11" t="n"/>
       <c r="Q72" s="11" t="n"/>
-      <c r="R72" s="11" t="n"/>
-      <c r="S72" s="11" t="n"/>
-      <c r="T72" s="11" t="n"/>
-      <c r="U72" s="11" t="n"/>
-      <c r="V72" s="11" t="n"/>
-      <c r="W72" s="11" t="n"/>
-      <c r="X72" s="11" t="n"/>
+      <c r="R72" s="11" t="inlineStr">
+        <is>
+          <t>사진, 산책, 휴식</t>
+        </is>
+      </c>
+      <c r="S72" s="11" t="inlineStr">
+        <is>
+          <t>레트로한, 캐주얼한, 정겨운</t>
+        </is>
+      </c>
+      <c r="T72" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U72" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V72" s="11" t="inlineStr">
+        <is>
+          <t>친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W72" s="11" t="inlineStr">
+        <is>
+          <t>지산유원지, 무등산 모노레일, 무등산 리프트</t>
+        </is>
+      </c>
+      <c r="X72" s="11" t="inlineStr">
+        <is>
+          <t>무등산 자락 지산유원지의 리프트와 모노레일.</t>
+        </is>
+      </c>
       <c r="Y72" s="11" t="n"/>
-      <c r="Z72" s="12" t="n"/>
+      <c r="Z72" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA72" s="11" t="n"/>
-      <c r="AB72" s="11" t="n"/>
+      <c r="AB72" s="11" t="inlineStr">
+        <is>
+          <t>주말·공휴일 09:00-19:00. 주소·시간·요금이 출처마다 다름. 주소가 출처마다 다름(지호로164번길 14-10 / 35-1). 출처: https://www.ktriptips.com/kor/tourspot/2755042. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
@@ -6454,33 +7898,101 @@
           <t>n_071</t>
         </is>
       </c>
-      <c r="B73" s="11" t="n"/>
-      <c r="C73" s="11" t="n"/>
-      <c r="D73" s="11" t="n"/>
-      <c r="E73" s="11" t="n"/>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>이강하미술관</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>남구 양림동</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 3·1만세운동길 6</t>
+        </is>
+      </c>
       <c r="F73" s="11" t="n"/>
       <c r="G73" s="11" t="n"/>
-      <c r="H73" s="12" t="n"/>
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <t>10:00-18:00</t>
+        </is>
+      </c>
       <c r="I73" s="12" t="n"/>
       <c r="J73" s="12" t="n"/>
-      <c r="K73" s="12" t="n"/>
-      <c r="L73" s="11" t="n"/>
-      <c r="M73" s="11" t="n"/>
-      <c r="N73" s="11" t="n"/>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="L73" s="11" t="inlineStr">
+        <is>
+          <t>1/1, 설·추석 연휴</t>
+        </is>
+      </c>
+      <c r="M73" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N73" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O73" s="11" t="n"/>
       <c r="P73" s="11" t="n"/>
       <c r="Q73" s="11" t="n"/>
-      <c r="R73" s="11" t="n"/>
-      <c r="S73" s="11" t="n"/>
-      <c r="T73" s="11" t="n"/>
-      <c r="U73" s="11" t="n"/>
-      <c r="V73" s="11" t="n"/>
-      <c r="W73" s="11" t="n"/>
-      <c r="X73" s="11" t="n"/>
+      <c r="R73" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람</t>
+        </is>
+      </c>
+      <c r="S73" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 아늑한</t>
+        </is>
+      </c>
+      <c r="T73" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U73" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V73" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W73" s="11" t="inlineStr">
+        <is>
+          <t>남구 이강하미술관</t>
+        </is>
+      </c>
+      <c r="X73" s="11" t="inlineStr">
+        <is>
+          <t>옛 양림동 주민센터를 리모델링해 2018년 2월 9일 개관한 남구 미술관.</t>
+        </is>
+      </c>
       <c r="Y73" s="11" t="n"/>
-      <c r="Z73" s="12" t="n"/>
+      <c r="Z73" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA73" s="11" t="n"/>
-      <c r="AB73" s="11" t="n"/>
+      <c r="AB73" s="11" t="inlineStr">
+        <is>
+          <t>점심시간 12:00-13:00 표기 있음. 공식 누리집 lkh-artmuseum.com 직접 확인 못 함. 2025~2026 전시 일정 기사는 찾지 못함. 문의 062-674-8515. 양림역사문화마을 안. 출처: https://www.ktriptips.com/kor/culture/3401691. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
@@ -6488,33 +8000,97 @@
           <t>n_072</t>
         </is>
       </c>
-      <c r="B74" s="11" t="n"/>
-      <c r="C74" s="11" t="n"/>
-      <c r="D74" s="11" t="n"/>
-      <c r="E74" s="11" t="n"/>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>호랑가시나무 아트폴리곤</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>남구 양림동</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 제중로47번길 20</t>
+        </is>
+      </c>
       <c r="F74" s="11" t="n"/>
       <c r="G74" s="11" t="n"/>
-      <c r="H74" s="12" t="n"/>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>10:00-18:00</t>
+        </is>
+      </c>
       <c r="I74" s="12" t="n"/>
       <c r="J74" s="12" t="n"/>
       <c r="K74" s="12" t="n"/>
-      <c r="L74" s="11" t="n"/>
-      <c r="M74" s="11" t="n"/>
-      <c r="N74" s="11" t="n"/>
+      <c r="L74" s="11" t="inlineStr">
+        <is>
+          <t>전시 준비 기간 휴무</t>
+        </is>
+      </c>
+      <c r="M74" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N74" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O74" s="11" t="n"/>
       <c r="P74" s="11" t="n"/>
       <c r="Q74" s="11" t="n"/>
-      <c r="R74" s="11" t="n"/>
-      <c r="S74" s="11" t="n"/>
-      <c r="T74" s="11" t="n"/>
-      <c r="U74" s="11" t="n"/>
-      <c r="V74" s="11" t="n"/>
-      <c r="W74" s="11" t="n"/>
-      <c r="X74" s="11" t="n"/>
+      <c r="R74" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 건축 구경, 사진</t>
+        </is>
+      </c>
+      <c r="S74" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 현대적인</t>
+        </is>
+      </c>
+      <c r="T74" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U74" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V74" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인</t>
+        </is>
+      </c>
+      <c r="W74" s="11" t="inlineStr">
+        <is>
+          <t>아트폴리곤, 호랑가시나무 창작소</t>
+        </is>
+      </c>
+      <c r="X74" s="11" t="inlineStr">
+        <is>
+          <t>원요한 선교사 사택의 차고였던 건물을 원래 구조를 살려 증축한 복합문화공간.</t>
+        </is>
+      </c>
       <c r="Y74" s="11" t="n"/>
-      <c r="Z74" s="12" t="n"/>
+      <c r="Z74" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA74" s="11" t="n"/>
-      <c r="AB74" s="11" t="n"/>
+      <c r="AB74" s="11" t="inlineStr">
+        <is>
+          <t>주소 출처 차이: 제중로47번길 20(디지털 광주문화대전 위키) / 22. 정기 휴무일 미확인, 전시 준비 기간에는 쉬므로 방문 전 전화 권장(062-682-0976). 양림역사문화마을 안. 출처: https://www.ktriptips.com/kor/culture/2953078. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
@@ -6522,33 +8098,93 @@
           <t>n_073</t>
         </is>
       </c>
-      <c r="B75" s="11" t="n"/>
-      <c r="C75" s="11" t="n"/>
-      <c r="D75" s="11" t="n"/>
-      <c r="E75" s="11" t="n"/>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>사직 빛의 숲</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>야간 콘텐츠</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>남구 사동</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 사직길 49</t>
+        </is>
+      </c>
       <c r="F75" s="11" t="n"/>
       <c r="G75" s="11" t="n"/>
-      <c r="H75" s="12" t="n"/>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>19:30-22:30</t>
+        </is>
+      </c>
       <c r="I75" s="12" t="n"/>
       <c r="J75" s="12" t="n"/>
       <c r="K75" s="12" t="n"/>
       <c r="L75" s="11" t="n"/>
-      <c r="M75" s="11" t="n"/>
-      <c r="N75" s="11" t="n"/>
+      <c r="M75" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N75" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O75" s="11" t="n"/>
       <c r="P75" s="11" t="n"/>
       <c r="Q75" s="11" t="n"/>
-      <c r="R75" s="11" t="n"/>
-      <c r="S75" s="11" t="n"/>
-      <c r="T75" s="11" t="n"/>
-      <c r="U75" s="11" t="n"/>
-      <c r="V75" s="11" t="n"/>
-      <c r="W75" s="11" t="n"/>
-      <c r="X75" s="11" t="n"/>
+      <c r="R75" s="11" t="inlineStr">
+        <is>
+          <t>야경, 산책, 사진</t>
+        </is>
+      </c>
+      <c r="S75" s="11" t="inlineStr">
+        <is>
+          <t>현대적인, 아늑한</t>
+        </is>
+      </c>
+      <c r="T75" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U75" s="11" t="inlineStr">
+        <is>
+          <t>저녁, 밤</t>
+        </is>
+      </c>
+      <c r="V75" s="11" t="inlineStr">
+        <is>
+          <t>친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W75" s="11" t="inlineStr">
+        <is>
+          <t>사직공원 빛의 숲, 미디어아트거리 빛의 숲, 사직 미디어아트</t>
+        </is>
+      </c>
+      <c r="X75" s="11" t="inlineStr">
+        <is>
+          <t>사직공원 기존 산책로 830m를 미디어아트 야간경관 코스로 꾸몄다.</t>
+        </is>
+      </c>
       <c r="Y75" s="11" t="n"/>
-      <c r="Z75" s="12" t="n"/>
+      <c r="Z75" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA75" s="11" t="n"/>
-      <c r="AB75" s="11" t="n"/>
+      <c r="AB75" s="11" t="inlineStr">
+        <is>
+          <t>4~10월 19:30-23:00, 11~3월 18:30-22:30 이라 겹치는 시간을 넣음. 사직공원 전망타워와 같은 공원. 기존 '사직공원 전망타워'와 같은 공원·같은 동선(전망타워가 코스에 포함). 별도 장소로 둘지, 전망타워에 합칠지 팀 판단 필요. 출처: https://www.metroseoul.co.kr/article/20231011500624. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
@@ -6556,33 +8192,93 @@
           <t>n_074</t>
         </is>
       </c>
-      <c r="B76" s="11" t="n"/>
-      <c r="C76" s="11" t="n"/>
-      <c r="D76" s="11" t="n"/>
-      <c r="E76" s="11" t="n"/>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>사직동 통기타거리</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>야간 콘텐츠</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>남구 사직동</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 사직동</t>
+        </is>
+      </c>
       <c r="F76" s="11" t="n"/>
       <c r="G76" s="11" t="n"/>
-      <c r="H76" s="12" t="n"/>
+      <c r="H76" s="12" t="inlineStr">
+        <is>
+          <t>19:00-25:00</t>
+        </is>
+      </c>
       <c r="I76" s="12" t="n"/>
       <c r="J76" s="12" t="n"/>
       <c r="K76" s="12" t="n"/>
       <c r="L76" s="11" t="n"/>
-      <c r="M76" s="11" t="n"/>
-      <c r="N76" s="11" t="n"/>
+      <c r="M76" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N76" s="11" t="n">
+        <v>15000</v>
+      </c>
       <c r="O76" s="11" t="n"/>
       <c r="P76" s="11" t="n"/>
       <c r="Q76" s="11" t="n"/>
-      <c r="R76" s="11" t="n"/>
-      <c r="S76" s="11" t="n"/>
-      <c r="T76" s="11" t="n"/>
-      <c r="U76" s="11" t="n"/>
-      <c r="V76" s="11" t="n"/>
-      <c r="W76" s="11" t="n"/>
-      <c r="X76" s="11" t="n"/>
+      <c r="R76" s="11" t="inlineStr">
+        <is>
+          <t>술, 공연·영화, 산책</t>
+        </is>
+      </c>
+      <c r="S76" s="11" t="inlineStr">
+        <is>
+          <t>레트로한, 정겨운</t>
+        </is>
+      </c>
+      <c r="T76" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U76" s="11" t="inlineStr">
+        <is>
+          <t>저녁, 밤</t>
+        </is>
+      </c>
+      <c r="V76" s="11" t="inlineStr">
+        <is>
+          <t>친구, 연인</t>
+        </is>
+      </c>
+      <c r="W76" s="11" t="inlineStr">
+        <is>
+          <t>사직 통기타 거리, 사직골, 살롱 드 사직</t>
+        </is>
+      </c>
+      <c r="X76" s="11" t="inlineStr">
+        <is>
+          <t>한국 포크음악의 거점으로 불려 온 사직동 라이브카페 골목.</t>
+        </is>
+      </c>
       <c r="Y76" s="11" t="n"/>
-      <c r="Z76" s="12" t="n"/>
+      <c r="Z76" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA76" s="11" t="n"/>
-      <c r="AB76" s="11" t="n"/>
+      <c r="AB76" s="11" t="inlineStr">
+        <is>
+          <t>영업시간·1인 지출은 임시값(라이브 카페·술집 거리, 가게마다 다름). 주소 미확인. 상권 육성·살롱 개장 기사의 연도가 검색 결과에서 분명하지 않음(2025년 기사인지 확인 못 함). 현재 라이브카페 영업 수·상시 버스킹 실제 운영 여부 미확인. 사직공원·빛의 숲 바로 아래라 야간 동선에 묶을 수 있음. 출처: https://www.wikitree.co.kr/articles/1048271. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
@@ -6590,33 +8286,93 @@
           <t>n_075</t>
         </is>
       </c>
-      <c r="B77" s="11" t="n"/>
-      <c r="C77" s="11" t="n"/>
-      <c r="D77" s="11" t="n"/>
-      <c r="E77" s="11" t="n"/>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>포충사</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>남구 원산동</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 남구 포충로 767</t>
+        </is>
+      </c>
       <c r="F77" s="11" t="n"/>
       <c r="G77" s="11" t="n"/>
-      <c r="H77" s="12" t="n"/>
+      <c r="H77" s="12" t="inlineStr">
+        <is>
+          <t>09:00-17:00</t>
+        </is>
+      </c>
       <c r="I77" s="12" t="n"/>
       <c r="J77" s="12" t="n"/>
       <c r="K77" s="12" t="n"/>
       <c r="L77" s="11" t="n"/>
-      <c r="M77" s="11" t="n"/>
-      <c r="N77" s="11" t="n"/>
+      <c r="M77" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N77" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O77" s="11" t="n"/>
       <c r="P77" s="11" t="n"/>
       <c r="Q77" s="11" t="n"/>
-      <c r="R77" s="11" t="n"/>
-      <c r="S77" s="11" t="n"/>
-      <c r="T77" s="11" t="n"/>
-      <c r="U77" s="11" t="n"/>
-      <c r="V77" s="11" t="n"/>
-      <c r="W77" s="11" t="n"/>
-      <c r="X77" s="11" t="n"/>
+      <c r="R77" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 건축 구경, 산책</t>
+        </is>
+      </c>
+      <c r="S77" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T77" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U77" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V77" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W77" s="11" t="inlineStr">
+        <is>
+          <t>광주 포충사</t>
+        </is>
+      </c>
+      <c r="X77" s="11" t="inlineStr">
+        <is>
+          <t>임진왜란 의병장 고경명과 아들 고종후·고인후, 금산전투에서 함께 순절한 유팽로·안영을 모신 사당.</t>
+        </is>
+      </c>
       <c r="Y77" s="11" t="n"/>
-      <c r="Z77" s="12" t="n"/>
+      <c r="Z77" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA77" s="11" t="n"/>
-      <c r="AB77" s="11" t="n"/>
+      <c r="AB77" s="11" t="inlineStr">
+        <is>
+          <t>3~10월 09:00-18:00, 11~2월 09:00-17:00(짧은 쪽). 관람료 미확인(0 으로 넣음). 운영시간은 ktriptips(2026-08-14 기준). 하절기 3~9월, 동절기 11~2월로 10월 시간 미확인. 휴관일·관람료 확인 못 함(closed_days/cost null). 원산동은 대촌동(행정동) 관할. 출처: https://www.ktriptips.com/kor/tourspot/126384. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">

--- a/docs/가게조사_챔필주변_초안.xlsx
+++ b/docs/가게조사_챔필주변_초안.xlsx
@@ -8380,33 +8380,97 @@
           <t>n_076</t>
         </is>
       </c>
-      <c r="B78" s="11" t="n"/>
-      <c r="C78" s="11" t="n"/>
-      <c r="D78" s="11" t="n"/>
-      <c r="E78" s="11" t="n"/>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>동구 인문학당</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>동구 동명동</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 동계천로 168-5</t>
+        </is>
+      </c>
       <c r="F78" s="11" t="n"/>
       <c r="G78" s="11" t="n"/>
-      <c r="H78" s="12" t="n"/>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>10:00-18:00</t>
+        </is>
+      </c>
       <c r="I78" s="12" t="n"/>
       <c r="J78" s="12" t="n"/>
-      <c r="K78" s="12" t="n"/>
+      <c r="K78" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
       <c r="L78" s="11" t="n"/>
-      <c r="M78" s="11" t="n"/>
-      <c r="N78" s="11" t="n"/>
+      <c r="M78" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N78" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O78" s="11" t="n"/>
       <c r="P78" s="11" t="n"/>
       <c r="Q78" s="11" t="n"/>
-      <c r="R78" s="11" t="n"/>
-      <c r="S78" s="11" t="n"/>
-      <c r="T78" s="11" t="n"/>
-      <c r="U78" s="11" t="n"/>
-      <c r="V78" s="11" t="n"/>
-      <c r="W78" s="11" t="n"/>
-      <c r="X78" s="11" t="n"/>
+      <c r="R78" s="11" t="inlineStr">
+        <is>
+          <t>건축 구경, 역사 탐방, 사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S78" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 레트로한, 아늑한</t>
+        </is>
+      </c>
+      <c r="T78" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U78" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V78" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W78" s="11" t="inlineStr">
+        <is>
+          <t>동구인문학당</t>
+        </is>
+      </c>
+      <c r="X78" s="11" t="inlineStr">
+        <is>
+          <t>1954년(상량문 기록) 지어진 동명동 근대 가옥(한옥과 양옥이 한 집을 이룬 구조)을 동구청이 매입·리모델링해 2022년 1월 개관한 인문 거점시설.</t>
+        </is>
+      </c>
       <c r="Y78" s="11" t="n"/>
-      <c r="Z78" s="12" t="n"/>
+      <c r="Z78" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA78" s="11" t="n"/>
-      <c r="AB78" s="11" t="n"/>
+      <c r="AB78" s="11" t="inlineStr">
+        <is>
+          <t>운영시간·월요일 휴관·무료·문의 062-608-2176은 관광정보 재가공 사이트(ktriptips) 기준이라 공식 확인 필요. 건축 연도 1953년으로 적은 자료도 있음. 동명동 카페거리 초입·푸른길 옆. 출처: https://kiramonthly.com/1830. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
@@ -8414,33 +8478,93 @@
           <t>n_077</t>
         </is>
       </c>
-      <c r="B79" s="11" t="n"/>
-      <c r="C79" s="11" t="n"/>
-      <c r="D79" s="11" t="n"/>
-      <c r="E79" s="11" t="n"/>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>주남마을 5·18 사적지 (양민학살지·위령비)</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>동구 지원동</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 지원동</t>
+        </is>
+      </c>
       <c r="F79" s="11" t="n"/>
       <c r="G79" s="11" t="n"/>
-      <c r="H79" s="12" t="n"/>
+      <c r="H79" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I79" s="12" t="n"/>
       <c r="J79" s="12" t="n"/>
       <c r="K79" s="12" t="n"/>
       <c r="L79" s="11" t="n"/>
-      <c r="M79" s="11" t="n"/>
-      <c r="N79" s="11" t="n"/>
+      <c r="M79" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="N79" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O79" s="11" t="n"/>
       <c r="P79" s="11" t="n"/>
       <c r="Q79" s="11" t="n"/>
-      <c r="R79" s="11" t="n"/>
-      <c r="S79" s="11" t="n"/>
-      <c r="T79" s="11" t="n"/>
-      <c r="U79" s="11" t="n"/>
-      <c r="V79" s="11" t="n"/>
-      <c r="W79" s="11" t="n"/>
-      <c r="X79" s="11" t="n"/>
+      <c r="R79" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방</t>
+        </is>
+      </c>
+      <c r="S79" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 정겨운</t>
+        </is>
+      </c>
+      <c r="T79" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U79" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V79" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 가족</t>
+        </is>
+      </c>
+      <c r="W79" s="11" t="inlineStr">
+        <is>
+          <t>주남마을 위령비, 주남마을 인근 양민학살지, 5·18 사적지 제14호</t>
+        </is>
+      </c>
+      <c r="X79" s="11" t="inlineStr">
+        <is>
+          <t>1980년 5월 23일 주남마을 입구 도로에서 계엄군이 미니버스에 총격을 가해 승객 대부분이 숨진 곳으로, 1998년 5·18 사적지 제14호로 지정됐다.</t>
+        </is>
+      </c>
       <c r="Y79" s="11" t="n"/>
-      <c r="Z79" s="12" t="n"/>
+      <c r="Z79" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA79" s="11" t="n"/>
-      <c r="AB79" s="11" t="n"/>
+      <c r="AB79" s="11" t="inlineStr">
+        <is>
+          <t>주소는 동 이름만(지도에서 좌표 수정 필요). 야외 위령비라 상시 개방으로 적었으나 공식 개방시간 자료는 없음. 위령비 도로명 주소 미확인. 도심(충장로)에서 화순 방향 외곽이라 차량 이동 필요. 희생자 수는 출처마다 다름(15명/17명). 출처: https://www.khan.co.kr/article/202406021611001. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
@@ -8448,33 +8572,93 @@
           <t>n_078</t>
         </is>
       </c>
-      <c r="B80" s="11" t="n"/>
-      <c r="C80" s="11" t="n"/>
-      <c r="D80" s="11" t="n"/>
-      <c r="E80" s="11" t="n"/>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>남동성당 (5·18 사적지)</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>동구 남동</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 남동</t>
+        </is>
+      </c>
       <c r="F80" s="11" t="n"/>
       <c r="G80" s="11" t="n"/>
-      <c r="H80" s="12" t="n"/>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I80" s="12" t="n"/>
       <c r="J80" s="12" t="n"/>
       <c r="K80" s="12" t="n"/>
       <c r="L80" s="11" t="n"/>
-      <c r="M80" s="11" t="n"/>
-      <c r="N80" s="11" t="n"/>
+      <c r="M80" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="N80" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O80" s="11" t="n"/>
       <c r="P80" s="11" t="n"/>
       <c r="Q80" s="11" t="n"/>
-      <c r="R80" s="11" t="n"/>
-      <c r="S80" s="11" t="n"/>
-      <c r="T80" s="11" t="n"/>
-      <c r="U80" s="11" t="n"/>
-      <c r="V80" s="11" t="n"/>
-      <c r="W80" s="11" t="n"/>
-      <c r="X80" s="11" t="n"/>
+      <c r="R80" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 건축 구경</t>
+        </is>
+      </c>
+      <c r="S80" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T80" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U80" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V80" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 가족</t>
+        </is>
+      </c>
+      <c r="W80" s="11" t="inlineStr">
+        <is>
+          <t>천주교 광주대교구 남동성당, 5·18 기념성당, 5·18 사적지 제25호</t>
+        </is>
+      </c>
+      <c r="X80" s="11" t="inlineStr">
+        <is>
+          <t>1980년 5월 22~26일 김성용 주임신부 등 광주 민주인사들이 모여 수습대책을 논의한 곳으로, 광주시 5·18 사적지 제25호(1998년 일괄 지정 24곳 이후 추가 지정)다.</t>
+        </is>
+      </c>
       <c r="Y80" s="11" t="n"/>
-      <c r="Z80" s="12" t="n"/>
+      <c r="Z80" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA80" s="11" t="n"/>
-      <c r="AB80" s="11" t="n"/>
+      <c r="AB80" s="11" t="inlineStr">
+        <is>
+          <t>주소는 동 이름만(지도에서 좌표 수정 필요). 운영시간은 임시값(성당 외관·사적 표지 위주). 도로명 주소·방문 가능 시간 미확인(현역 성당이라 미사 시간 외 출입 여부 확인 필요). ACC·남광주시장 사이 원도심이라 도보 코스에 넣기 좋음. 출처: https://www.ohmynews.com/NWS_Web/View/at_pg.aspx?CNTN_CD=A0003148182. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
@@ -8482,33 +8666,93 @@
           <t>n_079</t>
         </is>
       </c>
-      <c r="B81" s="11" t="n"/>
-      <c r="C81" s="11" t="n"/>
-      <c r="D81" s="11" t="n"/>
-      <c r="E81" s="11" t="n"/>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>5·18 민주인권길 (오월길 도보 코스)</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>동구 계림동</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 계림동</t>
+        </is>
+      </c>
       <c r="F81" s="11" t="n"/>
       <c r="G81" s="11" t="n"/>
-      <c r="H81" s="12" t="n"/>
+      <c r="H81" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I81" s="12" t="n"/>
       <c r="J81" s="12" t="n"/>
       <c r="K81" s="12" t="n"/>
       <c r="L81" s="11" t="n"/>
-      <c r="M81" s="11" t="n"/>
-      <c r="N81" s="11" t="n"/>
+      <c r="M81" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="N81" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O81" s="11" t="n"/>
       <c r="P81" s="11" t="n"/>
       <c r="Q81" s="11" t="n"/>
-      <c r="R81" s="11" t="n"/>
-      <c r="S81" s="11" t="n"/>
-      <c r="T81" s="11" t="n"/>
-      <c r="U81" s="11" t="n"/>
-      <c r="V81" s="11" t="n"/>
-      <c r="W81" s="11" t="n"/>
-      <c r="X81" s="11" t="n"/>
+      <c r="R81" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 산책</t>
+        </is>
+      </c>
+      <c r="S81" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 레트로한</t>
+        </is>
+      </c>
+      <c r="T81" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U81" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V81" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 가족</t>
+        </is>
+      </c>
+      <c r="W81" s="11" t="inlineStr">
+        <is>
+          <t>오월길, 오월인권길, 동구 민주인권길</t>
+        </is>
+      </c>
+      <c r="X81" s="11" t="inlineStr">
+        <is>
+          <t>광주고등학교에서 출발해 광주MBC 옛터, 녹두서점 옛터, 옛 YMCA, 옛 전남도청, 5·18민주광장, 옛 적십자병원 등 동구 5·18 사적지를 잇는 약 8km, 2~3시간 도보 코스(2017년 동구 조성).</t>
+        </is>
+      </c>
       <c r="Y81" s="11" t="n"/>
-      <c r="Z81" s="12" t="n"/>
+      <c r="Z81" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA81" s="11" t="n"/>
-      <c r="AB81" s="11" t="n"/>
+      <c r="AB81" s="11" t="inlineStr">
+        <is>
+          <t>코스 정보가 2017년 자료라 현재 안내판·노선 확인 필요. 출발점(광주고) 근처로 동 이름만 넣음. 코스 정보는 2017년 기사 기준이라 현재 구간·안내 상태는 확인 필요. 출처: https://m.go.seoul.co.kr/news/2017/02/16/20170216014009. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
@@ -8516,33 +8760,93 @@
           <t>n_080</t>
         </is>
       </c>
-      <c r="B82" s="11" t="n"/>
-      <c r="C82" s="11" t="n"/>
-      <c r="D82" s="11" t="n"/>
-      <c r="E82" s="11" t="n"/>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>조선대학교 본관</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>동구 서석동</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 필문대로 309</t>
+        </is>
+      </c>
       <c r="F82" s="11" t="n"/>
       <c r="G82" s="11" t="n"/>
-      <c r="H82" s="12" t="n"/>
+      <c r="H82" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I82" s="12" t="n"/>
       <c r="J82" s="12" t="n"/>
       <c r="K82" s="12" t="n"/>
       <c r="L82" s="11" t="n"/>
-      <c r="M82" s="11" t="n"/>
-      <c r="N82" s="11" t="n"/>
+      <c r="M82" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N82" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O82" s="11" t="n"/>
       <c r="P82" s="11" t="n"/>
       <c r="Q82" s="11" t="n"/>
-      <c r="R82" s="11" t="n"/>
-      <c r="S82" s="11" t="n"/>
-      <c r="T82" s="11" t="n"/>
-      <c r="U82" s="11" t="n"/>
-      <c r="V82" s="11" t="n"/>
-      <c r="W82" s="11" t="n"/>
-      <c r="X82" s="11" t="n"/>
+      <c r="R82" s="11" t="inlineStr">
+        <is>
+          <t>건축 구경, 사진, 산책</t>
+        </is>
+      </c>
+      <c r="S82" s="11" t="inlineStr">
+        <is>
+          <t>레트로한, 조용한</t>
+        </is>
+      </c>
+      <c r="T82" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U82" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V82" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W82" s="11" t="inlineStr">
+        <is>
+          <t>조선대 본관, 조선대 하얀 건물</t>
+        </is>
+      </c>
+      <c r="X82" s="11" t="inlineStr">
+        <is>
+          <t>국가등록문화유산.</t>
+        </is>
+      </c>
       <c r="Y82" s="11" t="n"/>
-      <c r="Z82" s="12" t="n"/>
+      <c r="Z82" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA82" s="11" t="n"/>
-      <c r="AB82" s="11" t="n"/>
+      <c r="AB82" s="11" t="inlineStr">
+        <is>
+          <t>외관 관람 위주. 주소는 대학 대표 주소(알려진 값, 확인 필요). 지번 동구 서석동 375. 등록 번호·도로명 주소 미확인. 대학 캠퍼스 건물이라 외관 관람 위주로, 내부 출입이나 공개 시간은 확인 못 함. 출처: https://dh.aks.ac.kr/~gwangju/wiki/index.php/%EA%B4%91%EC%A3%BC_%EC%A1%B0%EC%84%A0%EB%8C%80%ED%95%99%EA%B5%90_%EB%B3%B8%EA%B4%80. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
@@ -8550,33 +8854,93 @@
           <t>n_081</t>
         </is>
       </c>
-      <c r="B83" s="11" t="n"/>
-      <c r="C83" s="11" t="n"/>
-      <c r="D83" s="11" t="n"/>
-      <c r="E83" s="11" t="n"/>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>약사암</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>동구 운림동</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 증심사길160번길 89</t>
+        </is>
+      </c>
       <c r="F83" s="11" t="n"/>
       <c r="G83" s="11" t="n"/>
-      <c r="H83" s="12" t="n"/>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>06:00-18:00</t>
+        </is>
+      </c>
       <c r="I83" s="12" t="n"/>
       <c r="J83" s="12" t="n"/>
       <c r="K83" s="12" t="n"/>
       <c r="L83" s="11" t="n"/>
-      <c r="M83" s="11" t="n"/>
-      <c r="N83" s="11" t="n"/>
+      <c r="M83" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N83" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O83" s="11" t="n"/>
       <c r="P83" s="11" t="n"/>
       <c r="Q83" s="11" t="n"/>
-      <c r="R83" s="11" t="n"/>
-      <c r="S83" s="11" t="n"/>
-      <c r="T83" s="11" t="n"/>
-      <c r="U83" s="11" t="n"/>
-      <c r="V83" s="11" t="n"/>
-      <c r="W83" s="11" t="n"/>
-      <c r="X83" s="11" t="n"/>
+      <c r="R83" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 산책, 건축 구경</t>
+        </is>
+      </c>
+      <c r="S83" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T83" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U83" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V83" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W83" s="11" t="inlineStr">
+        <is>
+          <t>약사사, 인왕사</t>
+        </is>
+      </c>
+      <c r="X83" s="11" t="inlineStr">
+        <is>
+          <t>증심사의 부속 암자로 새인봉 아래에 있다.</t>
+        </is>
+      </c>
       <c r="Y83" s="11" t="n"/>
-      <c r="Z83" s="12" t="n"/>
+      <c r="Z83" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA83" s="11" t="n"/>
-      <c r="AB83" s="11" t="n"/>
+      <c r="AB83" s="11" t="inlineStr">
+        <is>
+          <t>운영시간은 임시값. 증심사에서 새인봉 쪽 등산로로 올라감. 관람시간과 입장 조건은 확인하지 못했다. 사찰이라 입장료가 없을 것으로 보고 0을 넣었으니 확인이 필요하다. 출처마다 '약사사'와 '약사암'을 섞어 쓴다. 출처: https://dh.aks.ac.kr/~heritage/wiki/index.php/%EA%B4%91%EC%A3%BC_%EC%95%BD%EC%82%AC%EC%95%94_%EC%84%9D%EC%A1%B0%EC%97%AC%EB%9E%98%EC%A2%8C%EC%83%81. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
@@ -8584,33 +8948,93 @@
           <t>n_082</t>
         </is>
       </c>
-      <c r="B84" s="11" t="n"/>
-      <c r="C84" s="11" t="n"/>
-      <c r="D84" s="11" t="n"/>
-      <c r="E84" s="11" t="n"/>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>계림동 헌책방거리</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>상점가</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>동구 계림동</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 계림동</t>
+        </is>
+      </c>
       <c r="F84" s="11" t="n"/>
       <c r="G84" s="11" t="n"/>
-      <c r="H84" s="12" t="n"/>
+      <c r="H84" s="12" t="inlineStr">
+        <is>
+          <t>10:00-19:00</t>
+        </is>
+      </c>
       <c r="I84" s="12" t="n"/>
       <c r="J84" s="12" t="n"/>
       <c r="K84" s="12" t="n"/>
       <c r="L84" s="11" t="n"/>
-      <c r="M84" s="11" t="n"/>
-      <c r="N84" s="11" t="n"/>
+      <c r="M84" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N84" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O84" s="11" t="n"/>
       <c r="P84" s="11" t="n"/>
       <c r="Q84" s="11" t="n"/>
-      <c r="R84" s="11" t="n"/>
-      <c r="S84" s="11" t="n"/>
-      <c r="T84" s="11" t="n"/>
-      <c r="U84" s="11" t="n"/>
-      <c r="V84" s="11" t="n"/>
-      <c r="W84" s="11" t="n"/>
-      <c r="X84" s="11" t="n"/>
+      <c r="R84" s="11" t="inlineStr">
+        <is>
+          <t>쇼핑, 산책, 사진</t>
+        </is>
+      </c>
+      <c r="S84" s="11" t="inlineStr">
+        <is>
+          <t>레트로한, 조용한, 정겨운</t>
+        </is>
+      </c>
+      <c r="T84" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U84" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V84" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인</t>
+        </is>
+      </c>
+      <c r="W84" s="11" t="inlineStr">
+        <is>
+          <t>계림동 헌책방 거리, 계림동 책방거리</t>
+        </is>
+      </c>
+      <c r="X84" s="11" t="inlineStr">
+        <is>
+          <t>1980년대 60곳이 넘던 헌책방이 2019년 7곳(일신·광주고서점·광일·문학·백화·유림·학문당), 2022년 6곳으로 줄었다.</t>
+        </is>
+      </c>
       <c r="Y84" s="11" t="n"/>
-      <c r="Z84" s="12" t="n"/>
+      <c r="Z84" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA84" s="11" t="n"/>
-      <c r="AB84" s="11" t="n"/>
+      <c r="AB84" s="11" t="inlineStr">
+        <is>
+          <t>운영시간은 임시값(서점마다 다름). 주소는 동 이름만. 남은 서점 수 확인 필요. 2025~2026년 현재 남은 점포 수는 확인 못 함(나무위키는 '서너 곳'). 2021년 전남일보: 광일·백화서점이 계림1구역 재개발 철거 대상. 2026년 2월 주간경향은 거리를 현재형으로 언급. 출처: https://gwangju.grandculture.net/gwangju/donggu/toc/GC60004969. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -8618,33 +9042,97 @@
           <t>n_083</t>
         </is>
       </c>
-      <c r="B85" s="11" t="n"/>
-      <c r="C85" s="11" t="n"/>
-      <c r="D85" s="11" t="n"/>
-      <c r="E85" s="11" t="n"/>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>은암미술관</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>동구 대의동</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 서석로85번길 8-12</t>
+        </is>
+      </c>
       <c r="F85" s="11" t="n"/>
       <c r="G85" s="11" t="n"/>
-      <c r="H85" s="12" t="n"/>
+      <c r="H85" s="12" t="inlineStr">
+        <is>
+          <t>10:00-17:00</t>
+        </is>
+      </c>
       <c r="I85" s="12" t="n"/>
       <c r="J85" s="12" t="n"/>
-      <c r="K85" s="12" t="n"/>
-      <c r="L85" s="11" t="n"/>
-      <c r="M85" s="11" t="n"/>
-      <c r="N85" s="11" t="n"/>
+      <c r="K85" s="12" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
+          <t>공휴일, 설·추석 연휴</t>
+        </is>
+      </c>
+      <c r="M85" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N85" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O85" s="11" t="n"/>
       <c r="P85" s="11" t="n"/>
       <c r="Q85" s="11" t="n"/>
-      <c r="R85" s="11" t="n"/>
-      <c r="S85" s="11" t="n"/>
-      <c r="T85" s="11" t="n"/>
-      <c r="U85" s="11" t="n"/>
-      <c r="V85" s="11" t="n"/>
+      <c r="R85" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람</t>
+        </is>
+      </c>
+      <c r="S85" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 아늑한</t>
+        </is>
+      </c>
+      <c r="T85" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U85" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V85" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인</t>
+        </is>
+      </c>
       <c r="W85" s="11" t="n"/>
-      <c r="X85" s="11" t="n"/>
+      <c r="X85" s="11" t="inlineStr">
+        <is>
+          <t>2010년 6월 설립된 사립 미술관. 기획전·초대전과 인문학 강좌, 음악회를 연다.</t>
+        </is>
+      </c>
       <c r="Y85" s="11" t="n"/>
-      <c r="Z85" s="12" t="n"/>
+      <c r="Z85" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA85" s="11" t="n"/>
-      <c r="AB85" s="11" t="n"/>
+      <c r="AB85" s="11" t="inlineStr">
+        <is>
+          <t>관람료 0원은 동구 공공데이터(기준일 2025-06-26) 표기로, 해당 항목이 은암미술관을 가리키는지 확실하지 않음. 전화가 062-231-5299와 062-226-6677로 다름. 출처: https://www.yugacrew.com/gwangju/donggu/museum/122_23. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
@@ -8652,33 +9140,97 @@
           <t>n_084</t>
         </is>
       </c>
-      <c r="B86" s="11" t="n"/>
-      <c r="C86" s="11" t="n"/>
-      <c r="D86" s="11" t="n"/>
-      <c r="E86" s="11" t="n"/>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>드영미술관</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>동구 동명동</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 성촌길 6</t>
+        </is>
+      </c>
       <c r="F86" s="11" t="n"/>
       <c r="G86" s="11" t="n"/>
-      <c r="H86" s="12" t="n"/>
+      <c r="H86" s="12" t="inlineStr">
+        <is>
+          <t>10:00-18:00</t>
+        </is>
+      </c>
       <c r="I86" s="12" t="n"/>
       <c r="J86" s="12" t="n"/>
-      <c r="K86" s="12" t="n"/>
+      <c r="K86" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
       <c r="L86" s="11" t="n"/>
-      <c r="M86" s="11" t="n"/>
-      <c r="N86" s="11" t="n"/>
+      <c r="M86" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N86" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O86" s="11" t="n"/>
       <c r="P86" s="11" t="n"/>
       <c r="Q86" s="11" t="n"/>
-      <c r="R86" s="11" t="n"/>
-      <c r="S86" s="11" t="n"/>
-      <c r="T86" s="11" t="n"/>
-      <c r="U86" s="11" t="n"/>
-      <c r="V86" s="11" t="n"/>
-      <c r="W86" s="11" t="n"/>
-      <c r="X86" s="11" t="n"/>
+      <c r="R86" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람</t>
+        </is>
+      </c>
+      <c r="S86" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 현대적인, 아늑한</t>
+        </is>
+      </c>
+      <c r="T86" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U86" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V86" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W86" s="11" t="inlineStr">
+        <is>
+          <t>D'young Art Museum</t>
+        </is>
+      </c>
+      <c r="X86" s="11" t="inlineStr">
+        <is>
+          <t>2018년 5월 1일 개관한 등록 사립 미술관. 기획·상설전시와 성인 강좌, 어린이 뮤지엄 교육을 운영한다.</t>
+        </is>
+      </c>
       <c r="Y86" s="11" t="n"/>
-      <c r="Z86" s="12" t="n"/>
+      <c r="Z86" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA86" s="11" t="n"/>
-      <c r="AB86" s="11" t="n"/>
+      <c r="AB86" s="11" t="inlineStr">
+        <is>
+          <t>성인 관람료 미확인(0 으로 넣음). 성인 관람료는 확인 못 함(yugacrew 는 '무료'와 '어린이 무료'를 함께 적음). 행정동이 동명동인지는 확인 못 함(성촌길은 동명동 일대로 보이나 미확인). 전화 062-223-6515. 동명동 카페거리 근처. 출처: https://www.yugacrew.com/gwangju/donggu/museum/122_2. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
@@ -8686,33 +9238,93 @@
           <t>n_085</t>
         </is>
       </c>
-      <c r="B87" s="11" t="n"/>
-      <c r="C87" s="11" t="n"/>
-      <c r="D87" s="11" t="n"/>
-      <c r="E87" s="11" t="n"/>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>무등산 보리밥 거리</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>동구 지산동</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 지호로127번길 29</t>
+        </is>
+      </c>
       <c r="F87" s="11" t="n"/>
       <c r="G87" s="11" t="n"/>
-      <c r="H87" s="12" t="n"/>
+      <c r="H87" s="12" t="inlineStr">
+        <is>
+          <t>10:00-20:00</t>
+        </is>
+      </c>
       <c r="I87" s="12" t="n"/>
       <c r="J87" s="12" t="n"/>
       <c r="K87" s="12" t="n"/>
       <c r="L87" s="11" t="n"/>
-      <c r="M87" s="11" t="n"/>
-      <c r="N87" s="11" t="n"/>
+      <c r="M87" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N87" s="11" t="n">
+        <v>12000</v>
+      </c>
       <c r="O87" s="11" t="n"/>
       <c r="P87" s="11" t="n"/>
       <c r="Q87" s="11" t="n"/>
-      <c r="R87" s="11" t="n"/>
-      <c r="S87" s="11" t="n"/>
-      <c r="T87" s="11" t="n"/>
-      <c r="U87" s="11" t="n"/>
-      <c r="V87" s="11" t="n"/>
-      <c r="W87" s="11" t="n"/>
-      <c r="X87" s="11" t="n"/>
+      <c r="R87" s="11" t="inlineStr">
+        <is>
+          <t>식사</t>
+        </is>
+      </c>
+      <c r="S87" s="11" t="inlineStr">
+        <is>
+          <t>정겨운, 전통적인, 캐주얼한</t>
+        </is>
+      </c>
+      <c r="T87" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U87" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V87" s="11" t="inlineStr">
+        <is>
+          <t>친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W87" s="11" t="inlineStr">
+        <is>
+          <t>무등산 보리밥지구, 증심사 보리밥 거리, 지산유원지 보리밥집</t>
+        </is>
+      </c>
+      <c r="X87" s="11" t="inlineStr">
+        <is>
+          <t>무등산 자락 지산유원지와 증심사지구 일대에 보리밥집이 몰려 있다.</t>
+        </is>
+      </c>
       <c r="Y87" s="11" t="n"/>
-      <c r="Z87" s="12" t="n"/>
+      <c r="Z87" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA87" s="11" t="n"/>
-      <c r="AB87" s="11" t="n"/>
+      <c r="AB87" s="11" t="inlineStr">
+        <is>
+          <t>운영시간은 임시값. 주소는 예시 가게(지산골 온천보리밥). 1인 지출은 어림값. 공식 명칭 '보리밥 거리'는 확인 못 함. 출처가 대부분 2015년 이전 자료. 예시 가게 지산골 온천보리밥은 지호로127번길 29(리뷰 사이트 기준). 증심사지구 쪽과 지산유원지 쪽 두 곳에 나뉘어 있을 수 있음. 출처: https://www.sidae.com/article/2015042014108066720. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -8720,33 +9332,97 @@
           <t>n_086</t>
         </is>
       </c>
-      <c r="B88" s="11" t="n"/>
-      <c r="C88" s="11" t="n"/>
-      <c r="D88" s="11" t="n"/>
-      <c r="E88" s="11" t="n"/>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>우제길미술관</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>동구 운림동</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 의재로 140-6</t>
+        </is>
+      </c>
       <c r="F88" s="11" t="n"/>
       <c r="G88" s="11" t="n"/>
-      <c r="H88" s="12" t="n"/>
+      <c r="H88" s="12" t="inlineStr">
+        <is>
+          <t>11:00-18:00</t>
+        </is>
+      </c>
       <c r="I88" s="12" t="n"/>
       <c r="J88" s="12" t="n"/>
-      <c r="K88" s="12" t="n"/>
+      <c r="K88" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
       <c r="L88" s="11" t="n"/>
-      <c r="M88" s="11" t="n"/>
-      <c r="N88" s="11" t="n"/>
+      <c r="M88" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N88" s="11" t="n">
+        <v>3000</v>
+      </c>
       <c r="O88" s="11" t="n"/>
       <c r="P88" s="11" t="n"/>
       <c r="Q88" s="11" t="n"/>
-      <c r="R88" s="11" t="n"/>
-      <c r="S88" s="11" t="n"/>
-      <c r="T88" s="11" t="n"/>
-      <c r="U88" s="11" t="n"/>
-      <c r="V88" s="11" t="n"/>
-      <c r="W88" s="11" t="n"/>
-      <c r="X88" s="11" t="n"/>
+      <c r="R88" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 건축 구경</t>
+        </is>
+      </c>
+      <c r="S88" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 현대적인</t>
+        </is>
+      </c>
+      <c r="T88" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U88" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V88" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인</t>
+        </is>
+      </c>
+      <c r="W88" s="11" t="inlineStr">
+        <is>
+          <t>Woo Jaeghil Art Museum</t>
+        </is>
+      </c>
+      <c r="X88" s="11" t="inlineStr">
+        <is>
+          <t>'빛의 화가'로 불리는 추상화가 우제길의 사립 미술관.</t>
+        </is>
+      </c>
       <c r="Y88" s="11" t="n"/>
-      <c r="Z88" s="12" t="n"/>
+      <c r="Z88" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA88" s="11" t="n"/>
-      <c r="AB88" s="11" t="n"/>
+      <c r="AB88" s="11" t="inlineStr">
+        <is>
+          <t>주말·공휴일은 10:00 개관. 운영시간이 출처마다 다름: yugacrew(공공데이터 2025-06-26)는 평일 11:00-18:00·주말 10:00-18:00, ktriptips 는 11:00-17:00. 출처: https://www.yugacrew.com/gwangju/donggu/museum/122_20. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
@@ -8754,33 +9430,93 @@
           <t>n_087</t>
         </is>
       </c>
-      <c r="B89" s="11" t="n"/>
-      <c r="C89" s="11" t="n"/>
-      <c r="D89" s="11" t="n"/>
-      <c r="E89" s="11" t="n"/>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>미로센터</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>동구 궁동</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 예술길 18-1</t>
+        </is>
+      </c>
       <c r="F89" s="11" t="n"/>
       <c r="G89" s="11" t="n"/>
-      <c r="H89" s="12" t="n"/>
+      <c r="H89" s="12" t="inlineStr">
+        <is>
+          <t>10:00-17:00</t>
+        </is>
+      </c>
       <c r="I89" s="12" t="n"/>
       <c r="J89" s="12" t="n"/>
       <c r="K89" s="12" t="n"/>
       <c r="L89" s="11" t="n"/>
-      <c r="M89" s="11" t="n"/>
-      <c r="N89" s="11" t="n"/>
+      <c r="M89" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N89" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O89" s="11" t="n"/>
       <c r="P89" s="11" t="n"/>
       <c r="Q89" s="11" t="n"/>
-      <c r="R89" s="11" t="n"/>
-      <c r="S89" s="11" t="n"/>
-      <c r="T89" s="11" t="n"/>
-      <c r="U89" s="11" t="n"/>
-      <c r="V89" s="11" t="n"/>
-      <c r="W89" s="11" t="n"/>
-      <c r="X89" s="11" t="n"/>
+      <c r="R89" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 공방 체험</t>
+        </is>
+      </c>
+      <c r="S89" s="11" t="inlineStr">
+        <is>
+          <t>현대적인, 캐주얼한</t>
+        </is>
+      </c>
+      <c r="T89" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U89" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V89" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W89" s="11" t="inlineStr">
+        <is>
+          <t>MIRO센터, 미로라운지</t>
+        </is>
+      </c>
+      <c r="X89" s="11" t="inlineStr">
+        <is>
+          <t>2019년 문을 연 예술의 거리 문화복합시설로 갤러리, 극장, 라이브러리, 공방, 다목적 공간과 교육·체험 공간 '미로라운지'를 갖췄다.</t>
+        </is>
+      </c>
       <c r="Y89" s="11" t="n"/>
-      <c r="Z89" s="12" t="n"/>
+      <c r="Z89" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA89" s="11" t="n"/>
-      <c r="AB89" s="11" t="n"/>
+      <c r="AB89" s="11" t="inlineStr">
+        <is>
+          <t>예술의 거리 안. 주소는 같은 단지(동구문화원) 기준, 확인 필요. 휴관일 미확인. EXISTING 의 '예술의 거리' 안에 있는 별도 시설. 정확한 도로명은 확인 못 함(예술길 18-1 'C동'에 동구문화원이 있다는 자료가 있어 예술길 18-1 일대로 보임). 출처: https://www.donggu.kr/menu.es?mid=a90307000000. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
@@ -8788,33 +9524,89 @@
           <t>n_088</t>
         </is>
       </c>
-      <c r="B90" s="11" t="n"/>
-      <c r="C90" s="11" t="n"/>
-      <c r="D90" s="11" t="n"/>
-      <c r="E90" s="11" t="n"/>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>비움박물관</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>동구 궁동</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 제봉로 143-1</t>
+        </is>
+      </c>
       <c r="F90" s="11" t="n"/>
       <c r="G90" s="11" t="n"/>
-      <c r="H90" s="12" t="n"/>
+      <c r="H90" s="12" t="inlineStr">
+        <is>
+          <t>10:00-18:00</t>
+        </is>
+      </c>
       <c r="I90" s="12" t="n"/>
       <c r="J90" s="12" t="n"/>
       <c r="K90" s="12" t="n"/>
       <c r="L90" s="11" t="n"/>
-      <c r="M90" s="11" t="n"/>
-      <c r="N90" s="11" t="n"/>
+      <c r="M90" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N90" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O90" s="11" t="n"/>
       <c r="P90" s="11" t="n"/>
       <c r="Q90" s="11" t="n"/>
-      <c r="R90" s="11" t="n"/>
-      <c r="S90" s="11" t="n"/>
-      <c r="T90" s="11" t="n"/>
-      <c r="U90" s="11" t="n"/>
-      <c r="V90" s="11" t="n"/>
+      <c r="R90" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 역사 탐방</t>
+        </is>
+      </c>
+      <c r="S90" s="11" t="inlineStr">
+        <is>
+          <t>레트로한, 정겨운, 전통적인</t>
+        </is>
+      </c>
+      <c r="T90" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U90" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V90" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
       <c r="W90" s="11" t="n"/>
-      <c r="X90" s="11" t="n"/>
+      <c r="X90" s="11" t="inlineStr">
+        <is>
+          <t>옛 광주읍성 동문 자리에 세운 사립 민속 박물관으로, 이영화 관장이 모은 밥사발·개다리소반·두레상 같은 서민 생활도구를 전시한다.</t>
+        </is>
+      </c>
       <c r="Y90" s="11" t="n"/>
-      <c r="Z90" s="12" t="n"/>
+      <c r="Z90" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA90" s="11" t="n"/>
-      <c r="AB90" s="11" t="n"/>
+      <c r="AB90" s="11" t="inlineStr">
+        <is>
+          <t>성인 관람료·휴관일 미확인(0 으로 넣음). 성인 관람료와 휴관일은 확인 못 함(어린이는 무료로 표기). 관람 1시간~1시간 30분(yugacrew). 행정동 궁동은 동구 관광 누리집이 '예술의 거리 인근'으로 소개한 데서 추정한 것. 출처: https://www.ytn.co.kr/_ln/0115_202011070535089804. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
@@ -8822,33 +9614,97 @@
           <t>n_089</t>
         </is>
       </c>
-      <c r="B91" s="11" t="n"/>
-      <c r="C91" s="11" t="n"/>
-      <c r="D91" s="11" t="n"/>
-      <c r="E91" s="11" t="n"/>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>금남지하도상가</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>상점가</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>동구 금남로1가</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 서석로 지하 56</t>
+        </is>
+      </c>
       <c r="F91" s="11" t="n"/>
       <c r="G91" s="11" t="n"/>
-      <c r="H91" s="12" t="n"/>
+      <c r="H91" s="12" t="inlineStr">
+        <is>
+          <t>10:00-19:00</t>
+        </is>
+      </c>
       <c r="I91" s="12" t="n"/>
       <c r="J91" s="12" t="n"/>
       <c r="K91" s="12" t="n"/>
-      <c r="L91" s="11" t="n"/>
-      <c r="M91" s="11" t="n"/>
-      <c r="N91" s="11" t="n"/>
+      <c r="L91" s="11" t="inlineStr">
+        <is>
+          <t>매월 첫째 일요일</t>
+        </is>
+      </c>
+      <c r="M91" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N91" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O91" s="11" t="n"/>
       <c r="P91" s="11" t="n"/>
       <c r="Q91" s="11" t="n"/>
-      <c r="R91" s="11" t="n"/>
-      <c r="S91" s="11" t="n"/>
-      <c r="T91" s="11" t="n"/>
-      <c r="U91" s="11" t="n"/>
-      <c r="V91" s="11" t="n"/>
-      <c r="W91" s="11" t="n"/>
-      <c r="X91" s="11" t="n"/>
+      <c r="R91" s="11" t="inlineStr">
+        <is>
+          <t>쇼핑, 산책</t>
+        </is>
+      </c>
+      <c r="S91" s="11" t="inlineStr">
+        <is>
+          <t>레트로한, 캐주얼한</t>
+        </is>
+      </c>
+      <c r="T91" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U91" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V91" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W91" s="11" t="inlineStr">
+        <is>
+          <t>금남로 지하상가, 금남지하상가</t>
+        </is>
+      </c>
+      <c r="X91" s="11" t="inlineStr">
+        <is>
+          <t>금남로 아래 지하상가로 2024년 기준 점포 371개, 그중 47곳이 비어 있었다(광주도시공사 자료).</t>
+        </is>
+      </c>
       <c r="Y91" s="11" t="n"/>
-      <c r="Z91" s="12" t="n"/>
+      <c r="Z91" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA91" s="11" t="n"/>
-      <c r="AB91" s="11" t="n"/>
+      <c r="AB91" s="11" t="inlineStr">
+        <is>
+          <t>매월 첫째 일요일 휴무. 비 오는 날 금남로·충장로 실내 동선. 운영시간·휴무는 한국관광공사 데이터 인용 사이트 기준(정보 기준일 2026-09-29). 점포별 영업시간은 따로이며 10:00-22:00 점포도 있음. 비 오는 날 금남로·충장로를 지나는 실내 동선으로 쓸 수 있음. 출처: https://info.koreacharts.com/tour/1621305/contents.html. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
@@ -8856,33 +9712,93 @@
           <t>n_090</t>
         </is>
       </c>
-      <c r="B92" s="11" t="n"/>
-      <c r="C92" s="11" t="n"/>
-      <c r="D92" s="11" t="n"/>
-      <c r="E92" s="11" t="n"/>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>너릿재 옛길 (너릿재 공원)</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>동구 선교동</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 남문로 48-8</t>
+        </is>
+      </c>
       <c r="F92" s="11" t="n"/>
       <c r="G92" s="11" t="n"/>
-      <c r="H92" s="12" t="n"/>
+      <c r="H92" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I92" s="12" t="n"/>
       <c r="J92" s="12" t="n"/>
       <c r="K92" s="12" t="n"/>
       <c r="L92" s="11" t="n"/>
-      <c r="M92" s="11" t="n"/>
-      <c r="N92" s="11" t="n"/>
+      <c r="M92" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="N92" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O92" s="11" t="n"/>
       <c r="P92" s="11" t="n"/>
       <c r="Q92" s="11" t="n"/>
-      <c r="R92" s="11" t="n"/>
-      <c r="S92" s="11" t="n"/>
-      <c r="T92" s="11" t="n"/>
-      <c r="U92" s="11" t="n"/>
-      <c r="V92" s="11" t="n"/>
-      <c r="W92" s="11" t="n"/>
-      <c r="X92" s="11" t="n"/>
+      <c r="R92" s="11" t="inlineStr">
+        <is>
+          <t>산책, 사진, 휴식</t>
+        </is>
+      </c>
+      <c r="S92" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 정겨운</t>
+        </is>
+      </c>
+      <c r="T92" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U92" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V92" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W92" s="11" t="inlineStr">
+        <is>
+          <t>너릿재 숲길, 너릿재 명품 숲길, 너릿재옛길</t>
+        </is>
+      </c>
+      <c r="X92" s="11" t="inlineStr">
+        <is>
+          <t>1971년 너릿재 터널이 뚫리기 전까지 광주와 화순을 잇던 고갯길로, 벚꽃길·배수로·순환산책로 정비를 거쳐 2012년 7월 숲길로 단장됐다.</t>
+        </is>
+      </c>
       <c r="Y92" s="11" t="n"/>
-      <c r="Z92" s="12" t="n"/>
+      <c r="Z92" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA92" s="11" t="n"/>
-      <c r="AB92" s="11" t="n"/>
+      <c r="AB92" s="11" t="inlineStr">
+        <is>
+          <t>공원 안 '데굴데굴 너릿재 유아숲'(유아 숲 체험) 있음. 주소가 화순 쪽 기준일 수 있음. 주소는 ktriptips 항목(전남광주통합특별시 표기)에서 가져왔다. 그런데 같은 항목의 문의처가 화순군 관광기획팀(061-379-3501)이라 화순 쪽 기준일 수 있다. 출처: https://www.ktriptips.com/kor/tourspot/127356. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
@@ -8890,33 +9806,93 @@
           <t>n_091</t>
         </is>
       </c>
-      <c r="B93" s="11" t="n"/>
-      <c r="C93" s="11" t="n"/>
-      <c r="D93" s="11" t="n"/>
-      <c r="E93" s="11" t="n"/>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>무등산 옛길 1구간 (산수동~원효사)</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>동구 산수동</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 산수동</t>
+        </is>
+      </c>
       <c r="F93" s="11" t="n"/>
       <c r="G93" s="11" t="n"/>
-      <c r="H93" s="12" t="n"/>
+      <c r="H93" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I93" s="12" t="n"/>
       <c r="J93" s="12" t="n"/>
       <c r="K93" s="12" t="n"/>
       <c r="L93" s="11" t="n"/>
-      <c r="M93" s="11" t="n"/>
-      <c r="N93" s="11" t="n"/>
+      <c r="M93" s="11" t="n">
+        <v>180</v>
+      </c>
+      <c r="N93" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O93" s="11" t="n"/>
       <c r="P93" s="11" t="n"/>
       <c r="Q93" s="11" t="n"/>
-      <c r="R93" s="11" t="n"/>
-      <c r="S93" s="11" t="n"/>
-      <c r="T93" s="11" t="n"/>
-      <c r="U93" s="11" t="n"/>
-      <c r="V93" s="11" t="n"/>
-      <c r="W93" s="11" t="n"/>
-      <c r="X93" s="11" t="n"/>
+      <c r="R93" s="11" t="inlineStr">
+        <is>
+          <t>산책, 역사 탐방, 사진</t>
+        </is>
+      </c>
+      <c r="S93" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T93" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U93" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V93" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W93" s="11" t="inlineStr">
+        <is>
+          <t>무등산 옛길 1코스, 산수오거리~원효사 옛길</t>
+        </is>
+      </c>
+      <c r="X93" s="11" t="inlineStr">
+        <is>
+          <t>2009년 복원한 무등산 옛길의 첫 구간이다.</t>
+        </is>
+      </c>
       <c r="Y93" s="11" t="n"/>
-      <c r="Z93" s="12" t="n"/>
+      <c r="Z93" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA93" s="11" t="n"/>
-      <c r="AB93" s="11" t="n"/>
+      <c r="AB93" s="11" t="inlineStr">
+        <is>
+          <t>출발점만 동구(도착 원효사는 북구). 편도 7.75km. 주소는 동 이름만. 출발점은 동구 산수동이지만 길 대부분과 도착점(원효사)은 북구다. 출발점의 도로명 주소는 확인하지 못했다. 출처: https://www.ktriptips.com/kor/leisure/1051763. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
@@ -8924,33 +9900,93 @@
           <t>n_092</t>
         </is>
       </c>
-      <c r="B94" s="11" t="n"/>
-      <c r="C94" s="11" t="n"/>
-      <c r="D94" s="11" t="n"/>
-      <c r="E94" s="11" t="n"/>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>광주 전통문화관</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>동구 운림동</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 운림동 323</t>
+        </is>
+      </c>
       <c r="F94" s="11" t="n"/>
       <c r="G94" s="11" t="n"/>
-      <c r="H94" s="12" t="n"/>
+      <c r="H94" s="12" t="inlineStr">
+        <is>
+          <t>09:00-18:00</t>
+        </is>
+      </c>
       <c r="I94" s="12" t="n"/>
       <c r="J94" s="12" t="n"/>
       <c r="K94" s="12" t="n"/>
       <c r="L94" s="11" t="n"/>
-      <c r="M94" s="11" t="n"/>
-      <c r="N94" s="11" t="n"/>
+      <c r="M94" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N94" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O94" s="11" t="n"/>
       <c r="P94" s="11" t="n"/>
       <c r="Q94" s="11" t="n"/>
-      <c r="R94" s="11" t="n"/>
-      <c r="S94" s="11" t="n"/>
-      <c r="T94" s="11" t="n"/>
-      <c r="U94" s="11" t="n"/>
-      <c r="V94" s="11" t="n"/>
-      <c r="W94" s="11" t="n"/>
-      <c r="X94" s="11" t="n"/>
+      <c r="R94" s="11" t="inlineStr">
+        <is>
+          <t>건축 구경, 전시 관람, 공연·영화, 사진</t>
+        </is>
+      </c>
+      <c r="S94" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T94" s="11" t="inlineStr">
+        <is>
+          <t>실내외</t>
+        </is>
+      </c>
+      <c r="U94" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V94" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 연인, 가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W94" s="11" t="inlineStr">
+        <is>
+          <t>무등산 전통문화관, 무송원</t>
+        </is>
+      </c>
+      <c r="X94" s="11" t="inlineStr">
+        <is>
+          <t>무등산국립공원 초입에 2012년 전통한옥 무송원(撫松院)을 옮겨 지어 조성했다.</t>
+        </is>
+      </c>
       <c r="Y94" s="11" t="n"/>
-      <c r="Z94" s="12" t="n"/>
+      <c r="Z94" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA94" s="11" t="n"/>
-      <c r="AB94" s="11" t="n"/>
+      <c r="AB94" s="11" t="inlineStr">
+        <is>
+          <t>주소는 지번. 매주 토요 상설공연(2024년 계획) 현황 미확인. 지번 주소는 동구 운림동 323(DH 교육용 위키)이고 도로명 주소는 확인하지 못했다. 출처: https://www.ktriptips.com/kor/culture/2733545. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
@@ -8958,33 +9994,93 @@
           <t>n_093</t>
         </is>
       </c>
-      <c r="B95" s="11" t="n"/>
-      <c r="C95" s="11" t="n"/>
-      <c r="D95" s="11" t="n"/>
-      <c r="E95" s="11" t="n"/>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>지산동 오층석탑</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>동구 지산동</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 지산동 448-4</t>
+        </is>
+      </c>
       <c r="F95" s="11" t="n"/>
       <c r="G95" s="11" t="n"/>
-      <c r="H95" s="12" t="n"/>
+      <c r="H95" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I95" s="12" t="n"/>
       <c r="J95" s="12" t="n"/>
       <c r="K95" s="12" t="n"/>
       <c r="L95" s="11" t="n"/>
-      <c r="M95" s="11" t="n"/>
-      <c r="N95" s="11" t="n"/>
+      <c r="M95" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N95" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O95" s="11" t="n"/>
       <c r="P95" s="11" t="n"/>
       <c r="Q95" s="11" t="n"/>
-      <c r="R95" s="11" t="n"/>
-      <c r="S95" s="11" t="n"/>
-      <c r="T95" s="11" t="n"/>
-      <c r="U95" s="11" t="n"/>
-      <c r="V95" s="11" t="n"/>
-      <c r="W95" s="11" t="n"/>
-      <c r="X95" s="11" t="n"/>
+      <c r="R95" s="11" t="inlineStr">
+        <is>
+          <t>역사 탐방, 사진</t>
+        </is>
+      </c>
+      <c r="S95" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 전통적인</t>
+        </is>
+      </c>
+      <c r="T95" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U95" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁</t>
+        </is>
+      </c>
+      <c r="V95" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W95" s="11" t="inlineStr">
+        <is>
+          <t>광주 동오층석탑, 동오층석탑</t>
+        </is>
+      </c>
+      <c r="X95" s="11" t="inlineStr">
+        <is>
+          <t>통일신라 후기 양식의 높이 7.24m 석탑으로, 보물 제110호(1963.1.21 지정)다.</t>
+        </is>
+      </c>
       <c r="Y95" s="11" t="n"/>
-      <c r="Z95" s="12" t="n"/>
+      <c r="Z95" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA95" s="11" t="n"/>
-      <c r="AB95" s="11" t="n"/>
+      <c r="AB95" s="11" t="inlineStr">
+        <is>
+          <t>주소는 지번. 주차 불가. 지산유원지 쪽 코스에 곁들이기. 지번은 동구 지산동 448-4이고 도로명 주소는 확인하지 못했다. ktriptips에 '상시 개방, 주차 불가'로 나온다(문의: 동구청 문화관광과 062-608-2401). 출처: https://www.ktriptips.com/kor/tourspot/1621388. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
@@ -8992,33 +10088,93 @@
           <t>n_094</t>
         </is>
       </c>
-      <c r="B96" s="11" t="n"/>
-      <c r="C96" s="11" t="n"/>
-      <c r="D96" s="11" t="n"/>
-      <c r="E96" s="11" t="n"/>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>대인예술시장 한평갤러리</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>동구 대인동</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 제봉로184번길 9-10</t>
+        </is>
+      </c>
       <c r="F96" s="11" t="n"/>
       <c r="G96" s="11" t="n"/>
-      <c r="H96" s="12" t="n"/>
+      <c r="H96" s="12" t="inlineStr">
+        <is>
+          <t>10:00-18:00</t>
+        </is>
+      </c>
       <c r="I96" s="12" t="n"/>
       <c r="J96" s="12" t="n"/>
       <c r="K96" s="12" t="n"/>
       <c r="L96" s="11" t="n"/>
-      <c r="M96" s="11" t="n"/>
-      <c r="N96" s="11" t="n"/>
+      <c r="M96" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N96" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O96" s="11" t="n"/>
       <c r="P96" s="11" t="n"/>
       <c r="Q96" s="11" t="n"/>
-      <c r="R96" s="11" t="n"/>
-      <c r="S96" s="11" t="n"/>
-      <c r="T96" s="11" t="n"/>
-      <c r="U96" s="11" t="n"/>
-      <c r="V96" s="11" t="n"/>
-      <c r="W96" s="11" t="n"/>
-      <c r="X96" s="11" t="n"/>
+      <c r="R96" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 시장 구경, 사진</t>
+        </is>
+      </c>
+      <c r="S96" s="11" t="inlineStr">
+        <is>
+          <t>정겨운, 레트로한</t>
+        </is>
+      </c>
+      <c r="T96" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U96" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁, 밤</t>
+        </is>
+      </c>
+      <c r="V96" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인</t>
+        </is>
+      </c>
+      <c r="W96" s="11" t="inlineStr">
+        <is>
+          <t>한 평 갤러리, 한평 갤러리</t>
+        </is>
+      </c>
+      <c r="X96" s="11" t="inlineStr">
+        <is>
+          <t>대인예술시장 북쪽 끝에 있는 한 평 크기의 전시 공간이다.</t>
+        </is>
+      </c>
       <c r="Y96" s="11" t="n"/>
-      <c r="Z96" s="12" t="n"/>
+      <c r="Z96" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA96" s="11" t="n"/>
-      <c r="AB96" s="11" t="n"/>
+      <c r="AB96" s="11" t="inlineStr">
+        <is>
+          <t>토요일은 18:00-22:00(야시장 때). 대인예술시장 안. 대인예술시장(EXISTING) 안에 있는 시설이다. 겹친다고 보면 updates 로 옮겨도 된다. 운영 시간과 연중무휴, 전화 062-233-0270 은 2024-11 등록 안내 페이지 하나에서만 나왔다. 출처: https://www.ktriptips.com/kor/culture/3406745. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
@@ -9026,33 +10182,93 @@
           <t>n_095</t>
         </is>
       </c>
-      <c r="B97" s="11" t="n"/>
-      <c r="C97" s="11" t="n"/>
-      <c r="D97" s="11" t="n"/>
-      <c r="E97" s="11" t="n"/>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>광주독립영화관 GIFT</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>동구 서석동</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 서석동</t>
+        </is>
+      </c>
       <c r="F97" s="11" t="n"/>
       <c r="G97" s="11" t="n"/>
-      <c r="H97" s="12" t="n"/>
+      <c r="H97" s="12" t="inlineStr">
+        <is>
+          <t>12:00-22:00</t>
+        </is>
+      </c>
       <c r="I97" s="12" t="n"/>
       <c r="J97" s="12" t="n"/>
       <c r="K97" s="12" t="n"/>
       <c r="L97" s="11" t="n"/>
-      <c r="M97" s="11" t="n"/>
-      <c r="N97" s="11" t="n"/>
+      <c r="M97" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="N97" s="11" t="n">
+        <v>7000</v>
+      </c>
       <c r="O97" s="11" t="n"/>
       <c r="P97" s="11" t="n"/>
       <c r="Q97" s="11" t="n"/>
-      <c r="R97" s="11" t="n"/>
-      <c r="S97" s="11" t="n"/>
-      <c r="T97" s="11" t="n"/>
-      <c r="U97" s="11" t="n"/>
-      <c r="V97" s="11" t="n"/>
-      <c r="W97" s="11" t="n"/>
-      <c r="X97" s="11" t="n"/>
+      <c r="R97" s="11" t="inlineStr">
+        <is>
+          <t>공연·영화</t>
+        </is>
+      </c>
+      <c r="S97" s="11" t="inlineStr">
+        <is>
+          <t>조용한, 아늑한</t>
+        </is>
+      </c>
+      <c r="T97" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U97" s="11" t="inlineStr">
+        <is>
+          <t>오후, 저녁, 밤</t>
+        </is>
+      </c>
+      <c r="V97" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인</t>
+        </is>
+      </c>
+      <c r="W97" s="11" t="inlineStr">
+        <is>
+          <t>GIFT, 광주독립영화관</t>
+        </is>
+      </c>
+      <c r="X97" s="11" t="inlineStr">
+        <is>
+          <t>영화진흥위원회 지원사업으로 2018년 동구에 문을 연 독립영화 전용관이다. 한국 독립영화를 연중 상영한다.</t>
+        </is>
+      </c>
       <c r="Y97" s="11" t="n"/>
-      <c r="Z97" s="12" t="n"/>
+      <c r="Z97" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA97" s="11" t="n"/>
-      <c r="AB97" s="11" t="n"/>
+      <c r="AB97" s="11" t="inlineStr">
+        <is>
+          <t>운영시간은 임시값(상영 시간표에 따름). 주소는 동 이름만(광주영상복합문화관 6층으로 알려짐). 관람료는 2018년 무렵 기준. 2017년 계획 기사에는 동구 서석동 광주영상복합문화관 6층 G-시네마 상영관을 전용관으로 쓴다고 나온다. 현재 도로명 주소, 상영 시간, 휴관일은 확인 못 함. 출처: https://www.radiokorea.com/news/article.php?uid=496657. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
@@ -9060,33 +10276,97 @@
           <t>n_096</t>
         </is>
       </c>
-      <c r="B98" s="11" t="n"/>
-      <c r="C98" s="11" t="n"/>
-      <c r="D98" s="11" t="n"/>
-      <c r="E98" s="11" t="n"/>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>ACC 어린이문화원</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>문화·전시</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>동구 광산동</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 문화전당로 38</t>
+        </is>
+      </c>
       <c r="F98" s="11" t="n"/>
       <c r="G98" s="11" t="n"/>
-      <c r="H98" s="12" t="n"/>
+      <c r="H98" s="12" t="inlineStr">
+        <is>
+          <t>10:00-18:00</t>
+        </is>
+      </c>
       <c r="I98" s="12" t="n"/>
       <c r="J98" s="12" t="n"/>
-      <c r="K98" s="12" t="n"/>
+      <c r="K98" s="12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
       <c r="L98" s="11" t="n"/>
-      <c r="M98" s="11" t="n"/>
-      <c r="N98" s="11" t="n"/>
+      <c r="M98" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="N98" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O98" s="11" t="n"/>
       <c r="P98" s="11" t="n"/>
       <c r="Q98" s="11" t="n"/>
-      <c r="R98" s="11" t="n"/>
-      <c r="S98" s="11" t="n"/>
-      <c r="T98" s="11" t="n"/>
-      <c r="U98" s="11" t="n"/>
-      <c r="V98" s="11" t="n"/>
-      <c r="W98" s="11" t="n"/>
-      <c r="X98" s="11" t="n"/>
+      <c r="R98" s="11" t="inlineStr">
+        <is>
+          <t>전시 관람, 공방 체험</t>
+        </is>
+      </c>
+      <c r="S98" s="11" t="inlineStr">
+        <is>
+          <t>활기찬, 현대적인</t>
+        </is>
+      </c>
+      <c r="T98" s="11" t="inlineStr">
+        <is>
+          <t>실내</t>
+        </is>
+      </c>
+      <c r="U98" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후</t>
+        </is>
+      </c>
+      <c r="V98" s="11" t="inlineStr">
+        <is>
+          <t>가족, 아이 동반</t>
+        </is>
+      </c>
+      <c r="W98" s="11" t="inlineStr">
+        <is>
+          <t>국립아시아문화전당 어린이문화원</t>
+        </is>
+      </c>
+      <c r="X98" s="11" t="inlineStr">
+        <is>
+          <t>국립아시아문화전당 안의 어린이 시설로, 체험 전시·도서관·공연·창의예술교육을 한곳에서 운영한다.</t>
+        </is>
+      </c>
       <c r="Y98" s="11" t="n"/>
-      <c r="Z98" s="12" t="n"/>
+      <c r="Z98" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA98" s="11" t="n"/>
-      <c r="AB98" s="11" t="n"/>
+      <c r="AB98" s="11" t="inlineStr">
+        <is>
+          <t>ACC 전시관 공통 시간(화~일, 월 휴관)을 넣음, 어린이문화원 적용 여부 미확인. 기본 관람료 미확인(0 으로 넣음). ACC(EXISTING) 안의 별도 관람 시설이다. 관람 시간, 휴관일, 기본 관람료는 확인 못 함. 하우펀 때 어린이체험관은 5,000원 유료였다. 출처: https://xn--ok0b236bp0a.com/place/29021. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
@@ -9094,33 +10374,93 @@
           <t>n_097</t>
         </is>
       </c>
-      <c r="B99" s="11" t="n"/>
-      <c r="C99" s="11" t="n"/>
-      <c r="D99" s="11" t="n"/>
-      <c r="E99" s="11" t="n"/>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>충장 레트로 골목</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>동구 충장로</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 충장로</t>
+        </is>
+      </c>
       <c r="F99" s="11" t="n"/>
       <c r="G99" s="11" t="n"/>
-      <c r="H99" s="12" t="n"/>
+      <c r="H99" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I99" s="12" t="n"/>
       <c r="J99" s="12" t="n"/>
       <c r="K99" s="12" t="n"/>
       <c r="L99" s="11" t="n"/>
-      <c r="M99" s="11" t="n"/>
-      <c r="N99" s="11" t="n"/>
+      <c r="M99" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N99" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O99" s="11" t="n"/>
       <c r="P99" s="11" t="n"/>
       <c r="Q99" s="11" t="n"/>
-      <c r="R99" s="11" t="n"/>
-      <c r="S99" s="11" t="n"/>
-      <c r="T99" s="11" t="n"/>
-      <c r="U99" s="11" t="n"/>
-      <c r="V99" s="11" t="n"/>
-      <c r="W99" s="11" t="n"/>
-      <c r="X99" s="11" t="n"/>
+      <c r="R99" s="11" t="inlineStr">
+        <is>
+          <t>산책, 사진</t>
+        </is>
+      </c>
+      <c r="S99" s="11" t="inlineStr">
+        <is>
+          <t>레트로한, 정겨운</t>
+        </is>
+      </c>
+      <c r="T99" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U99" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁, 밤</t>
+        </is>
+      </c>
+      <c r="V99" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인, 가족</t>
+        </is>
+      </c>
+      <c r="W99" s="11" t="inlineStr">
+        <is>
+          <t>도깨비골목, 꽃피는 충장로 샛길, 영화가 흐르는 골목</t>
+        </is>
+      </c>
+      <c r="X99" s="11" t="inlineStr">
+        <is>
+          <t>충장로 안쪽의 테마 골목 묶음이다.</t>
+        </is>
+      </c>
       <c r="Y99" s="11" t="n"/>
-      <c r="Z99" s="12" t="n"/>
+      <c r="Z99" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA99" s="11" t="n"/>
-      <c r="AB99" s="11" t="n"/>
+      <c r="AB99" s="11" t="inlineStr">
+        <is>
+          <t>충장로 4·5가 일대(도깨비골목·꽃피는 충장로 샛길·영화가 흐르는 골목). 주소는 도로 이름만. 공식 도로명 주소는 따로 없다(충장로 4·5가 일대). 상시 개방 골목이라 00:00-24:00 으로 적었다(골목 안 가게 영업시간은 다름). 충장로 상점가·광주극장(EXISTING)과 이웃해 있다. 출처: https://www.fnnews.com/news/202510011337226782. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
@@ -9128,33 +10468,93 @@
           <t>n_098</t>
         </is>
       </c>
-      <c r="B100" s="11" t="n"/>
-      <c r="C100" s="11" t="n"/>
-      <c r="D100" s="11" t="n"/>
-      <c r="E100" s="11" t="n"/>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>광주폴리 (충장권역)</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>명소·산책</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>동구 충장로</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>전남광주 동구 충장로</t>
+        </is>
+      </c>
       <c r="F100" s="11" t="n"/>
       <c r="G100" s="11" t="n"/>
-      <c r="H100" s="12" t="n"/>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
       <c r="I100" s="12" t="n"/>
       <c r="J100" s="12" t="n"/>
       <c r="K100" s="12" t="n"/>
       <c r="L100" s="11" t="n"/>
-      <c r="M100" s="11" t="n"/>
-      <c r="N100" s="11" t="n"/>
+      <c r="M100" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N100" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O100" s="11" t="n"/>
       <c r="P100" s="11" t="n"/>
       <c r="Q100" s="11" t="n"/>
-      <c r="R100" s="11" t="n"/>
-      <c r="S100" s="11" t="n"/>
-      <c r="T100" s="11" t="n"/>
-      <c r="U100" s="11" t="n"/>
-      <c r="V100" s="11" t="n"/>
-      <c r="W100" s="11" t="n"/>
-      <c r="X100" s="11" t="n"/>
+      <c r="R100" s="11" t="inlineStr">
+        <is>
+          <t>건축 구경, 사진, 산책, 야경</t>
+        </is>
+      </c>
+      <c r="S100" s="11" t="inlineStr">
+        <is>
+          <t>현대적인, 캐주얼한</t>
+        </is>
+      </c>
+      <c r="T100" s="11" t="inlineStr">
+        <is>
+          <t>실외</t>
+        </is>
+      </c>
+      <c r="U100" s="11" t="inlineStr">
+        <is>
+          <t>오전, 오후, 저녁, 밤</t>
+        </is>
+      </c>
+      <c r="V100" s="11" t="inlineStr">
+        <is>
+          <t>혼자, 친구, 연인</t>
+        </is>
+      </c>
+      <c r="W100" s="11" t="inlineStr">
+        <is>
+          <t>광주 폴리, 99칸, 광주사랑방, 유동성조절, 광주사람들</t>
+        </is>
+      </c>
+      <c r="X100" s="11" t="inlineStr">
+        <is>
+          <t>원도심 곳곳에 세운 건축 조형물(폴리)이다.</t>
+        </is>
+      </c>
       <c r="Y100" s="11" t="n"/>
-      <c r="Z100" s="12" t="n"/>
+      <c r="Z100" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="AA100" s="11" t="n"/>
-      <c r="AB100" s="11" t="n"/>
+      <c r="AB100" s="11" t="inlineStr">
+        <is>
+          <t>작품이 흩어져 있어 주소는 도로 이름만('99칸' 충장치안센터 앞 등). 경관조명 유지 여부 미확인. 작품이 여러 곳에 흩어져 있어 대표 주소가 없다. 2025~2026년에도 조명이 유지되는지는 확인 못 함. 코스에는 '99칸'이나 '광주사랑방' 한 점을 좌표로 쓰는 것이 현실적이다. 출처: https://www.seoul.co.kr/news/society/2024/01/24/20240124500213. 초안(자동): 웹 검색 대조, 현장·네이버 미확인. 머무는 시간은 추정값. 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
